--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EEBBBF-F803-6744-BA4A-D5BAA1DF13A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33574F1D-FDFB-334B-ACC5-E56FC6F611CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10940" yWindow="780" windowWidth="18460" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="618">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -380,25 +380,16 @@
     <t>LandtagKroatien</t>
   </si>
   <si>
-    <t>&lt;orgName key="LandtagKroatien" ref=""&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Landtag Kroatien/Parteien/Nationalpartei </t>
   </si>
   <si>
     <t>Nationalpartei</t>
   </si>
   <si>
-    <t>&lt;orgName key="Nationalpartei" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Landtag Kroatien/Parteien/Obzorpartei</t>
   </si>
   <si>
     <t>Obzorpartei</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Obzorpartei" ref=""&gt;</t>
   </si>
   <si>
     <t>Landtag Mähren</t>
@@ -711,9 +702,6 @@
     <t>Pressbuero</t>
   </si>
   <si>
-    <t>&lt;orgName key="Pressbuero" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Museum/Poldi Pezzoli</t>
   </si>
   <si>
@@ -926,9 +914,6 @@
     <t>BudapestiHirlap</t>
   </si>
   <si>
-    <t>&lt;orgName key="BudapestiHirlap" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Presse/Budapester Correspondenz</t>
   </si>
   <si>
@@ -1026,18 +1011,12 @@
     <t>MagyarOrszag</t>
   </si>
   <si>
-    <t>&lt;orgName key="MagyarOrszag" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Presse/Montagspresse</t>
   </si>
   <si>
     <t>Montagspresse</t>
   </si>
   <si>
-    <t>&lt;orgName key="Montagspresse" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Presse/Národní listy</t>
   </si>
   <si>
@@ -1096,9 +1075,6 @@
   </si>
   <si>
     <t>Obzor</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Obzor" ref=""&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Presse/Pester Lloyd </t>
@@ -1264,16 +1240,10 @@
     <t>ChristlichsozialeVereinigung</t>
   </si>
   <si>
-    <t>&lt;orgName key="ChristlichsozialeVereinigung" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Parteien/Club der Böhmischen Abgeordneten (Tschechen)</t>
   </si>
   <si>
     <t>TschechenKlub</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="TschechenKlub" ref=""&gt;</t>
   </si>
   <si>
     <t>Reichsrat/Abgeordnetenhaus/Parteien/Deutsche Agrarier (Deutsche Agrarpartei)</t>
@@ -1328,9 +1298,6 @@
     <t>DeutschoesterreichischerKlub</t>
   </si>
   <si>
-    <t>&lt;orgName key="DeutschoesterreichischerKlub" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Parteien/Deutsche Volkspartei</t>
   </si>
   <si>
@@ -1400,9 +1367,6 @@
     <t>Zentrum</t>
   </si>
   <si>
-    <t>&lt;orgName key="Zentrum" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Parteien/Katholische Volkspartei</t>
   </si>
   <si>
@@ -1436,9 +1400,6 @@
     <t>KonservativerGrossgrundbesitz</t>
   </si>
   <si>
-    <t>&lt;orgName key="KonservativerGrossgrundbesitz" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Parteien/Jungtschechen</t>
   </si>
   <si>
@@ -1557,9 +1518,6 @@
   </si>
   <si>
     <t>Ausgleichsausschuss</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Ausgleichsausschuss" ref=""&gt;</t>
   </si>
   <si>
     <t>Reichsrat/Abgeordnetenhauses/Budgetausschuss</t>
@@ -1632,9 +1590,6 @@
     <t>Reichsrat/Abgeordnetenhaus/Notstandsausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName key="Notstandsausschuss" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Permanenzausschuss</t>
   </si>
   <si>
@@ -1653,36 +1608,24 @@
     <t>Sprachenausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName key="Sprachenausschuss" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhaus/Steuerausschuss</t>
   </si>
   <si>
     <t>Steuerausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName key="Steuerausschuss" ref=""&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reichsrat/Abgeordnetenhauses/Wahlreformausschuss </t>
   </si>
   <si>
     <t>Wahlreformausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName key="Wahlreformausschuss" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichsrat/Abgeordnetenhauses/Zollausschuss</t>
   </si>
   <si>
     <t>Zollausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName key="Zollausschuss" ref=""&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reichsrat/Delegationen </t>
   </si>
   <si>
@@ -1711,9 +1654,6 @@
   </si>
   <si>
     <t>Verfassungspartei</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Verfassungspartei" ref=""&gt;</t>
   </si>
   <si>
     <t>Reichsrat/Staatsschulden-Kontroll-Kommission</t>
@@ -1768,9 +1708,6 @@
     <t>https://d-nb.info/gnd/4194545-1</t>
   </si>
   <si>
-    <t>ungarReichstag</t>
-  </si>
-  <si>
     <t>&lt;orgName key="Reichstag" ref="https://d-nb.info/gnd/4194545-1"&gt;</t>
   </si>
   <si>
@@ -1804,18 +1741,12 @@
     <t>LiberalePartei</t>
   </si>
   <si>
-    <t>&lt;orgName key="LiberalePartei" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Reichstag Ungarn/Parteien/Unabhängigkeitspartei</t>
   </si>
   <si>
     <t>Unabhaengigkeitspartei</t>
   </si>
   <si>
-    <t>&lt;orgName key="Unabhaengigkeitspartei" ref=""&gt;</t>
-  </si>
-  <si>
     <t>Sant Ambrogio</t>
   </si>
   <si>
@@ -1874,9 +1805,6 @@
   </si>
   <si>
     <t>Kronrat</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Kronrat" ref=""&gt;</t>
   </si>
   <si>
     <t>Reichsgericht</t>
@@ -2467,6 +2395,75 @@
       </rPr>
       <t>&gt;</t>
     </r>
+  </si>
+  <si>
+    <t>Reichstag</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Ausgleichsausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Sprachenausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Steuerausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Wahlreformausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Zollausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Verfassungspartei"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="LiberalePartei"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Unabhaengigkeitspartei"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Kronrat"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="LandtagKroatien"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Nationalpartei"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Obzorpartei"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Pressbuero"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="BudapestiHirlap"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="MagyarOrszag"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Obzor"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="ChristlichsozialeVereinigung"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="TschechenKlub"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Zentrum"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="KonservativerGrossgrundbesitz"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Notstandsausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="DeutschoesterreichischerKlub"&gt;</t>
   </si>
 </sst>
 </file>
@@ -2735,7 +2732,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2780,7 +2776,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2803,6 +2799,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2898,12 +2895,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D173" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D173" dataDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="key=wert" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Spalte4" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="key=wert" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Spalte4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Tabelle1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3132,13 +3129,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -3146,91 +3143,91 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="33" t="s">
-        <v>533</v>
+      <c r="A3" s="32" t="s">
+        <v>509</v>
       </c>
       <c r="B3" s="19"/>
-      <c r="C3" s="33" t="s">
-        <v>534</v>
+      <c r="C3" s="32" t="s">
+        <v>510</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="33" t="s">
-        <v>536</v>
+      <c r="A4" s="32" t="s">
+        <v>512</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>538</v>
+        <v>513</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>514</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>611</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="33" t="s">
-        <v>539</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="33" t="s">
-        <v>540</v>
+      <c r="A5" s="32" t="s">
+        <v>515</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="32" t="s">
+        <v>516</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="33" t="s">
-        <v>542</v>
+      <c r="A6" s="32" t="s">
+        <v>518</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>544</v>
+        <v>519</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>520</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>612</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="33" t="s">
-        <v>545</v>
+      <c r="A7" s="32" t="s">
+        <v>521</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="33" t="s">
-        <v>546</v>
+      <c r="C7" s="32" t="s">
+        <v>522</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="33" t="s">
-        <v>548</v>
+      <c r="A8" s="32" t="s">
+        <v>524</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="33" t="s">
-        <v>549</v>
+      <c r="C8" s="32" t="s">
+        <v>525</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="33" t="s">
-        <v>551</v>
+      <c r="A9" s="32" t="s">
+        <v>527</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="33" t="s">
-        <v>552</v>
+      <c r="C9" s="32" t="s">
+        <v>528</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3262,13 +3259,13 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -3276,13 +3273,13 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="32" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -3304,13 +3301,13 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="31" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -3372,13 +3369,13 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="33" t="s">
-        <v>554</v>
-      </c>
-      <c r="B20" s="28" t="s">
+      <c r="A20" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="32" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="6" t="s">
@@ -3386,13 +3383,13 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="31" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3437,32 +3434,32 @@
       <c r="C24" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="34" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="33" t="s">
-        <v>557</v>
+      <c r="A25" s="32" t="s">
+        <v>533</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>556</v>
+        <v>531</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>532</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>613</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="32" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="32" t="s">
         <v>64</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -3470,13 +3467,13 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="31" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -3484,34 +3481,34 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>496</v>
+      <c r="A28" s="31" t="s">
+        <v>473</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="32" t="s">
-        <v>496</v>
+      <c r="C28" s="31" t="s">
+        <v>473</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>497</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A29" s="32" t="s">
-        <v>501</v>
+      <c r="A29" s="31" t="s">
+        <v>477</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="32" t="s">
-        <v>501</v>
+      <c r="C29" s="31" t="s">
+        <v>477</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="35" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="9" t="s">
@@ -3522,13 +3519,13 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="31" t="s">
         <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -3536,265 +3533,265 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="31" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>80</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="31" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="32" t="s">
+      <c r="B33" s="37"/>
+      <c r="C33" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="32" t="s">
+      <c r="D33" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="B34" s="31"/>
+      <c r="C34" s="31" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32" t="s">
-        <v>86</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>87</v>
+        <v>607</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="4" t="s">
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="B38" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="C38" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="39" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="35" t="s">
+      <c r="B39" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="C39" s="41" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="40" t="s">
+      <c r="D39" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="41" t="s">
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="B40" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="C40" s="41" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="40" t="s">
+      <c r="D40" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="41" t="s">
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="42" t="s">
+      <c r="B41" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="C41" s="41" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="40" t="s">
+      <c r="D41" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="41" t="s">
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="B42" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="C42" s="41" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="40" t="s">
+      <c r="D42" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="24" t="s">
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="B43" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="C43" s="41" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="40" t="s">
+      <c r="D43" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B43" s="41" t="s">
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="B44" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="C44" s="41" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="40" t="s">
+      <c r="D44" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="B44" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="4" t="s">
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="B46" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="C46" s="31" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="32" t="s">
+      <c r="D46" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="37" t="s">
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="B47" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="C47" s="31" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="32" t="s">
+      <c r="D47" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="3" t="s">
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A48" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26">
+      <c r="A49" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="B49" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="C49" s="31" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>610</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26">
-      <c r="A49" s="32" t="s">
+      <c r="D49" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="3" t="s">
+    </row>
+    <row r="50" spans="1:26">
+      <c r="A50" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="C49" s="32" t="s">
+      <c r="B50" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="C50" s="42" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="50" spans="1:26">
-      <c r="A50" s="43" t="s">
+      <c r="D50" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="B50" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
@@ -3820,395 +3817,395 @@
       <c r="Z50" s="13"/>
     </row>
     <row r="51" spans="1:26" ht="16">
-      <c r="A51" s="39" t="s">
+      <c r="A51" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B51" s="4" t="s">
+    </row>
+    <row r="52" spans="1:26" ht="16">
+      <c r="A52" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="B52" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="52" spans="1:26" ht="16">
-      <c r="A52" s="39" t="s">
+      <c r="D52" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B52" s="4" t="s">
+    </row>
+    <row r="53" spans="1:26" ht="16">
+      <c r="A53" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="B53" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="53" spans="1:26" ht="16">
-      <c r="A53" s="39" t="s">
+      <c r="D53" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:26">
       <c r="A54" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26">
+      <c r="A55" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B55" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" s="35" t="s">
+      <c r="C55" s="31" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="55" spans="1:26">
-      <c r="A55" s="32" t="s">
+      <c r="D55" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B55" s="37" t="s">
+    </row>
+    <row r="56" spans="1:26">
+      <c r="A56" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="C55" s="32" t="s">
+      <c r="B56" s="3"/>
+      <c r="C56" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D56" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26">
+      <c r="A57" s="32" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="56" spans="1:26">
-      <c r="A56" s="32" t="s">
+      <c r="B57" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="32" t="s">
+      <c r="C57" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="14" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:26">
-      <c r="A57" s="33" t="s">
+    <row r="58" spans="1:26">
+      <c r="A58" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26">
+      <c r="A59" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B59" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C59" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D59" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="58" spans="1:26">
-      <c r="A58" s="33" t="s">
-        <v>558</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="C58" s="33" t="s">
-        <v>560</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
-      <c r="A59" s="32" t="s">
+    <row r="60" spans="1:26">
+      <c r="A60" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="37" t="s">
+      <c r="B60" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C59" s="32" t="s">
+      <c r="C60" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D60" s="45" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:26">
-      <c r="A60" s="45" t="s">
+    <row r="61" spans="1:26">
+      <c r="A61" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="34" t="s">
+      <c r="B61" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C61" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="46" t="s">
+      <c r="D61" s="7" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:26">
-      <c r="A61" s="47" t="s">
+    <row r="62" spans="1:26">
+      <c r="A62" s="32" t="s">
+        <v>537</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26">
+      <c r="A63" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26">
+      <c r="A64" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26">
+      <c r="A65" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C65" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D65" s="36" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26">
-      <c r="A62" s="33" t="s">
-        <v>561</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="33" t="s">
-        <v>562</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26">
-      <c r="A63" s="33" t="s">
-        <v>564</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>565</v>
-      </c>
-      <c r="C63" s="33" t="s">
-        <v>566</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="33" t="s">
-        <v>568</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="65" spans="1:26">
-      <c r="A65" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C65" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:26">
       <c r="A66" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B66" s="48" t="s">
-        <v>190</v>
+        <v>185</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>186</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D66" s="35" t="s">
-        <v>191</v>
+        <v>185</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="30">
-      <c r="A67" s="33" t="s">
-        <v>570</v>
-      </c>
-      <c r="B67" s="49" t="s">
-        <v>571</v>
-      </c>
-      <c r="C67" s="33" t="s">
-        <v>572</v>
+      <c r="A67" s="32" t="s">
+        <v>546</v>
+      </c>
+      <c r="B67" s="48" t="s">
+        <v>547</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>548</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="30">
-      <c r="A68" s="33" t="s">
-        <v>573</v>
+      <c r="A68" s="32" t="s">
+        <v>549</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>574</v>
-      </c>
-      <c r="C68" s="33" t="s">
-        <v>575</v>
+        <v>550</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>551</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
     </row>
     <row r="69" spans="1:26">
       <c r="A69" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="B69" s="48" t="s">
-        <v>193</v>
+        <v>188</v>
+      </c>
+      <c r="B69" s="47" t="s">
+        <v>189</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:26">
       <c r="A70" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:26">
       <c r="A71" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26">
+      <c r="A72" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B71" s="50" t="s">
+      <c r="B72" s="50" t="s">
+        <v>504</v>
+      </c>
+      <c r="C72" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="D72" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" ht="16">
+      <c r="A73" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="D71" s="35" t="s">
+      <c r="B73" s="37" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="72" spans="1:26">
-      <c r="A72" s="32" t="s">
+      <c r="C73" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B72" s="51" t="s">
-        <v>528</v>
-      </c>
-      <c r="C72" s="32" t="s">
+      <c r="D73" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26" ht="16">
-      <c r="A73" s="32" t="s">
+    </row>
+    <row r="74" spans="1:26">
+      <c r="A74" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="B73" s="38" t="s">
+      <c r="B74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C73" s="32" t="s">
+      <c r="C74" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26">
-      <c r="A74" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C74" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:26">
       <c r="A75" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32" t="s">
-        <v>216</v>
+      <c r="A76" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31" t="s">
+        <v>212</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>217</v>
+        <v>609</v>
       </c>
     </row>
     <row r="77" spans="1:26">
       <c r="A77" s="16" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26">
+      <c r="A78" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D77" s="5" t="s">
+    </row>
+    <row r="79" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A79" s="51" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="78" spans="1:26">
-      <c r="A78" s="33" t="s">
+      <c r="B79" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="C79" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="D79" s="18" t="s">
         <v>223</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A79" s="52" t="s">
-        <v>225</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C79" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>228</v>
       </c>
       <c r="E79" s="13"/>
       <c r="F79" s="13"/>
@@ -4234,1263 +4231,1263 @@
       <c r="Z79" s="13"/>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A80" s="39" t="s">
+      <c r="A80" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A81" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="C81" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39" t="s">
+      <c r="D81" s="5"/>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A82" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="B82" s="52" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A81" s="39" t="s">
+      <c r="C82" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B81" s="53" t="s">
+      <c r="D82" s="5"/>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A83" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="C81" s="39" t="s">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A82" s="39" t="s">
+      <c r="D83" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B82" s="53" t="s">
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A84" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="C82" s="39" t="s">
+      <c r="B84" s="31"/>
+      <c r="C84" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A83" s="40" t="s">
+      <c r="D84" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A85" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="B83" s="42"/>
-      <c r="C83" s="42" t="s">
+      <c r="B85" s="3"/>
+      <c r="C85" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D85" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A86" s="32" t="s">
+        <v>552</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="C86" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A87" s="39" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A84" s="32" t="s">
+      <c r="B87" s="40"/>
+      <c r="C87" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32" t="s">
+      <c r="D87" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D84" s="2" t="s">
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A88" s="32" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A85" s="32" t="s">
+      <c r="B88" s="19"/>
+      <c r="C88" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="32" t="s">
+      <c r="D88" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D85" s="2" t="s">
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A89" s="31" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A86" s="33" t="s">
-        <v>576</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="C86" s="33" t="s">
-        <v>578</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A87" s="40" t="s">
+      <c r="B89" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B87" s="41"/>
-      <c r="C87" s="42" t="s">
+      <c r="C89" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D89" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A88" s="33" t="s">
+    <row r="90" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A90" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="33" t="s">
+      <c r="B90" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="C90" s="31" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A89" s="32" t="s">
+      <c r="D90" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B89" s="3" t="s">
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A91" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C89" s="32" t="s">
+      <c r="B91" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="C91" s="31" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A90" s="32" t="s">
+      <c r="D91" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B90" s="51" t="s">
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A92" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="B92" s="31"/>
+      <c r="C92" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D92" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A93" s="31" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A91" s="32" t="s">
+      <c r="B93" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C93" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C91" s="32" t="s">
+      <c r="D93" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D91" s="2" t="s">
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A94" s="31" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A92" s="32" t="s">
+      <c r="B94" s="50" t="s">
+        <v>506</v>
+      </c>
+      <c r="C94" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="B92" s="32"/>
-      <c r="C92" s="32" t="s">
+      <c r="D94" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A95" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="B95" s="3" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A93" s="32" t="s">
+      <c r="C95" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C93" s="32" t="s">
+    </row>
+    <row r="96" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A96" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="B96" s="19"/>
+      <c r="C96" s="32" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A94" s="32" t="s">
+      <c r="D96" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="B94" s="51" t="s">
-        <v>530</v>
-      </c>
-      <c r="C94" s="32" t="s">
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A97" s="53" t="s">
+        <v>556</v>
+      </c>
+      <c r="B97" s="28"/>
+      <c r="C97" s="53" t="s">
+        <v>557</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A98" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A95" s="32" t="s">
+      <c r="B98" s="19"/>
+      <c r="C98" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="D98" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="C95" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A96" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="B96" s="19"/>
-      <c r="C96" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A97" s="54" t="s">
-        <v>580</v>
-      </c>
-      <c r="B97" s="29"/>
-      <c r="C97" s="54" t="s">
-        <v>581</v>
-      </c>
-      <c r="D97" s="30" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A98" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="B98" s="19"/>
-      <c r="C98" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1">
       <c r="A99" s="16" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
       <c r="A100" s="16" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A101" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B101" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A102" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C102" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D102" s="2" t="s">
         <v>290</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A101" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="B101" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="C101" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A102" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C102" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1">
       <c r="A103" s="16" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A104" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A105" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A106" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B106" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A107" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C107" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D107" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A104" s="32" t="s">
-        <v>498</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C104" s="32" t="s">
-        <v>498</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A105" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="B105" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="C105" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A106" s="32" t="s">
+    <row r="108" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A108" s="53" t="s">
+        <v>559</v>
+      </c>
+      <c r="B108" s="30"/>
+      <c r="C108" s="53" t="s">
+        <v>560</v>
+      </c>
+      <c r="D108" s="29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A109" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="B106" s="23" t="s">
+      <c r="B109" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="C106" s="32" t="s">
+      <c r="C109" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A107" s="33" t="s">
+    <row r="110" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A110" s="31" t="s">
         <v>305</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C107" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A108" s="54" t="s">
-        <v>583</v>
-      </c>
-      <c r="B108" s="31"/>
-      <c r="C108" s="54" t="s">
-        <v>584</v>
-      </c>
-      <c r="D108" s="30" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A109" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B109" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="C109" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A110" s="32" t="s">
-        <v>313</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>315</v>
+        <v>612</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A111" s="32" t="s">
-        <v>316</v>
+      <c r="A111" s="31" t="s">
+        <v>307</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>318</v>
+        <v>613</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A112" s="32" t="s">
-        <v>319</v>
+      <c r="A112" s="31" t="s">
+        <v>309</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C112" s="32" t="s">
-        <v>321</v>
+        <v>310</v>
+      </c>
+      <c r="C112" s="31" t="s">
+        <v>311</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1">
       <c r="A113" s="16" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="D113" s="35" t="s">
-        <v>326</v>
+        <v>315</v>
+      </c>
+      <c r="D113" s="34" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
       <c r="A114" s="16" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A115" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="B115" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A116" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A117" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="B117" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="C117" s="31" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A115" s="32" t="s">
+      <c r="D117" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="B115" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="C115" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A116" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C116" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A117" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="B117" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="C117" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
       <c r="A118" s="16" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="16" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
       <c r="A119" s="16" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="16" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1">
       <c r="A120" s="16" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="16" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="32" t="s">
-        <v>351</v>
+      <c r="A121" s="31" t="s">
+        <v>340</v>
       </c>
       <c r="B121" s="2"/>
-      <c r="C121" s="32" t="s">
-        <v>352</v>
+      <c r="C121" s="31" t="s">
+        <v>341</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>353</v>
+        <v>614</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="40" t="s">
-        <v>354</v>
-      </c>
-      <c r="B122" s="41"/>
-      <c r="C122" s="42" t="s">
-        <v>355</v>
+      <c r="A122" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="B122" s="40"/>
+      <c r="C122" s="41" t="s">
+        <v>343</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1">
       <c r="A123" s="16" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="16" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1">
       <c r="A124" s="16" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A125" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B125" s="2"/>
+      <c r="C125" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A126" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C126" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A127" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="B127" s="27"/>
+      <c r="C127" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A128" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B128" s="36" t="s">
         <v>361</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="C128" s="31" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="32" t="s">
+      <c r="D128" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B125" s="2"/>
-      <c r="C125" s="32" t="s">
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A129" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="B129" s="27"/>
+      <c r="C129" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="D129" s="14" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="32" t="s">
+    <row r="130" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A130" s="32" t="s">
         <v>366</v>
       </c>
-      <c r="B126" s="37" t="s">
+      <c r="B130" s="27"/>
+      <c r="C130" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C126" s="32" t="s">
+      <c r="D130" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="D126" s="2" t="s">
+    </row>
+    <row r="131" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A131" s="31" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="33" t="s">
+      <c r="B131" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="B127" s="28"/>
-      <c r="C127" s="33" t="s">
+      <c r="C131" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="D127" s="14" t="s">
+      <c r="D131" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A128" s="32" t="s">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A132" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="B128" s="37" t="s">
+      <c r="B132" s="36"/>
+      <c r="C132" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="C128" s="32" t="s">
+      <c r="D132" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D128" s="2" t="s">
+    </row>
+    <row r="133" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A133" s="31" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="33" t="s">
+      <c r="B133" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="B129" s="28"/>
-      <c r="C129" s="33" t="s">
-        <v>527</v>
-      </c>
-      <c r="D129" s="14" t="s">
+      <c r="C133" s="31" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="33" t="s">
+      <c r="D133" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="B130" s="28"/>
-      <c r="C130" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="D130" s="14" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="B131" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="C131" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B132" s="37"/>
-      <c r="C132" s="32" t="s">
-        <v>387</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="B133" s="37" t="s">
-        <v>390</v>
-      </c>
-      <c r="C133" s="32" t="s">
-        <v>391</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1">
       <c r="A134" s="16" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A135" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="C135" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A136" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="C136" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A137" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="B137" s="3"/>
+      <c r="C137" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A138" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B138" s="36" t="s">
         <v>394</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="C138" s="31" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="32" t="s">
+      <c r="D138" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B135" s="37" t="s">
+    </row>
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="46" t="s">
         <v>397</v>
       </c>
-      <c r="C135" s="32" t="s">
+      <c r="B139" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="C139" s="7" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A136" s="32" t="s">
+      <c r="D139" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="B136" s="37" t="s">
+    </row>
+    <row r="140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A140" s="39" t="s">
         <v>401</v>
       </c>
-      <c r="C136" s="32" t="s">
+      <c r="B140" s="40"/>
+      <c r="C140" s="41" t="s">
         <v>402</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D140" s="11" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="32" t="s">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A141" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="B137" s="3"/>
-      <c r="C137" s="32" t="s">
+      <c r="B141" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="C141" s="32" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="32" t="s">
+      <c r="D141" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="B138" s="37" t="s">
+    </row>
+    <row r="142" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A142" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="C138" s="32" t="s">
+      <c r="B142" s="3"/>
+      <c r="C142" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A143" s="54" t="s">
         <v>409</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="B143" s="55" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="47" t="s">
+      <c r="C143" s="56" t="s">
         <v>411</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="D143" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="C139" s="7" t="s">
+    </row>
+    <row r="144" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A144" s="54" t="s">
         <v>413</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="B144" s="40"/>
+      <c r="C144" s="56" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="40" t="s">
+      <c r="D144" s="21" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A145" s="57" t="s">
         <v>415</v>
       </c>
-      <c r="B140" s="41"/>
-      <c r="C140" s="42" t="s">
+      <c r="B145" s="4"/>
+      <c r="C145" s="57" t="s">
         <v>416</v>
       </c>
-      <c r="D140" s="11" t="s">
+      <c r="D145" s="9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A146" s="31" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="33" t="s">
+      <c r="B146" s="2"/>
+      <c r="C146" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="D146" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A147" s="31" t="s">
         <v>419</v>
       </c>
-      <c r="C141" s="33" t="s">
+      <c r="B147" s="2"/>
+      <c r="C147" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D147" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A148" s="31" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A142" s="32" t="s">
+      <c r="B148" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B142" s="3"/>
-      <c r="C142" s="32" t="s">
-        <v>526</v>
-      </c>
-      <c r="D142" s="2" t="s">
+      <c r="C148" s="31" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="55" t="s">
+      <c r="D148" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B143" s="56" t="s">
+    </row>
+    <row r="149" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A149" s="58" t="s">
         <v>425</v>
       </c>
-      <c r="C143" s="57" t="s">
+      <c r="B149" s="59" t="s">
         <v>426</v>
       </c>
-      <c r="D143" s="21" t="s">
+      <c r="C149" s="58" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A144" s="55" t="s">
+      <c r="D149" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B144" s="41"/>
-      <c r="C144" s="57" t="s">
+    </row>
+    <row r="150" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A150" s="31" t="s">
         <v>429</v>
       </c>
-      <c r="D144" s="21" t="s">
+      <c r="B150" s="2"/>
+      <c r="C150" s="31" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="58" t="s">
-        <v>431</v>
-      </c>
-      <c r="B145" s="4"/>
-      <c r="C145" s="58" t="s">
-        <v>432</v>
-      </c>
-      <c r="D145" s="9" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="32" t="s">
-        <v>434</v>
-      </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="32" t="s">
-        <v>435</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="32" t="s">
-        <v>438</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="32" t="s">
-        <v>440</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C148" s="32" t="s">
-        <v>442</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="59" t="s">
-        <v>444</v>
-      </c>
-      <c r="B149" s="60" t="s">
-        <v>445</v>
-      </c>
-      <c r="C149" s="59" t="s">
-        <v>446</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A150" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="B150" s="2"/>
-      <c r="C150" s="32" t="s">
-        <v>449</v>
-      </c>
       <c r="D150" s="2" t="s">
-        <v>450</v>
+        <v>601</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="16" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D151" s="35" t="s">
-        <v>454</v>
+        <v>433</v>
+      </c>
+      <c r="D151" s="34" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
       <c r="A152" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A153" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B153" s="36" t="s">
+        <v>440</v>
+      </c>
+      <c r="C153" s="31" t="s">
+        <v>595</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A154" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C154" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C155" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A157" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A158" s="32" t="s">
+        <v>562</v>
+      </c>
+      <c r="B158" s="14"/>
+      <c r="C158" s="32" t="s">
+        <v>563</v>
+      </c>
+      <c r="D158" s="14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A159" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="B159" s="14"/>
+      <c r="C159" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="D159" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A160" s="32" t="s">
+        <v>568</v>
+      </c>
+      <c r="B160" s="14"/>
+      <c r="C160" s="32" t="s">
+        <v>569</v>
+      </c>
+      <c r="D160" s="14" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="32" t="s">
+        <v>571</v>
+      </c>
+      <c r="B161" s="14"/>
+      <c r="C161" s="32" t="s">
+        <v>572</v>
+      </c>
+      <c r="D161" s="14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A162" s="32" t="s">
+        <v>574</v>
+      </c>
+      <c r="B162" s="14"/>
+      <c r="C162" s="32" t="s">
+        <v>575</v>
+      </c>
+      <c r="D162" s="14" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A163" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="B163" s="14"/>
+      <c r="C163" s="32" t="s">
+        <v>578</v>
+      </c>
+      <c r="D163" s="14" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A164" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="B164" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="C164" s="32" t="s">
         <v>455</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="D164" s="14" t="s">
         <v>456</v>
-      </c>
-      <c r="C152" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="32" t="s">
-        <v>459</v>
-      </c>
-      <c r="B153" s="37" t="s">
-        <v>460</v>
-      </c>
-      <c r="C153" s="32" t="s">
-        <v>461</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="32" t="s">
-        <v>463</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C154" s="32" t="s">
-        <v>465</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="32" t="s">
-        <v>467</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C155" s="32" t="s">
-        <v>469</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="32" t="s">
-        <v>471</v>
-      </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="32" t="s">
-        <v>472</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="32" t="s">
-        <v>475</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="33" t="s">
-        <v>586</v>
-      </c>
-      <c r="B158" s="14"/>
-      <c r="C158" s="33" t="s">
-        <v>587</v>
-      </c>
-      <c r="D158" s="14" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="33" t="s">
-        <v>589</v>
-      </c>
-      <c r="B159" s="14"/>
-      <c r="C159" s="33" t="s">
-        <v>590</v>
-      </c>
-      <c r="D159" s="14" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="33" t="s">
-        <v>592</v>
-      </c>
-      <c r="B160" s="14"/>
-      <c r="C160" s="33" t="s">
-        <v>593</v>
-      </c>
-      <c r="D160" s="14" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="33" t="s">
-        <v>595</v>
-      </c>
-      <c r="B161" s="14"/>
-      <c r="C161" s="33" t="s">
-        <v>596</v>
-      </c>
-      <c r="D161" s="14" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="33" t="s">
-        <v>598</v>
-      </c>
-      <c r="B162" s="14"/>
-      <c r="C162" s="33" t="s">
-        <v>599</v>
-      </c>
-      <c r="D162" s="14" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="33" t="s">
-        <v>601</v>
-      </c>
-      <c r="B163" s="14"/>
-      <c r="C163" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="D163" s="14" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="B164" s="51" t="s">
-        <v>532</v>
-      </c>
-      <c r="C164" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="D164" s="14" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1">
       <c r="A165" s="16" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A166" s="32" t="s">
-        <v>484</v>
+      <c r="A166" s="31" t="s">
+        <v>461</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C166" s="32" t="s">
-        <v>486</v>
+        <v>462</v>
+      </c>
+      <c r="C166" s="31" t="s">
+        <v>463</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
       <c r="A167" s="7" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="32" t="s">
-        <v>492</v>
+      <c r="A168" s="31" t="s">
+        <v>469</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="C168" s="32" t="s">
-        <v>494</v>
+        <v>470</v>
+      </c>
+      <c r="C168" s="31" t="s">
+        <v>471</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
       <c r="A169" s="16" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="B169" s="20"/>
       <c r="C169" s="16" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="32" t="s">
-        <v>505</v>
+      <c r="A170" s="31" t="s">
+        <v>481</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C170" s="32" t="s">
-        <v>507</v>
+        <v>482</v>
+      </c>
+      <c r="C170" s="31" t="s">
+        <v>483</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="33" t="s">
-        <v>604</v>
+      <c r="A171" s="32" t="s">
+        <v>580</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>605</v>
-      </c>
-      <c r="C171" s="33" t="s">
-        <v>606</v>
+        <v>581</v>
+      </c>
+      <c r="C171" s="32" t="s">
+        <v>582</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="33" t="s">
-        <v>607</v>
+      <c r="A172" s="32" t="s">
+        <v>583</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="C172" s="33" t="s">
-        <v>609</v>
+        <v>584</v>
+      </c>
+      <c r="C172" s="32" t="s">
+        <v>585</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1">
       <c r="A173" s="16" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="16" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1">
       <c r="A174" s="2" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
       <c r="A175" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="B175" s="37" t="s">
-        <v>523</v>
+        <v>498</v>
+      </c>
+      <c r="B175" s="36" t="s">
+        <v>499</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="61" t="s">
-        <v>512</v>
+      <c r="A176" s="60" t="s">
+        <v>488</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C176" s="33" t="s">
-        <v>514</v>
+        <v>489</v>
+      </c>
+      <c r="C176" s="32" t="s">
+        <v>490</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1"/>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5605977B-6CFC-0F47-8773-DEF1829849D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002279D8-74E7-B043-9708-A80FF473E2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="694">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -1486,13 +1486,7 @@
     <t>&lt;orgName key="VerfassungstreuerGrossgrundbesitz" ref="https://d-nb.info/gnd/2120665-X"&gt;</t>
   </si>
   <si>
-    <t>Reichsrat/Abgeordnetenhauses/Ausgleichsausschuss</t>
-  </si>
-  <si>
     <t>Ausgleichsausschuss</t>
-  </si>
-  <si>
-    <t>Reichsrat/Abgeordnetenhauses/Budgetausschuss</t>
   </si>
   <si>
     <t>https://d-nb.info/gnd/1701874-2</t>
@@ -2100,9 +2094,6 @@
     <t>RestaurantCardinal</t>
   </si>
   <si>
-    <t>&lt;orgName key="Cardinal"&gt;</t>
-  </si>
-  <si>
     <t>Restaurant/Königin von England (Angol Királynő Szálló)</t>
   </si>
   <si>
@@ -2477,11 +2468,206 @@
     <t>https://d-nb.info/gnd/1043681051</t>
   </si>
   <si>
-    <t>Elbemühle</t>
-  </si>
-  <si>
-    <r>
-      <t>&lt;orgName key="Elbemühle" ref="</t>
+    <t>Presse/The Fortnightly Review</t>
+  </si>
+  <si>
+    <t>FortnightlyReview</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4253570-0</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="FortnightlyReview" ref="https://d-nb.info/gnd/4253570-0"&gt;</t>
+  </si>
+  <si>
+    <t>Heiligster Regierender Synod</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1234688-3</t>
+  </si>
+  <si>
+    <t>HeiligerSynod</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HeiligerSynod" ref="https://d-nb.info/gnd/1234688-3"&gt;</t>
+  </si>
+  <si>
+    <t>Eisenbahn/Kaiser Ferdinands-Nordbahn</t>
+  </si>
+  <si>
+    <t>Nordbahn</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Nordbahn" ref="https://d-nb.info/gnd/2065980-5"&gt;</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/2065980-5</t>
+  </si>
+  <si>
+    <t>Eisenbahn/Kaschau-Oderberger Bahn</t>
+  </si>
+  <si>
+    <t>OesterreichischeDonaudampfschifffahrtsgesellschaft</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1056582-6</t>
+  </si>
+  <si>
+    <t>Erste Donaudampfschifffahrtsgesellschaft</t>
+  </si>
+  <si>
+    <t>Presse/Prager Abendblatt</t>
+  </si>
+  <si>
+    <t>PragerAbendblatt</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="PragerAbendblatt"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/Prager Zeitung</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="PragerZeitung"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/Pražské hospodářské noviny</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="PrazkeNoviny"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/Sarajevoer Tagblatt</t>
+  </si>
+  <si>
+    <t>&lt;orgName key"SarajevoerTagblatt"&gt;</t>
+  </si>
+  <si>
+    <t>Eisenbahn/k.k. Staatsbahn</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/16158248-5</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Staatsbahn" ref="https://d-nb.info/gnd/16158248-5"&gt;</t>
+  </si>
+  <si>
+    <t>Süddeutsche Donau-Schiffahrts-Gesellschaft </t>
+  </si>
+  <si>
+    <t>SueddeutscheDonauSchifffahrt</t>
+  </si>
+  <si>
+    <t>&lt;orgName ="SueddeutscheDonauSchifffahrt"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/TheTimes</t>
+  </si>
+  <si>
+    <t>TheTimes</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="TheTimes" key="https://d-nb.info/gnd/4185524-3"&gt;</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4185524-3</t>
+  </si>
+  <si>
+    <t>Union générale</t>
+  </si>
+  <si>
+    <t>UnionGenerale</t>
+  </si>
+  <si>
+    <t>&lt;orgName ="UnionGenerale"&gt;</t>
+  </si>
+  <si>
+    <t>Deutscher Volksrat für Böhmen</t>
+  </si>
+  <si>
+    <t>Volksrat</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1701546-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;orgName key="Volksrat" ref="https://d-nb.info/gnd/1701546-7"&gt;  </t>
+  </si>
+  <si>
+    <t>Deutscher Volksrat für Böhmen/Zweiteilungsausschuss</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/5246403-9</t>
+  </si>
+  <si>
+    <t>VolksratZweiteilungsausschuss</t>
+  </si>
+  <si>
+    <t>Reichsrat/Abgeordnetenhaus/Ausgleichsausschuss</t>
+  </si>
+  <si>
+    <t>Reichsrat/Abgeordnetenhaus/Budgetausschuss</t>
+  </si>
+  <si>
+    <t>Reichsrat/Abgeordnetenhaus/Ausschuss des Äußern</t>
+  </si>
+  <si>
+    <t>AusschussdesAeussern</t>
+  </si>
+  <si>
+    <t>&lt;orgName ="AusschussdesAeussern"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="RestaurantCardinal"&gt;</t>
+  </si>
+  <si>
+    <t>Kirche/KatholischeKirche</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/2009545-4</t>
+  </si>
+  <si>
+    <t>KatholischeKirche</t>
+  </si>
+  <si>
+    <t>Landesausschuss für Böhmen</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/5172011-5</t>
+  </si>
+  <si>
+    <t>PragerZeitung</t>
+  </si>
+  <si>
+    <t>PrazskeNoviny</t>
+  </si>
+  <si>
+    <t>SarajevoerTagblatt</t>
+  </si>
+  <si>
+    <t>Staatsbahn</t>
+  </si>
+  <si>
+    <t>Presse/Union: Zeitschrift für Versicherungswesen und Volkswirthschaft</t>
+  </si>
+  <si>
+    <t>Union</t>
+  </si>
+  <si>
+    <t>&lt;orgname key="Union"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="VolksratZweiteilungsausschuss" ref="https://d-nb.info/gnd/41998-9"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="OesterreichischeDonaudampfschifffahrtsgesellschaft" ref="https://d-nb.info/gnd/1056582-6"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgname="Elbemuehle" ref="https://d-nb.info/gnd/1043681051"&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;orgName key="Freimaurer" ref="</t>
     </r>
     <r>
       <rPr>
@@ -2491,7 +2677,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>https://d-nb.info/gnd/1043681051</t>
+      <t>https://d-nb.info/gnd/4123227-6</t>
     </r>
     <r>
       <rPr>
@@ -2505,151 +2691,7 @@
     </r>
   </si>
   <si>
-    <t>Presse/The Fortnightly Review</t>
-  </si>
-  <si>
-    <t>FortnightlyReview</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/4253570-0</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="FortnightlyReview" ref="https://d-nb.info/gnd/4253570-0"&gt;</t>
-  </si>
-  <si>
-    <t>Heiligster Regierender Synod</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/1234688-3</t>
-  </si>
-  <si>
-    <t>HeiligerSynod</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="HeiligerSynod" ref="https://d-nb.info/gnd/1234688-3"&gt;</t>
-  </si>
-  <si>
-    <t>Eisenbahn/Kaiser Ferdinands-Nordbahn</t>
-  </si>
-  <si>
-    <t>Nordbahn</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Nordbahn" ref="https://d-nb.info/gnd/2065980-5"&gt;</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/2065980-5</t>
-  </si>
-  <si>
-    <t>Eisenbahn/Kaschau-Oderberger Bahn</t>
-  </si>
-  <si>
-    <t>OesterreichischeDonaudampfschifffahrtsgesellschaft</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/1056582-6</t>
-  </si>
-  <si>
-    <t>Erste Donaudampfschifffahrtsgesellschaft</t>
-  </si>
-  <si>
-    <t>Presse/Prager Abendblatt</t>
-  </si>
-  <si>
-    <t>PragerAbendblatt</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="PragerAbendblatt"&gt;</t>
-  </si>
-  <si>
-    <t>Presse/Prager Zeitung</t>
-  </si>
-  <si>
-    <t>Prager Zeitung</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="PragerZeitung"&gt;</t>
-  </si>
-  <si>
-    <t>Presse/Pražské hospodářské noviny</t>
-  </si>
-  <si>
-    <t>PrazkeNoviny</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="PrazkeNoviny"&gt;</t>
-  </si>
-  <si>
-    <t>Presse/Sarajevoer Tagblatt</t>
-  </si>
-  <si>
-    <t>Sarajevoer</t>
-  </si>
-  <si>
-    <t>&lt;orgName key"SarajevoerTagblatt"&gt;</t>
-  </si>
-  <si>
-    <t>Eisenbahn/k.k. Staatsbahn</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/16158248-5</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="Staatsbahn" ref="https://d-nb.info/gnd/16158248-5"&gt;</t>
-  </si>
-  <si>
-    <t>Süddeutsche Donau-Schiffahrts-Gesellschaft </t>
-  </si>
-  <si>
-    <t>SueddeutscheDonauSchifffahrt</t>
-  </si>
-  <si>
-    <t>&lt;orgName ="SueddeutscheDonauSchifffahrt"&gt;</t>
-  </si>
-  <si>
-    <t>Presse/TheTimes</t>
-  </si>
-  <si>
-    <t>TheTimes</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="TheTimes" key="https://d-nb.info/gnd/4185524-3"&gt;</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/4185524-3</t>
-  </si>
-  <si>
-    <t>Union générale</t>
-  </si>
-  <si>
-    <t>UnionGenerale</t>
-  </si>
-  <si>
-    <t>&lt;orgName ="UnionGenerale"&gt;</t>
-  </si>
-  <si>
-    <t>Deutscher Volksrat für Böhmen</t>
-  </si>
-  <si>
-    <t>Volksrat</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/1701546-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;orgName key="Volksrat" ref="https://d-nb.info/gnd/1701546-7"&gt;  </t>
-  </si>
-  <si>
-    <t>Deutscher Volksrat für Böhmen/Zweiteilungsausschuss</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/5246403-9</t>
-  </si>
-  <si>
-    <t>VolksratZweiteilungsausschuss</t>
-  </si>
-  <si>
-    <t>&lt;orgName key="VolksratZweiteilungsausschuss" ref="https://d-nb.info/gnd/5246403-9"&gt;</t>
+    <t>Elbemuehle</t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3124,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D191" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D194" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3291,7 +3333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1124"/>
+  <dimension ref="A1:Z1127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3331,90 +3373,90 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="32" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="32" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>510</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>512</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="32" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="32" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>516</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>518</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="32" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="32" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="32" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="32" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="32" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="32" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3433,16 +3475,16 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>620</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>622</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3461,44 +3503,44 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>294</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>640</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3517,21 +3559,21 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="32" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="16" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>57</v>
@@ -3545,30 +3587,30 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="16" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="32" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B20" s="62" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>629</v>
+        <v>693</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>294</v>
+        <v>691</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3582,7 +3624,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>630</v>
+        <v>692</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3601,30 +3643,30 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>616</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>617</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="16" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3697,7 +3739,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="32" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B30" s="27" t="s">
         <v>43</v>
@@ -3753,2171 +3795,2206 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="32" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="32" t="s">
+        <v>677</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>679</v>
+      </c>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="C36" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="31" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C37" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A37" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="31" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="9" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A39" s="31" t="s">
+        <v>680</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B40" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C40" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D40" s="9" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>73</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>603</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="37"/>
+        <v>76</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C42" s="31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>86</v>
+      <c r="D44" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B47" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="38" t="s">
+    <row r="48" spans="1:4">
+      <c r="A48" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B48" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="38" t="s">
+      <c r="C48" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D48" s="10" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="B48" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:26">
       <c r="A49" s="39" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C49" s="41" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:26">
       <c r="A50" s="39" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="A51" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:26">
       <c r="A52" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B52" s="40" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>111</v>
       </c>
       <c r="C52" s="41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:26">
       <c r="A53" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26">
+      <c r="A54" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="40" t="s">
+      <c r="B54" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C53" s="41" t="s">
+      <c r="C54" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
-      <c r="A54" s="16" t="s">
+    <row r="55" spans="1:26">
+      <c r="A55" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26">
-      <c r="A55" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:26">
       <c r="A56" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26">
+      <c r="A57" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="31" t="s">
+      <c r="C57" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>584</v>
-      </c>
-      <c r="B57" s="3" t="s">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A58" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C57" s="31" t="s">
-        <v>491</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26">
-      <c r="A58" s="31" t="s">
+    </row>
+    <row r="59" spans="1:26">
+      <c r="A59" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C59" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:26">
-      <c r="A59" s="42" t="s">
+    <row r="60" spans="1:26">
+      <c r="A60" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="43" t="s">
+      <c r="B60" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="42" t="s">
+      <c r="C60" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D60" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
-      <c r="Q59" s="13"/>
-      <c r="R59" s="13"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="13"/>
-      <c r="U59" s="13"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="13"/>
-      <c r="X59" s="13"/>
-      <c r="Y59" s="13"/>
-      <c r="Z59" s="13"/>
-    </row>
-    <row r="60" spans="1:26" ht="16">
-      <c r="A60" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
+      <c r="Q60" s="13"/>
+      <c r="R60" s="13"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="13"/>
+      <c r="U60" s="13"/>
+      <c r="V60" s="13"/>
+      <c r="W60" s="13"/>
+      <c r="X60" s="13"/>
+      <c r="Y60" s="13"/>
+      <c r="Z60" s="13"/>
     </row>
     <row r="61" spans="1:26" ht="16">
       <c r="A61" s="38" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="16">
       <c r="A62" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" ht="16">
+      <c r="A63" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D63" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:26">
-      <c r="A63" s="16" t="s">
+    <row r="64" spans="1:26">
+      <c r="A64" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B63" s="61" t="s">
+      <c r="B64" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C64" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D64" s="34" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B64" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="31" t="s">
+      <c r="B66" s="3"/>
+      <c r="C66" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>166</v>
+      <c r="D66" s="2" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="C68" s="32" t="s">
         <v>532</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>534</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="31" t="s">
+      <c r="D68" s="6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="36" t="s">
+      <c r="B69" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C69" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="44" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="33" t="s">
+      <c r="B70" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C70" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D70" s="45" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="46" t="s">
+    <row r="71" spans="1:4">
+      <c r="A71" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B71" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C71" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D71" s="7" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="32" t="s">
-        <v>535</v>
-      </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="32" t="s">
-        <v>536</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="32" t="s">
-        <v>538</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>539</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="B72" s="19"/>
       <c r="C72" s="32" t="s">
-        <v>540</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>541</v>
+        <v>534</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="B73" s="19"/>
+        <v>536</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>537</v>
+      </c>
       <c r="C73" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>543</v>
+        <v>538</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C74" s="31" t="s">
+      <c r="C75" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="D74" s="36" t="s">
+      <c r="D75" s="36" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="16" t="s">
+    <row r="76" spans="1:4">
+      <c r="A76" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B75" s="47" t="s">
+      <c r="B76" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C76" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D75" s="34" t="s">
+      <c r="D76" s="34" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="30">
-      <c r="A76" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="B76" s="48" t="s">
-        <v>545</v>
-      </c>
-      <c r="C76" s="32" t="s">
-        <v>546</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="30">
       <c r="A77" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="B77" s="48" t="s">
+        <v>543</v>
+      </c>
+      <c r="C77" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="30">
+      <c r="A78" s="32" t="s">
+        <v>545</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="C78" s="32" t="s">
         <v>547</v>
       </c>
-      <c r="B77" s="17" t="s">
-        <v>548</v>
-      </c>
-      <c r="C77" s="32" t="s">
-        <v>549</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B78" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>188</v>
+      <c r="D78" s="6" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B79" s="16"/>
+        <v>186</v>
+      </c>
+      <c r="B79" s="47" t="s">
+        <v>187</v>
+      </c>
       <c r="C79" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26">
+      <c r="A81" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B80" s="49" t="s">
+      <c r="B81" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C81" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="D80" s="34" t="s">
+      <c r="D81" s="34" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="81" spans="1:26">
-      <c r="A81" s="31" t="s">
+    <row r="82" spans="1:26">
+      <c r="A82" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B81" s="50" t="s">
-        <v>502</v>
-      </c>
-      <c r="C81" s="31" t="s">
+      <c r="B82" s="50" t="s">
+        <v>500</v>
+      </c>
+      <c r="C82" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" ht="16">
-      <c r="A82" s="31" t="s">
+      <c r="D82" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" ht="16">
+      <c r="A83" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B82" s="37" t="s">
+      <c r="B83" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="C82" s="31" t="s">
+      <c r="C83" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="83" spans="1:26">
-      <c r="A83" s="31" t="s">
+    <row r="84" spans="1:26">
+      <c r="A84" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B84" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C84" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:26">
-      <c r="A84" s="16" t="s">
+    <row r="85" spans="1:26">
+      <c r="A85" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16" t="s">
+      <c r="B85" s="16"/>
+      <c r="C85" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="85" spans="1:26">
-      <c r="A85" s="31" t="s">
+    <row r="86" spans="1:26">
+      <c r="A86" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31" t="s">
+      <c r="B86" s="31"/>
+      <c r="C86" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26">
-      <c r="A86" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>213</v>
+      <c r="D86" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:26">
       <c r="A87" s="16" t="s">
-        <v>624</v>
+        <v>211</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16" t="s">
-        <v>625</v>
+        <v>212</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>626</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:26">
-      <c r="A88" s="32" t="s">
+      <c r="A88" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26">
+      <c r="A89" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C88" s="32" t="s">
+      <c r="C89" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D89" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A89" s="51" t="s">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A90" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B90" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C89" s="51" t="s">
+      <c r="C90" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D90" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
-      <c r="M89" s="13"/>
-      <c r="N89" s="13"/>
-      <c r="O89" s="13"/>
-      <c r="P89" s="13"/>
-      <c r="Q89" s="13"/>
-      <c r="R89" s="13"/>
-      <c r="S89" s="13"/>
-      <c r="T89" s="13"/>
-      <c r="U89" s="13"/>
-      <c r="V89" s="13"/>
-      <c r="W89" s="13"/>
-      <c r="X89" s="13"/>
-      <c r="Y89" s="13"/>
-      <c r="Z89" s="13"/>
-    </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A90" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="B90" s="38"/>
-      <c r="C90" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>224</v>
-      </c>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="13"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="13"/>
+      <c r="U90" s="13"/>
+      <c r="V90" s="13"/>
+      <c r="W90" s="13"/>
+      <c r="X90" s="13"/>
+      <c r="Y90" s="13"/>
+      <c r="Z90" s="13"/>
     </row>
     <row r="91" spans="1:26" ht="15.75" customHeight="1">
       <c r="A91" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="B91" s="52" t="s">
-        <v>226</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B91" s="38"/>
       <c r="C91" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="D91" s="5"/>
+        <v>223</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="92" spans="1:26" ht="15.75" customHeight="1">
       <c r="A92" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="B92" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D92" s="5"/>
+    </row>
+    <row r="93" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A93" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="B92" s="52" t="s">
+      <c r="B93" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="C92" s="38" t="s">
+      <c r="C93" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A93" s="39" t="s">
+      <c r="D93" s="5"/>
+    </row>
+    <row r="94" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A94" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="B93" s="41"/>
-      <c r="C93" s="41" t="s">
+      <c r="B94" s="41"/>
+      <c r="C94" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D94" s="5" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A94" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B94" s="31"/>
-      <c r="C94" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="95" spans="1:26" ht="15.75" customHeight="1">
       <c r="A95" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="B95" s="31"/>
+      <c r="C95" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A96" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="31" t="s">
+      <c r="B96" s="3"/>
+      <c r="C96" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A96" s="32" t="s">
+    <row r="97" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A97" s="32" t="s">
+        <v>548</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="C97" s="32" t="s">
         <v>550</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="D97" s="14" t="s">
         <v>551</v>
       </c>
-      <c r="C96" s="32" t="s">
-        <v>552</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A97" s="39" t="s">
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A98" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="B97" s="40"/>
-      <c r="C97" s="41" t="s">
+      <c r="B98" s="40"/>
+      <c r="C98" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D98" s="11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A98" s="32" t="s">
+    <row r="99" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A99" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="B98" s="19"/>
-      <c r="C98" s="32" t="s">
+      <c r="B99" s="19"/>
+      <c r="C99" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="D99" s="14" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A99" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C99" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
       <c r="A100" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="B100" s="50" t="s">
-        <v>249</v>
+        <v>244</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1">
       <c r="A101" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
+      </c>
+      <c r="B101" s="50" t="s">
+        <v>249</v>
       </c>
       <c r="C101" s="31" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1">
       <c r="A102" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="B102" s="31"/>
+        <v>252</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>253</v>
+      </c>
       <c r="C102" s="31" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>609</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1">
       <c r="A103" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>259</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="B103" s="31"/>
       <c r="C103" s="31" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>261</v>
+        <v>606</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1">
       <c r="A104" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="B104" s="50" t="s">
-        <v>504</v>
+        <v>258</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="C104" s="31" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>505</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1">
       <c r="A105" s="31" t="s">
-        <v>647</v>
-      </c>
-      <c r="B105" s="50"/>
+        <v>262</v>
+      </c>
+      <c r="B105" s="50" t="s">
+        <v>502</v>
+      </c>
       <c r="C105" s="31" t="s">
-        <v>648</v>
+        <v>263</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>649</v>
+        <v>503</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1">
       <c r="A106" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>265</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="B106" s="50"/>
       <c r="C106" s="31" t="s">
-        <v>266</v>
+        <v>643</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>267</v>
+        <v>644</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1">
       <c r="A107" s="31" t="s">
-        <v>650</v>
-      </c>
-      <c r="B107" s="3"/>
+        <v>264</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="C107" s="31" t="s">
-        <v>651</v>
+        <v>266</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>652</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1">
       <c r="A108" s="31" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="31" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A109" s="32" t="s">
+      <c r="A109" s="31" t="s">
+        <v>647</v>
+      </c>
+      <c r="B109" s="3"/>
+      <c r="C109" s="31" t="s">
+        <v>683</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A110" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="B109" s="19"/>
-      <c r="C109" s="32" t="s">
+      <c r="B110" s="19"/>
+      <c r="C110" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D110" s="14" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A110" s="53" t="s">
+    <row r="111" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A111" s="53" t="s">
+        <v>552</v>
+      </c>
+      <c r="B111" s="28"/>
+      <c r="C111" s="53" t="s">
+        <v>553</v>
+      </c>
+      <c r="D111" s="29" t="s">
         <v>554</v>
-      </c>
-      <c r="B110" s="28"/>
-      <c r="C110" s="53" t="s">
-        <v>555</v>
-      </c>
-      <c r="D110" s="29" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A111" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="B111" s="19"/>
-      <c r="C111" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1">
       <c r="A112" s="32" t="s">
-        <v>656</v>
+        <v>271</v>
       </c>
       <c r="B112" s="19"/>
       <c r="C112" s="32" t="s">
-        <v>657</v>
+        <v>272</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>658</v>
+        <v>273</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A113" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>277</v>
+      <c r="A113" s="32" t="s">
+        <v>649</v>
+      </c>
+      <c r="B113" s="19"/>
+      <c r="C113" s="32" t="s">
+        <v>684</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
       <c r="A114" s="16" t="s">
-        <v>631</v>
+        <v>274</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>633</v>
+        <v>275</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>632</v>
+        <v>276</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>634</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
       <c r="A115" s="16" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>668</v>
+        <v>628</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>666</v>
+        <v>627</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>667</v>
+        <v>629</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
       <c r="A116" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A117" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A118" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="16" t="s">
+      <c r="B118" s="4"/>
+      <c r="C118" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D118" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A117" s="31" t="s">
+    <row r="119" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A119" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="B117" s="36" t="s">
+      <c r="B119" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="C117" s="31" t="s">
+      <c r="C119" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D119" s="2" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A118" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C118" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A119" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="B119" s="20"/>
-      <c r="C119" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1">
       <c r="A120" s="31" t="s">
-        <v>472</v>
+        <v>285</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>473</v>
+        <v>286</v>
       </c>
       <c r="C120" s="31" t="s">
-        <v>472</v>
+        <v>287</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>474</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="B121" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>182</v>
+      <c r="A121" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B121" s="20"/>
+      <c r="C121" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1">
       <c r="A122" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A123" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B123" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A124" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="B122" s="22" t="s">
+      <c r="B124" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="C122" s="31" t="s">
+      <c r="C124" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="32" t="s">
+    <row r="125" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A125" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B125" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C123" s="32" t="s">
+      <c r="C125" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D125" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A124" s="53" t="s">
+    <row r="126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A126" s="53" t="s">
+        <v>555</v>
+      </c>
+      <c r="B126" s="30"/>
+      <c r="C126" s="53" t="s">
+        <v>556</v>
+      </c>
+      <c r="D126" s="29" t="s">
         <v>557</v>
-      </c>
-      <c r="B124" s="30"/>
-      <c r="C124" s="53" t="s">
-        <v>558</v>
-      </c>
-      <c r="D124" s="29" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="B125" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1">
       <c r="A127" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="C127" s="31" t="s">
+        <v>301</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>611</v>
+        <v>302</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1">
       <c r="A128" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A129" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A130" s="31" t="s">
         <v>307</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B130" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C128" s="31" t="s">
+      <c r="C130" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="16" t="s">
+    <row r="131" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A131" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B131" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C129" s="16" t="s">
+      <c r="C131" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="D129" s="34" t="s">
+      <c r="D131" s="34" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A132" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="16" t="s">
+      <c r="B132" s="4"/>
+      <c r="C132" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="B131" s="36" t="s">
-        <v>318</v>
-      </c>
-      <c r="C131" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C132" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>324</v>
+      <c r="D132" s="5" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1">
       <c r="A133" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>318</v>
+      </c>
+      <c r="C133" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A134" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C134" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A135" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="B133" s="36" t="s">
+      <c r="B135" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="C133" s="31" t="s">
+      <c r="C135" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D135" s="2" t="s">
         <v>328</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A134" s="16" t="s">
-        <v>329</v>
-      </c>
-      <c r="B134" s="5"/>
-      <c r="C134" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="30" customHeight="1">
-      <c r="A135" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1">
       <c r="A136" s="16" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="30" customHeight="1">
+      <c r="A137" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="B137" s="5"/>
+      <c r="C137" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A138" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B138" s="5"/>
+      <c r="C138" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D138" s="5" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="31" t="s">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="31" t="s">
+      <c r="B139" s="2"/>
+      <c r="C139" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="39" t="s">
+      <c r="D139" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A140" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="B138" s="40"/>
-      <c r="C138" s="41" t="s">
+      <c r="B140" s="40"/>
+      <c r="C140" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="D138" s="11" t="s">
+      <c r="D140" s="11" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="16" t="s">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A141" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B139" s="5"/>
-      <c r="C139" s="16" t="s">
+      <c r="B141" s="5"/>
+      <c r="C141" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="D139" s="5" t="s">
+      <c r="D141" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="16" t="s">
+    <row r="142" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A142" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="16" t="s">
+      <c r="B142" s="5"/>
+      <c r="C142" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D142" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="31" t="s">
+    <row r="143" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A143" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="31" t="s">
+      <c r="B143" s="2"/>
+      <c r="C143" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A142" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="B142" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="C142" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B143" s="27"/>
-      <c r="C143" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="D143" s="14" t="s">
-        <v>357</v>
+      <c r="D143" s="2" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
       <c r="A144" s="31" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C144" s="31" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1">
       <c r="A145" s="32" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B145" s="27"/>
       <c r="C145" s="32" t="s">
-        <v>501</v>
+        <v>356</v>
       </c>
       <c r="D145" s="14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A146" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B146" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="C146" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A147" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="B147" s="27"/>
+      <c r="C147" s="32" t="s">
+        <v>499</v>
+      </c>
+      <c r="D147" s="14" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="32" t="s">
+    <row r="148" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A148" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="B146" s="27"/>
-      <c r="C146" s="32" t="s">
+      <c r="B148" s="27"/>
+      <c r="C148" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="D146" s="14" t="s">
+      <c r="D148" s="14" t="s">
         <v>366</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="B147" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="C147" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
       <c r="A149" s="31" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B149" s="36" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C149" s="31" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A150" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="B150" s="4"/>
-      <c r="C150" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>380</v>
+      <c r="A150" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="B150" s="36"/>
+      <c r="C150" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="31" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B151" s="36" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C151" s="31" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="B152" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="C152" s="31" t="s">
-        <v>387</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>388</v>
+      <c r="A152" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1">
       <c r="A153" s="31" t="s">
-        <v>389</v>
-      </c>
-      <c r="B153" s="3"/>
+        <v>381</v>
+      </c>
+      <c r="B153" s="36" t="s">
+        <v>382</v>
+      </c>
       <c r="C153" s="31" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>594</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1">
       <c r="A154" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B154" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="C154" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="31" t="s">
+        <v>671</v>
+      </c>
+      <c r="B155" s="3"/>
+      <c r="C155" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="31" t="s">
+        <v>673</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="31" t="s">
+        <v>674</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A157" s="31" t="s">
+        <v>672</v>
+      </c>
+      <c r="B157" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="C157" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="B154" s="36" t="s">
+      <c r="D157" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C154" s="31" t="s">
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A158" s="46" t="s">
         <v>393</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="B158" s="4" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="46" t="s">
+      <c r="C158" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="D158" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="C155" s="7" t="s">
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A159" s="39" t="s">
         <v>397</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="B159" s="40"/>
+      <c r="C159" s="41" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="39" t="s">
+      <c r="D159" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="B156" s="40"/>
-      <c r="C156" s="41" t="s">
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A160" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="D156" s="11" t="s">
+      <c r="B160" s="6" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="32" t="s">
+      <c r="C160" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="D160" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="C157" s="32" t="s">
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="B161" s="3"/>
+      <c r="C161" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A162" s="54" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="31" t="s">
+      <c r="B162" s="55" t="s">
         <v>406</v>
       </c>
-      <c r="B158" s="3"/>
-      <c r="C158" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="54" t="s">
+      <c r="C162" s="56" t="s">
         <v>407</v>
       </c>
-      <c r="B159" s="55" t="s">
+      <c r="D162" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="C159" s="56" t="s">
+    </row>
+    <row r="163" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A163" s="54" t="s">
         <v>409</v>
       </c>
-      <c r="D159" s="21" t="s">
+      <c r="B163" s="40"/>
+      <c r="C163" s="56" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="54" t="s">
+      <c r="D163" s="21" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A164" s="57" t="s">
         <v>411</v>
       </c>
-      <c r="B160" s="40"/>
-      <c r="C160" s="56" t="s">
+      <c r="B164" s="4"/>
+      <c r="C164" s="57" t="s">
         <v>412</v>
       </c>
-      <c r="D160" s="21" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="57" t="s">
+      <c r="D164" s="9" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A165" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="B161" s="4"/>
-      <c r="C161" s="57" t="s">
+      <c r="B165" s="2"/>
+      <c r="C165" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="D161" s="9" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="31" t="s">
-        <v>415</v>
-      </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="B163" s="2"/>
-      <c r="C163" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C164" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="58" t="s">
-        <v>423</v>
-      </c>
-      <c r="B165" s="59" t="s">
-        <v>424</v>
-      </c>
-      <c r="C165" s="58" t="s">
-        <v>425</v>
-      </c>
       <c r="D165" s="2" t="s">
-        <v>426</v>
+        <v>594</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
       <c r="A166" s="31" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B166" s="2"/>
       <c r="C166" s="31" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C167" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="D167" s="34" t="s">
-        <v>432</v>
+      <c r="A167" s="31" t="s">
+        <v>417</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C167" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C168" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>436</v>
+      <c r="A168" s="58" t="s">
+        <v>421</v>
+      </c>
+      <c r="B168" s="59" t="s">
+        <v>422</v>
+      </c>
+      <c r="C168" s="58" t="s">
+        <v>423</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
       <c r="A169" s="31" t="s">
-        <v>437</v>
-      </c>
-      <c r="B169" s="36" t="s">
-        <v>438</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="B169" s="2"/>
       <c r="C169" s="31" t="s">
-        <v>593</v>
+        <v>426</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>439</v>
+        <v>596</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C170" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>443</v>
+      <c r="A170" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="D170" s="34" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C171" s="31" t="s">
-        <v>446</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>447</v>
+      <c r="A171" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
       <c r="A172" s="31" t="s">
-        <v>448</v>
-      </c>
-      <c r="B172" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="B172" s="36" t="s">
+        <v>436</v>
+      </c>
       <c r="C172" s="31" t="s">
-        <v>449</v>
+        <v>590</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>600</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1">
       <c r="A173" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="B173" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>439</v>
+      </c>
       <c r="C173" s="31" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>601</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="32" t="s">
-        <v>560</v>
-      </c>
-      <c r="B174" s="14"/>
-      <c r="C174" s="32" t="s">
-        <v>561</v>
-      </c>
-      <c r="D174" s="14" t="s">
-        <v>562</v>
+      <c r="A174" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C174" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="32" t="s">
-        <v>563</v>
-      </c>
-      <c r="B175" s="14"/>
-      <c r="C175" s="32" t="s">
-        <v>564</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>565</v>
+      <c r="A175" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B175" s="2"/>
+      <c r="C175" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="32" t="s">
-        <v>566</v>
-      </c>
-      <c r="B176" s="14"/>
-      <c r="C176" s="32" t="s">
-        <v>567</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>568</v>
+      <c r="A176" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B176" s="2"/>
+      <c r="C176" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1">
       <c r="A177" s="32" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="B177" s="14"/>
       <c r="C177" s="32" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1">
       <c r="A178" s="32" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="B178" s="14"/>
       <c r="C178" s="32" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1">
       <c r="A179" s="32" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B179" s="14"/>
       <c r="C179" s="32" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
       <c r="A180" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="B180" s="14"/>
+      <c r="C180" s="32" t="s">
+        <v>567</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A181" s="32" t="s">
+        <v>569</v>
+      </c>
+      <c r="B181" s="14"/>
+      <c r="C181" s="32" t="s">
+        <v>570</v>
+      </c>
+      <c r="D181" s="14" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A182" s="32" t="s">
+        <v>572</v>
+      </c>
+      <c r="B182" s="14"/>
+      <c r="C182" s="32" t="s">
+        <v>573</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A183" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="B183" s="50" t="s">
+        <v>504</v>
+      </c>
+      <c r="C183" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="D183" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="B180" s="50" t="s">
-        <v>506</v>
-      </c>
-      <c r="C180" s="32" t="s">
+    </row>
+    <row r="184" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A184" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="D180" s="14" t="s">
+      <c r="B184" s="4" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="16" t="s">
+      <c r="C184" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="D184" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="C181" s="16" t="s">
+    </row>
+    <row r="185" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A185" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="B185" s="4"/>
+      <c r="C185" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A186" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="D181" s="5" t="s">
+      <c r="B186" s="3" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A182" s="16" t="s">
+      <c r="C186" s="31" t="s">
+        <v>459</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A187" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A188" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C188" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A189" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="B189" s="20"/>
+      <c r="C189" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A190" s="31" t="s">
+        <v>477</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C190" s="31" t="s">
+        <v>479</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A191" s="32" t="s">
+        <v>575</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="C191" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A192" s="32" t="s">
+        <v>578</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C192" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A193" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="B193" s="20"/>
+      <c r="C193" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A194" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="B194" s="20"/>
+      <c r="C194" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="B182" s="4"/>
-      <c r="C182" s="16" t="s">
+      <c r="D194" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A183" s="31" t="s">
-        <v>459</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C183" s="31" t="s">
-        <v>461</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A184" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="D184" s="7" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A185" s="31" t="s">
-        <v>467</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C185" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="B186" s="20"/>
-      <c r="C186" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="31" t="s">
-        <v>479</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="C187" s="31" t="s">
-        <v>481</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="32" t="s">
-        <v>578</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="C188" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="32" t="s">
-        <v>581</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="C189" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="B190" s="20"/>
-      <c r="C190" s="16" t="s">
+    </row>
+    <row r="195" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A195" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A196" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B196" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A197" s="60" t="s">
         <v>484</v>
       </c>
-      <c r="D190" s="5" t="s">
+      <c r="B197" s="6" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="B191" s="20"/>
-      <c r="C191" s="16" t="s">
-        <v>670</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B193" s="36" t="s">
-        <v>497</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A194" s="60" t="s">
+      <c r="C197" s="32" t="s">
         <v>486</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="D197" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="C194" s="32" t="s">
-        <v>488</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="196" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1"/>
+    </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="199" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="200" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6845,6 +6922,9 @@
     <row r="1122" ht="15.75" customHeight="1"/>
     <row r="1123" ht="15.75" customHeight="1"/>
     <row r="1124" ht="15.75" customHeight="1"/>
+    <row r="1125" ht="15.75" customHeight="1"/>
+    <row r="1126" ht="15.75" customHeight="1"/>
+    <row r="1127" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6853,7 +6933,7 @@
     <hyperlink ref="B16" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B21" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D21" r:id="rId7" display="&lt;orgName key=&quot;Freimaurer&quot; ref=&quot;https://d-nb.info/gnd/4123227-6&quot;&gt;" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D21" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="B22" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="B25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="B26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
@@ -6866,129 +6946,130 @@
     <hyperlink ref="B33" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="B18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="D18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B35" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D35" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B36" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B39" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B40" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B41" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B44" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B47" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D47" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B48" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B52" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B53" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B54" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B55" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B56" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B58" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B59" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B60" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B61" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B62" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B63" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D63" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B64" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B66" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B68" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B69" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D69" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B70" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D74" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B75" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D75" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B80" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B82" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B83" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B88" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D88" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B89" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B91" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B92" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B99" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B100" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B101" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B103" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B113" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B117" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B118" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B121" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B122" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B123" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D123" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B125" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B128" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B129" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D129" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B131" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B132" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B133" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B142" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B144" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B147" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B149" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B151" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B152" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B154" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B155" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B157" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D157" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B159" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B164" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B165" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B167" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D167" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B168" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B169" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B170" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B171" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B181" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B183" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B184" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B185" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B120" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B187" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B57" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B192" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B193" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B81" r:id="rId113" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B104" r:id="rId114" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B180" r:id="rId115" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B36" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D36" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B37" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B40" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B41" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B42" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B45" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B46" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B47" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B48" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D48" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B49" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B51" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B53" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B54" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B55" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B56" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B57" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B59" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B60" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B61" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B62" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B63" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B64" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D64" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B65" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B67" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B69" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B70" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D70" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B71" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B75" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D75" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B76" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D76" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B79" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B81" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D81" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B83" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B84" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B89" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D89" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B90" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B92" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B93" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B100" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B101" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B102" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B104" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B114" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B119" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B120" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B123" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B124" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B125" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D125" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B127" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B130" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B131" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D131" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B133" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B134" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B135" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B144" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B146" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B149" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B151" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B153" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B154" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B157" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B158" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B160" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D160" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B162" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B167" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B168" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B170" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D170" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B171" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B172" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B173" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B174" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B184" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B186" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B187" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B188" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B122" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B190" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B58" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B195" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B196" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B82" r:id="rId113" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B105" r:id="rId114" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B183" r:id="rId115" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="B4" r:id="rId116" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="D4" r:id="rId117" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B6" r:id="rId118" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D6" r:id="rId119" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
     <hyperlink ref="B34" r:id="rId120" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
     <hyperlink ref="D34" r:id="rId121" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B67" r:id="rId122" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D67" r:id="rId123" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B72" r:id="rId124" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D72" r:id="rId125" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B76" r:id="rId126" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D76" r:id="rId127" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B77" r:id="rId128" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D77" r:id="rId129" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B96" r:id="rId130" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B188" r:id="rId131" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D188" r:id="rId132" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B189" r:id="rId133" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D189" r:id="rId134" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B194" r:id="rId135" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D194" r:id="rId136" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B68" r:id="rId122" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D68" r:id="rId123" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B73" r:id="rId124" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D73" r:id="rId125" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B77" r:id="rId126" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D77" r:id="rId127" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B78" r:id="rId128" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D78" r:id="rId129" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B97" r:id="rId130" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B191" r:id="rId131" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D191" r:id="rId132" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B192" r:id="rId133" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D192" r:id="rId134" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B197" r:id="rId135" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D197" r:id="rId136" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B20" r:id="rId137" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B15" r:id="rId138" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId138"/>
+    <tablePart r:id="rId139"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002279D8-74E7-B043-9708-A80FF473E2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CA0BA6-5A35-BA4F-906A-A1C517E5DBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="699">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>&lt;orgName key="CottascheVerlagsbuchhandlung" ref="https://d-nb.info/gnd/5056474-2"&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deutsche Universität Prag </t>
   </si>
   <si>
     <t>https://d-nb.info/gnd/2047130-0</t>
@@ -707,33 +704,6 @@
     <t>OberlandesgerichtPrag</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>&lt;orgName key="OberlandesgerichtPrag" ref="</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://d-nb.info/gnd/7553054-5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>"&gt;</t>
-    </r>
-  </si>
-  <si>
     <t>Österreichischer Lloyd</t>
   </si>
   <si>
@@ -1785,18 +1755,9 @@
     <t>Landesausschuss</t>
   </si>
   <si>
-    <t>&lt;orgName ="Landesausschuss"&gt;</t>
-  </si>
-  <si>
     <t>Staatsgerichtshof</t>
   </si>
   <si>
-    <t>&lt;orgName ="Staatsgerichtshof"&gt;</t>
-  </si>
-  <si>
-    <t>Tschechische Karls-Universität</t>
-  </si>
-  <si>
     <t>https://d-nb.info/gnd/67240-3</t>
   </si>
   <si>
@@ -1810,9 +1771,6 @@
   </si>
   <si>
     <t>UngaroCroata</t>
-  </si>
-  <si>
-    <t>&lt;orgName ="UngaroCroata"&gt;</t>
   </si>
   <si>
     <t>Wiener Musikverein</t>
@@ -2459,9 +2417,6 @@
     <t>DeutschnationaleKorrespondenz</t>
   </si>
   <si>
-    <t>&lt;orgName ="DeutschnationaleKorrespondenz"&gt;</t>
-  </si>
-  <si>
     <t>Elbemühle (Papierfabrik)</t>
   </si>
   <si>
@@ -2558,9 +2513,6 @@
     <t>SueddeutscheDonauSchifffahrt</t>
   </si>
   <si>
-    <t>&lt;orgName ="SueddeutscheDonauSchifffahrt"&gt;</t>
-  </si>
-  <si>
     <t>Presse/TheTimes</t>
   </si>
   <si>
@@ -2579,9 +2531,6 @@
     <t>UnionGenerale</t>
   </si>
   <si>
-    <t>&lt;orgName ="UnionGenerale"&gt;</t>
-  </si>
-  <si>
     <t>Deutscher Volksrat für Böhmen</t>
   </si>
   <si>
@@ -2615,9 +2564,6 @@
     <t>AusschussdesAeussern</t>
   </si>
   <si>
-    <t>&lt;orgName ="AusschussdesAeussern"&gt;</t>
-  </si>
-  <si>
     <t>&lt;orgName key="RestaurantCardinal"&gt;</t>
   </si>
   <si>
@@ -2654,16 +2600,10 @@
     <t>Union</t>
   </si>
   <si>
-    <t>&lt;orgname key="Union"&gt;</t>
-  </si>
-  <si>
     <t>&lt;orgName key="VolksratZweiteilungsausschuss" ref="https://d-nb.info/gnd/41998-9"&gt;</t>
   </si>
   <si>
     <t>&lt;orgName key="OesterreichischeDonaudampfschifffahrtsgesellschaft" ref="https://d-nb.info/gnd/1056582-6"&gt;</t>
-  </si>
-  <si>
-    <t>&lt;orgname="Elbemuehle" ref="https://d-nb.info/gnd/1043681051"&gt;</t>
   </si>
   <si>
     <r>
@@ -2693,12 +2633,86 @@
   <si>
     <t>Elbemuehle</t>
   </si>
+  <si>
+    <t>UniversitaetWien</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/2024703-5</t>
+  </si>
+  <si>
+    <t>Universitäten/Universität Wien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitäten/Deutsche Universität Prag </t>
+  </si>
+  <si>
+    <t>Universitäten/Tschechische Karls-Universität</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="UniversitaetWien" ref="https://d-nb.info/gnd/2024703-5"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="UngaroCroata"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="UnionGenerale"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Staatsgerichtshof"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="SueddeutscheDonauSchifffahrt"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="AusschussdesAeussern"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Union"&gt;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t>&lt;orgName key="OberlandesgerichtPrag" ref="</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t>https://d-nb.info/gnd/7553054-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t>"&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;orgName key="Elbemuehle" ref="https://d-nb.info/gnd/1043681051"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="KatholischeKirche"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Landesausschuss"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="DeutschnationaleKorrespondenz"&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2837,6 +2851,11 @@
       <color rgb="FF0000FF"/>
       <name val="Lato"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2925,7 +2944,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2961,7 +2980,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2993,7 +3011,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3029,6 +3046,7 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3124,7 +3142,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D194" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D193" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3333,7 +3351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1127"/>
+  <dimension ref="A1:Z1128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3358,13 +3376,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -3372,91 +3390,91 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="31" t="s">
         <v>505</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="32" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="31" t="s">
         <v>506</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="32" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="31" t="s">
         <v>508</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>510</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="32" t="s">
+      <c r="D6" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="31" t="s">
         <v>511</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="32" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="31" t="s">
         <v>512</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D7" s="14" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="32" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="31" t="s">
         <v>514</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="31" t="s">
         <v>515</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="D8" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="32" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="32" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="31" t="s">
         <v>518</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>519</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="32" t="s">
-        <v>520</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="32" t="s">
-        <v>521</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="32" t="s">
-        <v>523</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="32" t="s">
-        <v>524</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3475,1622 +3493,1622 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="16" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="16" t="s">
-        <v>12</v>
+        <v>655</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>657</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>14</v>
+        <v>656</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>15</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>668</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>669</v>
+        <v>634</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>633</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>670</v>
+        <v>632</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>641</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>640</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>639</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>690</v>
+      <c r="A15" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>16</v>
+      <c r="A16" s="31" t="s">
+        <v>627</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>630</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>628</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>18</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="32" t="s">
-        <v>634</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>637</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>635</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>636</v>
+      <c r="A17" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="16" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>57</v>
+        <v>645</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>59</v>
+        <v>675</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>653</v>
+      <c r="A19" s="31" t="s">
+        <v>617</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>618</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>681</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="32" t="s">
-        <v>624</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>625</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>693</v>
+      <c r="A20" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>18</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="33" t="s">
+      <c r="A21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>692</v>
+      <c r="B21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>22</v>
+        <v>607</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>609</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>23</v>
+        <v>608</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>24</v>
+        <v>610</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="16" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>632</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>633</v>
+      <c r="A24" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="A25" s="16" t="s">
         <v>28</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B26" s="4"/>
       <c r="C26" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C27" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="A29" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="B29" s="26" t="s">
         <v>42</v>
       </c>
+      <c r="C29" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="32" t="s">
-        <v>526</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="A30" s="30" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="31" t="s">
+      <c r="B30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="D30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="2" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="16">
+      <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="16">
-      <c r="A32" s="7" t="s">
+      <c r="B31" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="C31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="B32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>53</v>
       </c>
+      <c r="D32" s="5" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>56</v>
+      <c r="A33" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="32" t="s">
-        <v>529</v>
+      <c r="A34" s="31" t="s">
+        <v>667</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>528</v>
+        <v>668</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>669</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>584</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="32" t="s">
-        <v>677</v>
+      <c r="A35" s="31" t="s">
+        <v>59</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>679</v>
-      </c>
-      <c r="D35" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="6" t="s">
+      <c r="A36" s="30" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="31" t="s">
+      <c r="B36" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C36" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="D36" s="2" t="s">
         <v>66</v>
       </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A37" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="30" t="s">
+        <v>467</v>
+      </c>
       <c r="D37" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A38" s="30" t="s">
+        <v>670</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="9" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>680</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>473</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>474</v>
+      <c r="B39" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="9" t="s">
-        <v>68</v>
+      <c r="A40" s="30" t="s">
+        <v>71</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>74</v>
+      <c r="A41" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>75</v>
+        <v>594</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="31" t="s">
+      <c r="A42" s="30" t="s">
         <v>78</v>
       </c>
+      <c r="B42" s="36"/>
+      <c r="C42" s="30" t="s">
+        <v>79</v>
+      </c>
       <c r="D42" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="31" t="s">
+      <c r="A43" s="30" t="s">
         <v>80</v>
       </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30" t="s">
+        <v>81</v>
+      </c>
       <c r="D43" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31" t="s">
+      <c r="A44" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>602</v>
+      <c r="B44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="7" t="s">
+      <c r="A47" s="37" t="s">
         <v>94</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" s="10" t="s">
         <v>97</v>
       </c>
+      <c r="B48" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>100</v>
+      <c r="A49" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>103</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>104</v>
+      <c r="A50" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>107</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="B51" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="41" t="s">
-        <v>108</v>
+      <c r="A51" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="40" t="s">
+        <v>111</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>112</v>
+      <c r="A52" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="40" t="s">
+        <v>115</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B53" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>116</v>
+      <c r="A53" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="40" t="s">
+        <v>119</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" s="11" t="s">
+      <c r="A54" s="16" t="s">
         <v>121</v>
       </c>
+      <c r="B54" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="A55" s="30" t="s">
         <v>125</v>
       </c>
+      <c r="B55" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="31" t="s">
-        <v>128</v>
+      <c r="A56" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26">
-      <c r="A57" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A57" s="30" t="s">
+        <v>575</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>132</v>
+        <v>482</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>483</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26">
+      <c r="A58" s="30" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A58" s="31" t="s">
-        <v>581</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>489</v>
+      <c r="B58" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>490</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="A59" s="41" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="60" spans="1:26">
-      <c r="A60" s="42" t="s">
+      <c r="B59" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="B60" s="43" t="s">
+      <c r="C59" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="42" t="s">
+      <c r="D59" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
+      <c r="Q59" s="13"/>
+      <c r="R59" s="13"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="13"/>
+      <c r="U59" s="13"/>
+      <c r="V59" s="13"/>
+      <c r="W59" s="13"/>
+      <c r="X59" s="13"/>
+      <c r="Y59" s="13"/>
+      <c r="Z59" s="13"/>
+    </row>
+    <row r="60" spans="1:26" ht="16">
+      <c r="A60" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
-      <c r="Q60" s="13"/>
-      <c r="R60" s="13"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="13"/>
-      <c r="U60" s="13"/>
-      <c r="V60" s="13"/>
-      <c r="W60" s="13"/>
-      <c r="X60" s="13"/>
-      <c r="Y60" s="13"/>
-      <c r="Z60" s="13"/>
+      <c r="B60" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="61" spans="1:26" ht="16">
-      <c r="A61" s="38" t="s">
-        <v>142</v>
+      <c r="A61" s="37" t="s">
+        <v>145</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="16">
-      <c r="A62" s="38" t="s">
-        <v>146</v>
+      <c r="A62" s="37" t="s">
+        <v>149</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26" ht="16">
-      <c r="A63" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C63" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D63" s="7" t="s">
+    </row>
+    <row r="63" spans="1:26">
+      <c r="A63" s="16" t="s">
         <v>153</v>
       </c>
+      <c r="B63" s="59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="64" spans="1:26">
-      <c r="A64" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B64" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D64" s="34" t="s">
+      <c r="A64" s="30" t="s">
         <v>156</v>
       </c>
+      <c r="B64" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="B65" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="31" t="s">
-        <v>159</v>
+      <c r="A65" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>160</v>
+        <v>597</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B66" s="3"/>
+        <v>162</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="C66" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>603</v>
+        <v>164</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="32" t="s">
-        <v>163</v>
+      <c r="A67" s="31" t="s">
+        <v>524</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="30" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="32" t="s">
-        <v>530</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>532</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>585</v>
+      <c r="B68" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="B69" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="C69" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="A69" s="43" t="s">
         <v>170</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="B70" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="45" t="s">
+      <c r="B70" s="4" t="s">
         <v>174</v>
       </c>
+      <c r="C70" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C71" s="7" t="s">
+      <c r="A71" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="B71" s="19"/>
+      <c r="C71" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="31" t="s">
+        <v>530</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="B74" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="32" t="s">
-        <v>533</v>
-      </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="32" t="s">
-        <v>534</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="32" t="s">
+      <c r="C74" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D74" s="35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" s="33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="30">
+      <c r="A76" s="31" t="s">
         <v>536</v>
       </c>
-      <c r="B73" s="26" t="s">
+      <c r="B76" s="46" t="s">
         <v>537</v>
       </c>
-      <c r="C73" s="32" t="s">
+      <c r="C76" s="31" t="s">
         <v>538</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D76" s="6" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="30">
+      <c r="A77" s="31" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="32" t="s">
+      <c r="B77" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="32" t="s">
-        <v>540</v>
-      </c>
-      <c r="D74" s="25" t="s">
+      <c r="C77" s="31" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D75" s="36" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B76" s="47" t="s">
+      <c r="D77" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="C76" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D76" s="34" t="s">
+      <c r="B78" s="45" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="30">
-      <c r="A77" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="B77" s="48" t="s">
-        <v>543</v>
-      </c>
-      <c r="C77" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="30">
-      <c r="A78" s="32" t="s">
-        <v>545</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="C78" s="32" t="s">
-        <v>547</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>587</v>
+      <c r="C78" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B79" s="47" t="s">
         <v>187</v>
       </c>
+      <c r="B79" s="16"/>
       <c r="C79" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B80" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="B80" s="47" t="s">
+        <v>191</v>
+      </c>
       <c r="C80" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="B81" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="C81" s="16" t="s">
+      <c r="A81" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="D81" s="34" t="s">
+      <c r="B81" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="C81" s="30" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="82" spans="1:26">
-      <c r="A82" s="31" t="s">
+      <c r="D81" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" ht="16">
+      <c r="A82" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="B82" s="50" t="s">
-        <v>500</v>
-      </c>
-      <c r="C82" s="31" t="s">
+      <c r="B82" s="36" t="s">
         <v>197</v>
       </c>
+      <c r="C82" s="30" t="s">
+        <v>198</v>
+      </c>
       <c r="D82" s="2" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="83" spans="1:26" ht="16">
-      <c r="A83" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="B83" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="C83" s="31" t="s">
+    </row>
+    <row r="83" spans="1:26">
+      <c r="A83" s="30" t="s">
         <v>200</v>
       </c>
+      <c r="B83" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>202</v>
+      </c>
       <c r="D83" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:26">
-      <c r="A84" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C84" s="31" t="s">
+      <c r="A84" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="B84" s="16"/>
+      <c r="C84" s="16" t="s">
         <v>205</v>
       </c>
+      <c r="D84" s="5" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="85" spans="1:26">
-      <c r="A85" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16" t="s">
+      <c r="A85" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="B85" s="30"/>
+      <c r="C85" s="30" t="s">
         <v>208</v>
       </c>
+      <c r="D85" s="2" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="86" spans="1:26">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B86" s="31"/>
-      <c r="C86" s="31" t="s">
+      <c r="B86" s="16"/>
+      <c r="C86" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>604</v>
+      <c r="D86" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:26">
       <c r="A87" s="16" t="s">
-        <v>211</v>
+        <v>615</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26">
+      <c r="A88" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="B88" s="17" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="88" spans="1:26">
-      <c r="A88" s="16" t="s">
-        <v>621</v>
-      </c>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16" t="s">
-        <v>622</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26">
-      <c r="A89" s="32" t="s">
+      <c r="C88" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="D88" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C89" s="32" t="s">
+    </row>
+    <row r="89" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A89" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="B89" s="4" t="s">
         <v>217</v>
       </c>
+      <c r="C89" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13"/>
+      <c r="P89" s="13"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="13"/>
+      <c r="S89" s="13"/>
+      <c r="T89" s="13"/>
+      <c r="U89" s="13"/>
+      <c r="V89" s="13"/>
+      <c r="W89" s="13"/>
+      <c r="X89" s="13"/>
+      <c r="Y89" s="13"/>
+      <c r="Z89" s="13"/>
     </row>
     <row r="90" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A90" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C90" s="51" t="s">
+      <c r="A90" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="B90" s="37"/>
+      <c r="C90" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-      <c r="K90" s="13"/>
-      <c r="L90" s="13"/>
-      <c r="M90" s="13"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="13"/>
-      <c r="P90" s="13"/>
-      <c r="Q90" s="13"/>
-      <c r="R90" s="13"/>
-      <c r="S90" s="13"/>
-      <c r="T90" s="13"/>
-      <c r="U90" s="13"/>
-      <c r="V90" s="13"/>
-      <c r="W90" s="13"/>
-      <c r="X90" s="13"/>
-      <c r="Y90" s="13"/>
-      <c r="Z90" s="13"/>
+      <c r="D90" s="5" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="91" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A91" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="B91" s="38"/>
-      <c r="C91" s="38" t="s">
+      <c r="A91" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="B91" s="50" t="s">
         <v>224</v>
       </c>
+      <c r="C91" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D91" s="5"/>
     </row>
     <row r="92" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A92" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="B92" s="52" t="s">
+      <c r="A92" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="C92" s="38" t="s">
+      <c r="B92" s="50" t="s">
         <v>227</v>
+      </c>
+      <c r="C92" s="37" t="s">
+        <v>228</v>
       </c>
       <c r="D92" s="5"/>
     </row>
     <row r="93" spans="1:26" ht="15.75" customHeight="1">
       <c r="A93" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="B93" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="C93" s="38" t="s">
+      <c r="B93" s="40"/>
+      <c r="C93" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D93" s="5"/>
+      <c r="D93" s="5" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="94" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A94" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="B94" s="41"/>
-      <c r="C94" s="41" t="s">
+      <c r="A94" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="B94" s="30"/>
+      <c r="C94" s="30" t="s">
         <v>233</v>
       </c>
+      <c r="D94" s="2" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="95" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B95" s="31"/>
-      <c r="C95" s="31" t="s">
+      <c r="B95" s="3"/>
+      <c r="C95" s="30" t="s">
         <v>235</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>605</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1">
       <c r="A96" s="31" t="s">
+        <v>542</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A97" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="31" t="s">
+      <c r="B97" s="39"/>
+      <c r="C97" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D97" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A98" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" s="19"/>
+      <c r="C98" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A99" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A97" s="32" t="s">
-        <v>548</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="C97" s="32" t="s">
-        <v>550</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A98" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="B98" s="40"/>
-      <c r="C98" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A99" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="B99" s="19"/>
-      <c r="C99" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>243</v>
+      <c r="C99" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A100" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C100" s="31" t="s">
+      <c r="A100" s="30" t="s">
         <v>246</v>
       </c>
+      <c r="B100" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="D100" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A101" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="B101" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="C101" s="31" t="s">
+      <c r="A101" s="30" t="s">
         <v>250</v>
       </c>
+      <c r="B101" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>252</v>
+      </c>
       <c r="D101" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A102" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C102" s="31" t="s">
+      <c r="A102" s="30" t="s">
         <v>254</v>
       </c>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30" t="s">
+        <v>255</v>
+      </c>
       <c r="D102" s="2" t="s">
-        <v>255</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A103" s="31" t="s">
+      <c r="A103" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="B103" s="31"/>
-      <c r="C103" s="31" t="s">
+      <c r="B103" s="3" t="s">
         <v>257</v>
       </c>
+      <c r="C103" s="30" t="s">
+        <v>258</v>
+      </c>
       <c r="D103" s="2" t="s">
-        <v>606</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A104" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C104" s="31" t="s">
+      <c r="A104" s="30" t="s">
         <v>260</v>
       </c>
+      <c r="B104" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="C104" s="30" t="s">
+        <v>261</v>
+      </c>
       <c r="D104" s="2" t="s">
-        <v>261</v>
+        <v>497</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A105" s="31" t="s">
+      <c r="A105" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="B105" s="48"/>
+      <c r="C105" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A106" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="B105" s="50" t="s">
-        <v>502</v>
-      </c>
-      <c r="C105" s="31" t="s">
+      <c r="B106" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A106" s="31" t="s">
-        <v>642</v>
-      </c>
-      <c r="B106" s="50"/>
-      <c r="C106" s="31" t="s">
-        <v>643</v>
+      <c r="C106" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>644</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A107" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C107" s="31" t="s">
-        <v>266</v>
+      <c r="A107" s="30" t="s">
+        <v>638</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="30" t="s">
+        <v>672</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>267</v>
+        <v>639</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A108" s="31" t="s">
-        <v>645</v>
+      <c r="A108" s="30" t="s">
+        <v>640</v>
       </c>
       <c r="B108" s="3"/>
-      <c r="C108" s="31" t="s">
-        <v>682</v>
+      <c r="C108" s="30" t="s">
+        <v>673</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1">
       <c r="A109" s="31" t="s">
-        <v>647</v>
-      </c>
-      <c r="B109" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="B109" s="19"/>
       <c r="C109" s="31" t="s">
-        <v>683</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>648</v>
+        <v>267</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A110" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="B110" s="19"/>
-      <c r="C110" s="32" t="s">
+      <c r="A110" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="B110" s="27"/>
+      <c r="C110" s="51" t="s">
+        <v>547</v>
+      </c>
+      <c r="D110" s="28" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A111" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="B111" s="19"/>
+      <c r="C111" s="31" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A111" s="53" t="s">
-        <v>552</v>
-      </c>
-      <c r="B111" s="28"/>
-      <c r="C111" s="53" t="s">
-        <v>553</v>
-      </c>
-      <c r="D111" s="29" t="s">
-        <v>554</v>
+      <c r="D111" s="14" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A112" s="32" t="s">
-        <v>271</v>
+      <c r="A112" s="31" t="s">
+        <v>642</v>
       </c>
       <c r="B112" s="19"/>
-      <c r="C112" s="32" t="s">
+      <c r="C112" s="31" t="s">
+        <v>674</v>
+      </c>
+      <c r="D112" s="14" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A113" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="D112" s="14" t="s">
+      <c r="B113" s="4" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A113" s="32" t="s">
-        <v>649</v>
-      </c>
-      <c r="B113" s="19"/>
-      <c r="C113" s="32" t="s">
-        <v>684</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>650</v>
+      <c r="C113" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
       <c r="A114" s="16" t="s">
-        <v>274</v>
+        <v>619</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>275</v>
+        <v>621</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>276</v>
+        <v>620</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>277</v>
+        <v>622</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
       <c r="A115" s="16" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
       <c r="A116" s="16" t="s">
-        <v>657</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>660</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="B116" s="4"/>
       <c r="C116" s="16" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>659</v>
+        <v>693</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1">
       <c r="A117" s="16" t="s">
-        <v>686</v>
+        <v>276</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="16" t="s">
-        <v>687</v>
+        <v>277</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>688</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A118" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="B118" s="4"/>
-      <c r="C118" s="16" t="s">
+      <c r="A118" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="B118" s="35" t="s">
         <v>280</v>
       </c>
+      <c r="C118" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A119" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="B119" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="C119" s="31" t="s">
+      <c r="A119" s="30" t="s">
         <v>283</v>
       </c>
+      <c r="B119" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C119" s="30" t="s">
+        <v>285</v>
+      </c>
       <c r="D119" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A120" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C120" s="31" t="s">
+      <c r="A120" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="B120" s="20"/>
+      <c r="C120" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D120" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C121" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A122" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B122" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C122" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A123" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B121" s="20"/>
-      <c r="C121" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="D121" s="5" t="s">
+      <c r="B123" s="22" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="31" t="s">
-        <v>470</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C122" s="31" t="s">
-        <v>470</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="B123" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>181</v>
+      <c r="C123" s="30" t="s">
+        <v>291</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>182</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1">
       <c r="A124" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="B124" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="C124" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C125" s="32" t="s">
+      <c r="A125" s="51" t="s">
+        <v>549</v>
+      </c>
+      <c r="B125" s="29"/>
+      <c r="C125" s="51" t="s">
+        <v>550</v>
+      </c>
+      <c r="D125" s="28" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A126" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="B126" s="35" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="53" t="s">
-        <v>555</v>
-      </c>
-      <c r="B126" s="30"/>
-      <c r="C126" s="53" t="s">
-        <v>556</v>
-      </c>
-      <c r="D126" s="29" t="s">
-        <v>557</v>
+      <c r="C126" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="B127" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="C127" s="31" t="s">
+      <c r="A127" s="30" t="s">
         <v>301</v>
       </c>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="D127" s="2" t="s">
-        <v>302</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A128" s="31" t="s">
+      <c r="A128" s="30" t="s">
         <v>303</v>
       </c>
       <c r="B128" s="2"/>
@@ -5098,904 +5116,919 @@
         <v>304</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="31" t="s">
+      <c r="A129" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>306</v>
       </c>
+      <c r="C129" s="30" t="s">
+        <v>307</v>
+      </c>
       <c r="D129" s="2" t="s">
-        <v>608</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C130" s="31" t="s">
+      <c r="A130" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="B130" s="4" t="s">
         <v>310</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D130" s="33" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1">
       <c r="A131" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>312</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="B131" s="4"/>
       <c r="C131" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="D131" s="34" t="s">
         <v>314</v>
       </c>
+      <c r="D131" s="5" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="B132" s="4"/>
-      <c r="C132" s="16" t="s">
+      <c r="B132" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>612</v>
+      <c r="C132" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="B133" s="36" t="s">
-        <v>318</v>
-      </c>
-      <c r="C133" s="31" t="s">
+      <c r="A133" s="30" t="s">
         <v>319</v>
       </c>
+      <c r="B133" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C133" s="30" t="s">
+        <v>321</v>
+      </c>
       <c r="D133" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A134" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C134" s="31" t="s">
+      <c r="A134" s="30" t="s">
         <v>323</v>
       </c>
+      <c r="B134" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C134" s="30" t="s">
+        <v>325</v>
+      </c>
       <c r="D134" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B135" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="C135" s="31" t="s">
+      <c r="A135" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="B135" s="5"/>
+      <c r="C135" s="16" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="D135" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="30" customHeight="1">
       <c r="A136" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="30" customHeight="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" customHeight="1">
       <c r="A137" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="B138" s="5"/>
-      <c r="C138" s="16" t="s">
+      <c r="A138" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="B138" s="2"/>
+      <c r="C138" s="30" t="s">
         <v>337</v>
       </c>
+      <c r="D138" s="2" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="31" t="s">
+      <c r="A139" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B139" s="2"/>
-      <c r="C139" s="31" t="s">
+      <c r="B139" s="39"/>
+      <c r="C139" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>609</v>
+      <c r="D139" s="11" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="39" t="s">
-        <v>340</v>
-      </c>
-      <c r="B140" s="40"/>
-      <c r="C140" s="41" t="s">
+      <c r="A140" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="D140" s="11" t="s">
+      <c r="B140" s="5"/>
+      <c r="C140" s="16" t="s">
         <v>342</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1">
       <c r="A141" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A142" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="B142" s="5"/>
-      <c r="C142" s="16" t="s">
+      <c r="A142" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="B142" s="2"/>
+      <c r="C142" s="30" t="s">
         <v>348</v>
       </c>
+      <c r="D142" s="2" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="31" t="s">
+      <c r="A143" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="31" t="s">
+      <c r="B143" s="35" t="s">
         <v>350</v>
       </c>
+      <c r="C143" s="30" t="s">
+        <v>351</v>
+      </c>
       <c r="D143" s="2" t="s">
-        <v>610</v>
+        <v>352</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
       <c r="A144" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="B144" s="36" t="s">
-        <v>352</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="B144" s="26"/>
       <c r="C144" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="D144" s="2" t="s">
         <v>354</v>
       </c>
+      <c r="D144" s="14" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B145" s="27"/>
-      <c r="C145" s="32" t="s">
+      <c r="A145" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="D145" s="14" t="s">
+      <c r="B145" s="35" t="s">
         <v>357</v>
+      </c>
+      <c r="C145" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
       <c r="A146" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="B146" s="36" t="s">
-        <v>359</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="B146" s="26"/>
       <c r="C146" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="D146" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D146" s="14" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="32" t="s">
+      <c r="A147" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="B147" s="27"/>
-      <c r="C147" s="32" t="s">
-        <v>499</v>
+      <c r="B147" s="26"/>
+      <c r="C147" s="31" t="s">
+        <v>363</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="B148" s="27"/>
-      <c r="C148" s="32" t="s">
+      <c r="A148" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="D148" s="14" t="s">
+      <c r="B148" s="35" t="s">
         <v>366</v>
       </c>
+      <c r="C148" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="B149" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="C149" s="31" t="s">
+      <c r="A149" s="30" t="s">
         <v>369</v>
       </c>
+      <c r="B149" s="35"/>
+      <c r="C149" s="30" t="s">
+        <v>370</v>
+      </c>
       <c r="D149" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A150" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="B150" s="36"/>
-      <c r="C150" s="31" t="s">
+      <c r="A150" s="30" t="s">
         <v>372</v>
       </c>
+      <c r="B150" s="35" t="s">
+        <v>373</v>
+      </c>
+      <c r="C150" s="30" t="s">
+        <v>374</v>
+      </c>
       <c r="D150" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A151" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="B151" s="36" t="s">
-        <v>375</v>
-      </c>
-      <c r="C151" s="31" t="s">
+      <c r="A151" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="B151" s="4"/>
+      <c r="C151" s="16" t="s">
         <v>377</v>
       </c>
+      <c r="D151" s="5" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="B152" s="4"/>
-      <c r="C152" s="16" t="s">
+      <c r="A152" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="D152" s="5" t="s">
+      <c r="B152" s="35" t="s">
         <v>380</v>
       </c>
+      <c r="C152" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="B153" s="36" t="s">
-        <v>382</v>
-      </c>
-      <c r="C153" s="31" t="s">
+      <c r="A153" s="30" t="s">
         <v>383</v>
       </c>
+      <c r="B153" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="C153" s="30" t="s">
+        <v>385</v>
+      </c>
       <c r="D153" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="B154" s="36" t="s">
-        <v>386</v>
-      </c>
-      <c r="C154" s="31" t="s">
+      <c r="A154" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B154" s="3"/>
+      <c r="C154" s="30" t="s">
         <v>387</v>
       </c>
       <c r="D154" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="30" t="s">
+        <v>664</v>
+      </c>
+      <c r="B155" s="3"/>
+      <c r="C155" s="30" t="s">
+        <v>665</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="B156" s="35" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="31" t="s">
-        <v>671</v>
-      </c>
-      <c r="B155" s="3"/>
-      <c r="C155" s="31" t="s">
+      <c r="C156" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="31" t="s">
-        <v>673</v>
-      </c>
-      <c r="B156" s="3"/>
-      <c r="C156" s="31" t="s">
-        <v>674</v>
-      </c>
       <c r="D156" s="2" t="s">
-        <v>675</v>
+        <v>390</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="31" t="s">
-        <v>672</v>
-      </c>
-      <c r="B157" s="36" t="s">
-        <v>390</v>
-      </c>
-      <c r="C157" s="31" t="s">
+      <c r="A157" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="B157" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="C157" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="46" t="s">
-        <v>393</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C158" s="7" t="s">
+      <c r="A158" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="B158" s="39"/>
+      <c r="C158" s="40" t="s">
         <v>396</v>
       </c>
+      <c r="D158" s="11" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="39" t="s">
-        <v>397</v>
-      </c>
-      <c r="B159" s="40"/>
-      <c r="C159" s="41" t="s">
+      <c r="A159" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="D159" s="11" t="s">
+      <c r="B159" s="6" t="s">
         <v>399</v>
       </c>
+      <c r="C159" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="32" t="s">
-        <v>400</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="C160" s="32" t="s">
+      <c r="A160" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="B160" s="3"/>
+      <c r="C160" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="52" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="31" t="s">
+      <c r="B161" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="B161" s="3"/>
-      <c r="C161" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>611</v>
+      <c r="C161" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D161" s="21" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="B162" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="C162" s="56" t="s">
+      <c r="A162" s="52" t="s">
         <v>407</v>
       </c>
+      <c r="B162" s="39"/>
+      <c r="C162" s="54" t="s">
+        <v>408</v>
+      </c>
       <c r="D162" s="21" t="s">
-        <v>408</v>
+        <v>586</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="54" t="s">
+      <c r="A163" s="55" t="s">
         <v>409</v>
       </c>
-      <c r="B163" s="40"/>
-      <c r="C163" s="56" t="s">
+      <c r="B163" s="4"/>
+      <c r="C163" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="D163" s="21" t="s">
-        <v>592</v>
+      <c r="D163" s="9" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="57" t="s">
+      <c r="A164" s="30" t="s">
         <v>411</v>
       </c>
-      <c r="B164" s="4"/>
-      <c r="C164" s="57" t="s">
+      <c r="B164" s="2"/>
+      <c r="C164" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="D164" s="9" t="s">
-        <v>593</v>
+      <c r="D164" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="31" t="s">
+      <c r="A165" s="30" t="s">
         <v>413</v>
       </c>
       <c r="B165" s="2"/>
-      <c r="C165" s="31" t="s">
+      <c r="C165" s="30" t="s">
         <v>414</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A166" s="31" t="s">
+      <c r="A166" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="B166" s="2"/>
-      <c r="C166" s="31" t="s">
+      <c r="B166" s="3" t="s">
         <v>416</v>
       </c>
+      <c r="C166" s="30" t="s">
+        <v>417</v>
+      </c>
       <c r="D166" s="2" t="s">
-        <v>595</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C167" s="31" t="s">
+      <c r="A167" s="56" t="s">
         <v>419</v>
       </c>
+      <c r="B167" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C167" s="56" t="s">
+        <v>421</v>
+      </c>
       <c r="D167" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="58" t="s">
-        <v>421</v>
-      </c>
-      <c r="B168" s="59" t="s">
-        <v>422</v>
-      </c>
-      <c r="C168" s="58" t="s">
+      <c r="A168" s="30" t="s">
         <v>423</v>
       </c>
+      <c r="B168" s="2"/>
+      <c r="C168" s="30" t="s">
+        <v>424</v>
+      </c>
       <c r="D168" s="2" t="s">
-        <v>424</v>
+        <v>590</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="31" t="s">
+      <c r="A169" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="B169" s="2"/>
-      <c r="C169" s="31" t="s">
+      <c r="B169" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>596</v>
+      <c r="C169" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D169" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
       <c r="A170" s="16" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="D170" s="34" t="s">
-        <v>430</v>
+        <v>431</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C171" s="16" t="s">
+      <c r="A171" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="D171" s="5" t="s">
+      <c r="B171" s="35" t="s">
         <v>434</v>
       </c>
+      <c r="C171" s="30" t="s">
+        <v>584</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="B172" s="36" t="s">
+      <c r="A172" s="30" t="s">
         <v>436</v>
       </c>
-      <c r="C172" s="31" t="s">
-        <v>590</v>
+      <c r="B172" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C172" s="30" t="s">
+        <v>438</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="31" t="s">
-        <v>438</v>
+      <c r="A173" s="30" t="s">
+        <v>440</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="C173" s="31" t="s">
-        <v>440</v>
+        <v>441</v>
+      </c>
+      <c r="C173" s="30" t="s">
+        <v>442</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C174" s="31" t="s">
+      <c r="A174" s="30" t="s">
         <v>444</v>
       </c>
+      <c r="B174" s="2"/>
+      <c r="C174" s="30" t="s">
+        <v>445</v>
+      </c>
       <c r="D174" s="2" t="s">
-        <v>445</v>
+        <v>591</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="31" t="s">
+      <c r="A175" s="30" t="s">
         <v>446</v>
       </c>
       <c r="B175" s="2"/>
-      <c r="C175" s="31" t="s">
+      <c r="C175" s="30" t="s">
         <v>447</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
       <c r="A176" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="B176" s="14"/>
+      <c r="C176" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="B177" s="14"/>
+      <c r="C177" s="31" t="s">
+        <v>555</v>
+      </c>
+      <c r="D177" s="14" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A178" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="B178" s="14"/>
+      <c r="C178" s="31" t="s">
+        <v>558</v>
+      </c>
+      <c r="D178" s="14" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A179" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="B179" s="14"/>
+      <c r="C179" s="31" t="s">
+        <v>561</v>
+      </c>
+      <c r="D179" s="14" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A180" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="B180" s="14"/>
+      <c r="C180" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A181" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="B181" s="14"/>
+      <c r="C181" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="D181" s="14" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A182" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B176" s="2"/>
-      <c r="C176" s="31" t="s">
+      <c r="B182" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="C182" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="D176" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="32" t="s">
-        <v>558</v>
-      </c>
-      <c r="B177" s="14"/>
-      <c r="C177" s="32" t="s">
-        <v>559</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="32" t="s">
-        <v>560</v>
-      </c>
-      <c r="B178" s="14"/>
-      <c r="C178" s="32" t="s">
-        <v>561</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="32" t="s">
-        <v>563</v>
-      </c>
-      <c r="B179" s="14"/>
-      <c r="C179" s="32" t="s">
-        <v>564</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A180" s="32" t="s">
-        <v>566</v>
-      </c>
-      <c r="B180" s="14"/>
-      <c r="C180" s="32" t="s">
-        <v>567</v>
-      </c>
-      <c r="D180" s="14" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="32" t="s">
-        <v>569</v>
-      </c>
-      <c r="B181" s="14"/>
-      <c r="C181" s="32" t="s">
-        <v>570</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A182" s="32" t="s">
-        <v>572</v>
-      </c>
-      <c r="B182" s="14"/>
-      <c r="C182" s="32" t="s">
-        <v>573</v>
-      </c>
       <c r="D182" s="14" t="s">
-        <v>574</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A183" s="32" t="s">
-        <v>450</v>
-      </c>
-      <c r="B183" s="50" t="s">
-        <v>504</v>
-      </c>
-      <c r="C183" s="32" t="s">
+      <c r="A183" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D183" s="14" t="s">
+      <c r="B183" s="4" t="s">
         <v>452</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
       <c r="A184" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>454</v>
-      </c>
+        <v>647</v>
+      </c>
+      <c r="B184" s="4"/>
       <c r="C184" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A185" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="B185" s="3" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A185" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="B185" s="4"/>
-      <c r="C185" s="16" t="s">
-        <v>655</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>656</v>
+      <c r="C185" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C186" s="31" t="s">
+      <c r="A186" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="B186" s="4" t="s">
         <v>460</v>
       </c>
+      <c r="C186" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="C187" s="7" t="s">
+      <c r="A187" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="D187" s="7" t="s">
+      <c r="B187" s="3" t="s">
         <v>464</v>
       </c>
+      <c r="C187" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C188" s="31" t="s">
-        <v>467</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>468</v>
+      <c r="A188" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B188" s="20"/>
+      <c r="C188" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="B189" s="20"/>
-      <c r="C189" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>476</v>
+      <c r="A189" s="31" t="s">
+        <v>569</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="C189" s="31" t="s">
+        <v>571</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1">
       <c r="A190" s="31" t="s">
+        <v>572</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C190" s="31" t="s">
+        <v>574</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A191" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="B191" s="20"/>
+      <c r="C191" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="B190" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C190" s="31" t="s">
-        <v>479</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="32" t="s">
-        <v>575</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="C191" s="32" t="s">
-        <v>577</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>588</v>
+      <c r="D191" s="5" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="32" t="s">
-        <v>578</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="C192" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>589</v>
+      <c r="A192" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="B192" s="20"/>
+      <c r="C192" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1">
       <c r="A193" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="B193" s="20"/>
+        <v>684</v>
+      </c>
+      <c r="B193" s="20" t="s">
+        <v>683</v>
+      </c>
       <c r="C193" s="16" t="s">
-        <v>482</v>
+        <v>682</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
       <c r="A194" s="16" t="s">
-        <v>661</v>
-      </c>
-      <c r="B194" s="20"/>
+        <v>685</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C194" s="16" t="s">
-        <v>662</v>
+        <v>13</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>663</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A195" s="2" t="s">
-        <v>491</v>
+      <c r="A195" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>491</v>
+        <v>473</v>
+      </c>
+      <c r="C195" s="30" t="s">
+        <v>474</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B196" s="36" t="s">
-        <v>495</v>
+        <v>485</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A197" s="60" t="s">
-        <v>484</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="C197" s="32" t="s">
-        <v>486</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1"/>
+      <c r="A197" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B197" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A198" s="58" t="s">
+        <v>478</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C198" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="200" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="201" spans="1:4" ht="15.75" customHeight="1"/>
@@ -6925,151 +6958,154 @@
     <row r="1125" ht="15.75" customHeight="1"/>
     <row r="1126" ht="15.75" customHeight="1"/>
     <row r="1127" ht="15.75" customHeight="1"/>
+    <row r="1128" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B16" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B21" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D21" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B22" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B28" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B30" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B31" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B32" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B33" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B36" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D36" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B37" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B40" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B41" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B42" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B45" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B46" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B47" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B48" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D48" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B49" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B51" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B53" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B54" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B55" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B56" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B57" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B59" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B60" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B61" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B62" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B63" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B64" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D64" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B65" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B67" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B69" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B70" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D70" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B71" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B75" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D75" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B76" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D76" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B79" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B81" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D81" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B83" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B84" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B89" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D89" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B90" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B92" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B93" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B100" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B101" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B102" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B104" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B114" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B119" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B120" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B123" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B124" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B125" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D125" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B127" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B130" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B131" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D131" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B133" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B134" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B135" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B144" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B146" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B149" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B151" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B153" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B154" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B157" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B158" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B160" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D160" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B162" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B167" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B168" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B170" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D170" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B171" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B172" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B173" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B174" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B184" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B186" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B187" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B188" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B122" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B190" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B58" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B195" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B196" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B82" r:id="rId113" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B105" r:id="rId114" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B183" r:id="rId115" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B194" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B20" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D20" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B25" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B28" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B29" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D29" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B30" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B31" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B35" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D35" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B36" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B39" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B40" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B41" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B44" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B47" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D47" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B48" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B52" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B53" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B54" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B55" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B56" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B58" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B59" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B60" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B61" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B62" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B63" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D63" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B64" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B66" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B68" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B69" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D69" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B70" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D74" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B75" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D75" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B80" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B82" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B83" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B88" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D88" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B89" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B91" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B92" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B99" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B100" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B101" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B103" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B113" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B118" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B119" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B122" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B123" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B124" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D124" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B126" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B129" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B130" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D130" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B132" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B133" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B134" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B143" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B145" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B148" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B150" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B152" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B153" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B156" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B157" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B159" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D159" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B161" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B166" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B167" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B169" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D169" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B170" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B171" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B172" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B173" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B183" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B185" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B186" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B187" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B121" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B195" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B57" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B196" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B197" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B81" r:id="rId113" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B104" r:id="rId114" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B182" r:id="rId115" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="B4" r:id="rId116" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="D4" r:id="rId117" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B6" r:id="rId118" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D6" r:id="rId119" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B34" r:id="rId120" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D34" r:id="rId121" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B68" r:id="rId122" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D68" r:id="rId123" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B73" r:id="rId124" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D73" r:id="rId125" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B77" r:id="rId126" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D77" r:id="rId127" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B78" r:id="rId128" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D78" r:id="rId129" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B97" r:id="rId130" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B191" r:id="rId131" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D191" r:id="rId132" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B192" r:id="rId133" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D192" r:id="rId134" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B197" r:id="rId135" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D197" r:id="rId136" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B20" r:id="rId137" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B15" r:id="rId138" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B33" r:id="rId120" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D33" r:id="rId121" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B67" r:id="rId122" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D67" r:id="rId123" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B72" r:id="rId124" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D72" r:id="rId125" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B76" r:id="rId126" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D76" r:id="rId127" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B77" r:id="rId128" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D77" r:id="rId129" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B96" r:id="rId130" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B189" r:id="rId131" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D189" r:id="rId132" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B190" r:id="rId133" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D190" r:id="rId134" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B198" r:id="rId135" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D198" r:id="rId136" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B19" r:id="rId137" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B14" r:id="rId138" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B51" r:id="rId139" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B22" r:id="rId140" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId139"/>
+    <tablePart r:id="rId141"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CA0BA6-5A35-BA4F-906A-A1C517E5DBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235E6BA3-E40C-3B47-820A-40B7B44344BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="738">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -1873,9 +1873,6 @@
     <t>https://d-nb.info/gnd/4524426-1</t>
   </si>
   <si>
-    <t xml:space="preserve"> CafeGerbeaud</t>
-  </si>
-  <si>
     <t>Cafe Henry</t>
   </si>
   <si>
@@ -2495,9 +2492,6 @@
     <t>Presse/Sarajevoer Tagblatt</t>
   </si>
   <si>
-    <t>&lt;orgName key"SarajevoerTagblatt"&gt;</t>
-  </si>
-  <si>
     <t>Eisenbahn/k.k. Staatsbahn</t>
   </si>
   <si>
@@ -2706,6 +2700,129 @@
   </si>
   <si>
     <t>&lt;orgName key="DeutschnationaleKorrespondenz"&gt;</t>
+  </si>
+  <si>
+    <t>Landesirren-Anstalt Dobřan</t>
+  </si>
+  <si>
+    <t>Landesirrenanstalt</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Landesirrenanstalt"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="SarajevoerTagblatt"&gt;</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/110494894X</t>
+  </si>
+  <si>
+    <t>AkademieWissenschaftenWien</t>
+  </si>
+  <si>
+    <t>Kaiserliche Akademie der Wissenschaften in Wien</t>
+  </si>
+  <si>
+    <t>Serbische Akademie der Wissenschaften und Künste</t>
+  </si>
+  <si>
+    <t>AkademieWissenschaftenBelgrad</t>
+  </si>
+  <si>
+    <t>Neue Wiener Handelsakademie</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/380838-5</t>
+  </si>
+  <si>
+    <t>Handelsakademie</t>
+  </si>
+  <si>
+    <t>Handelskammer Belgrad</t>
+  </si>
+  <si>
+    <t>Handelskammer Sofia</t>
+  </si>
+  <si>
+    <t>Landesregierung für Bosnien und Herzegowina</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/5123628-X</t>
+  </si>
+  <si>
+    <t>LandesregierungBosnien</t>
+  </si>
+  <si>
+    <t>Landtag Bosnien-Herzegowina</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4640060-6</t>
+  </si>
+  <si>
+    <t>LandtagBosnien</t>
+  </si>
+  <si>
+    <t>Nationalmuseum Belgrad</t>
+  </si>
+  <si>
+    <t>NationalmuseumBelgrad</t>
+  </si>
+  <si>
+    <t>Reichsrat/Abgeordnetenhaus/Parteien/Deutscher Nationalverband</t>
+  </si>
+  <si>
+    <t>DeutscherNationalverband</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1041439075</t>
+  </si>
+  <si>
+    <t>CafeGerbeaud</t>
+  </si>
+  <si>
+    <t>Nemzeti Kaszinó</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/7742011-1</t>
+  </si>
+  <si>
+    <t>NemzetiKaszino</t>
+  </si>
+  <si>
+    <t>Prosvjeta</t>
+  </si>
+  <si>
+    <t>Prosvjeta (Serbischer Kulturverein)</t>
+  </si>
+  <si>
+    <t>Presse/Reichspost</t>
+  </si>
+  <si>
+    <t>Reichspost</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4491729-6</t>
+  </si>
+  <si>
+    <t>Serbisches Rotes Kreuz</t>
+  </si>
+  <si>
+    <t>SerbischesRotesKreuz</t>
+  </si>
+  <si>
+    <t>Presse/Le Temps</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/7729567-5</t>
+  </si>
+  <si>
+    <t>Temps</t>
+  </si>
+  <si>
+    <t>Universitäten/Universität Belgrad</t>
+  </si>
+  <si>
+    <t>UniversitaetBelgrad</t>
   </si>
 </sst>
 </file>
@@ -2944,7 +3061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3047,6 +3164,7 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3142,7 +3260,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D193" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D208" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3351,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1128"/>
+  <dimension ref="A1:Z1144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3390,2671 +3508,2829 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>501</v>
-      </c>
+      <c r="A3" s="30" t="s">
+        <v>703</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>576</v>
-      </c>
+      <c r="A4" s="30" t="s">
+        <v>704</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="30" t="s">
+        <v>705</v>
+      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="31" t="s">
-        <v>505</v>
-      </c>
-      <c r="B5" s="23"/>
+        <v>499</v>
+      </c>
+      <c r="B5" s="19"/>
       <c r="C5" s="31" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>510</v>
+        <v>722</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="31" t="s">
-        <v>511</v>
-      </c>
-      <c r="B7" s="19"/>
+        <v>504</v>
+      </c>
+      <c r="B7" s="23"/>
       <c r="C7" s="31" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="31" t="s">
-        <v>514</v>
-      </c>
-      <c r="B8" s="19"/>
+        <v>507</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>508</v>
+      </c>
       <c r="C8" s="31" t="s">
-        <v>515</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>516</v>
+        <v>509</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="31" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>518</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="16" t="s">
-        <v>611</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>613</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="16" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>657</v>
+        <v>9</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>656</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>658</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>659</v>
+        <v>610</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>660</v>
+        <v>611</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>661</v>
+        <v>612</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>678</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="B14" s="59" t="s">
+        <v>653</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16" t="s">
         <v>633</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="B16" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C16" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>629</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>627</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="16" t="s">
+        <v>642</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>617</v>
+      </c>
+      <c r="C21" s="31" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="31" t="s">
-        <v>627</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>630</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>628</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="16" t="s">
-        <v>644</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>675</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="31" t="s">
-        <v>617</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>618</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>681</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="31" t="s">
+      <c r="D21" s="6" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B22" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C22" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="16" t="s">
-        <v>607</v>
-      </c>
-      <c r="B22" s="59" t="s">
-        <v>609</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>608</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>610</v>
+      <c r="D22" s="6" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="16" t="s">
-        <v>623</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>624</v>
+        <v>21</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>625</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>626</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
+      <c r="A24" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>608</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="16" t="s">
-        <v>28</v>
+        <v>622</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>29</v>
+        <v>623</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>31</v>
+        <v>625</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>34</v>
+      <c r="A26" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="4"/>
       <c r="C28" s="16" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="31" t="s">
-        <v>520</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="A29" s="16" t="s">
+        <v>709</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="16">
-      <c r="A31" s="7" t="s">
-        <v>49</v>
+      <c r="A30" s="16" t="s">
+        <v>710</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="16" t="s">
+        <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>52</v>
+        <v>36</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="16" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="B33" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16">
+      <c r="A35" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C37" s="31" t="s">
         <v>521</v>
       </c>
-      <c r="C33" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="31" t="s">
+      <c r="D37" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C38" s="31" t="s">
         <v>667</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>669</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="31" t="s">
+      <c r="D38" s="6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C39" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>670</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>471</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A41" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A42" s="30" t="s">
+        <v>668</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B45" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C45" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="30" t="s">
+    <row r="46" spans="1:4">
+      <c r="A46" s="30" t="s">
+        <v>714</v>
+      </c>
+      <c r="B46" s="48" t="s">
+        <v>715</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>716</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C47" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D47" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="36"/>
+      <c r="C48" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42" s="2" t="s">
+    <row r="49" spans="1:4">
+      <c r="A49" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="2" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>712</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A64" s="30" t="s">
+        <v>574</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26">
+      <c r="A65" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B65" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26">
+      <c r="A66" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="13"/>
+      <c r="Q66" s="13"/>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="13"/>
+      <c r="V66" s="13"/>
+      <c r="W66" s="13"/>
+      <c r="X66" s="13"/>
+      <c r="Y66" s="13"/>
+      <c r="Z66" s="13"/>
+    </row>
+    <row r="67" spans="1:26" ht="16">
+      <c r="A67" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" ht="16">
+      <c r="A68" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" ht="16">
+      <c r="A69" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26">
+      <c r="A70" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26">
+      <c r="A71" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26">
+      <c r="A72" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26">
-      <c r="A49" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26">
-      <c r="A50" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26">
-      <c r="A51" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B51" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26">
-      <c r="A52" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26">
-      <c r="A53" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26">
-      <c r="A54" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26">
-      <c r="A55" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26">
-      <c r="A56" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>575</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26">
-      <c r="A58" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="B58" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
-      <c r="A59" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="B59" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C59" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
-      <c r="Q59" s="13"/>
-      <c r="R59" s="13"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="13"/>
-      <c r="U59" s="13"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="13"/>
-      <c r="X59" s="13"/>
-      <c r="Y59" s="13"/>
-      <c r="Z59" s="13"/>
-    </row>
-    <row r="60" spans="1:26" ht="16">
-      <c r="A60" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" ht="16">
-      <c r="A61" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26" ht="16">
-      <c r="A62" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26">
-      <c r="A63" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B63" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D63" s="33" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="B64" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="D65" s="2" t="s">
+    <row r="73" spans="1:26">
+      <c r="A73" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26">
+      <c r="A74" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26">
+      <c r="A75" s="31" t="s">
+        <v>717</v>
+      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" s="31" t="s">
+        <v>718</v>
+      </c>
+      <c r="D75" s="6"/>
+    </row>
+    <row r="76" spans="1:26">
+      <c r="A76" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26">
+      <c r="A77" s="30" t="s">
+        <v>706</v>
+      </c>
+      <c r="B77" s="48" t="s">
+        <v>707</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>708</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="1:26">
+      <c r="A78" s="30" t="s">
+        <v>723</v>
+      </c>
+      <c r="B78" s="48" t="s">
+        <v>724</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>725</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="1:26">
+      <c r="A79" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26">
+      <c r="A80" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="B81" s="19"/>
+      <c r="C81" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="D81" s="24" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B83" s="19"/>
+      <c r="C83" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="D83" s="24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="30">
+      <c r="A86" s="31" t="s">
+        <v>535</v>
+      </c>
+      <c r="B86" s="46" t="s">
+        <v>536</v>
+      </c>
+      <c r="C86" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="30">
+      <c r="A87" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="C87" s="31" t="s">
+        <v>540</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B88" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D90" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="16">
+      <c r="A92" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C66" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="31" t="s">
-        <v>524</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="C67" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="B68" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="B69" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="31" t="s">
-        <v>530</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>531</v>
-      </c>
-      <c r="C72" s="31" t="s">
-        <v>532</v>
-      </c>
-      <c r="D72" s="26" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="31" t="s">
-        <v>534</v>
-      </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="31" t="s">
-        <v>534</v>
-      </c>
-      <c r="D73" s="24" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D74" s="35" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B75" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D75" s="33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="30">
-      <c r="A76" s="31" t="s">
-        <v>536</v>
-      </c>
-      <c r="B76" s="46" t="s">
-        <v>537</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>538</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="30">
-      <c r="A77" s="31" t="s">
-        <v>539</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>540</v>
-      </c>
-      <c r="C77" s="31" t="s">
+    <row r="96" spans="1:4">
+      <c r="A96" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26">
+      <c r="A97" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16" t="s">
+        <v>615</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26">
+      <c r="A98" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A99" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="13"/>
+      <c r="L99" s="13"/>
+      <c r="M99" s="13"/>
+      <c r="N99" s="13"/>
+      <c r="O99" s="13"/>
+      <c r="P99" s="13"/>
+      <c r="Q99" s="13"/>
+      <c r="R99" s="13"/>
+      <c r="S99" s="13"/>
+      <c r="T99" s="13"/>
+      <c r="U99" s="13"/>
+      <c r="V99" s="13"/>
+      <c r="W99" s="13"/>
+      <c r="X99" s="13"/>
+      <c r="Y99" s="13"/>
+      <c r="Z99" s="13"/>
+    </row>
+    <row r="100" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A100" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A101" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D101" s="5"/>
+    </row>
+    <row r="102" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A102" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="D102" s="5"/>
+    </row>
+    <row r="103" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A103" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="40"/>
+      <c r="C103" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A104" s="62" t="s">
+        <v>733</v>
+      </c>
+      <c r="B104" s="48" t="s">
+        <v>734</v>
+      </c>
+      <c r="C104" s="62" t="s">
+        <v>735</v>
+      </c>
+      <c r="D104" s="5"/>
+    </row>
+    <row r="105" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A105" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A106" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A107" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B78" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B80" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26">
-      <c r="A81" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="B81" s="48" t="s">
-        <v>494</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" ht="16">
-      <c r="A82" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B82" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="83" spans="1:26">
-      <c r="A83" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C83" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="84" spans="1:26">
-      <c r="A84" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="85" spans="1:26">
-      <c r="A85" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26">
-      <c r="A86" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26">
-      <c r="A87" s="16" t="s">
-        <v>615</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16" t="s">
-        <v>616</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="88" spans="1:26">
-      <c r="A88" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C88" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A89" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C89" s="49" t="s">
-        <v>218</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
-      <c r="M89" s="13"/>
-      <c r="N89" s="13"/>
-      <c r="O89" s="13"/>
-      <c r="P89" s="13"/>
-      <c r="Q89" s="13"/>
-      <c r="R89" s="13"/>
-      <c r="S89" s="13"/>
-      <c r="T89" s="13"/>
-      <c r="U89" s="13"/>
-      <c r="V89" s="13"/>
-      <c r="W89" s="13"/>
-      <c r="X89" s="13"/>
-      <c r="Y89" s="13"/>
-      <c r="Z89" s="13"/>
-    </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A90" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A91" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="B91" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="C91" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A92" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="B92" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="C92" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A93" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="B93" s="40"/>
-      <c r="C93" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A94" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A95" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A96" s="31" t="s">
+      <c r="B107" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="C107" s="31" t="s">
         <v>543</v>
       </c>
-      <c r="C96" s="31" t="s">
+      <c r="D107" s="14" t="s">
         <v>544</v>
       </c>
-      <c r="D96" s="14" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A97" s="38" t="s">
+    </row>
+    <row r="108" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A108" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B97" s="39"/>
-      <c r="C97" s="40" t="s">
+      <c r="B108" s="39"/>
+      <c r="C108" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D108" s="11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A98" s="31" t="s">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A109" s="31" t="s">
         <v>239</v>
-      </c>
-      <c r="B98" s="19"/>
-      <c r="C98" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A99" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C99" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A100" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="B100" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="C100" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A101" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C101" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A102" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A103" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C103" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A104" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B104" s="48" t="s">
-        <v>496</v>
-      </c>
-      <c r="C104" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A105" s="30" t="s">
-        <v>635</v>
-      </c>
-      <c r="B105" s="48"/>
-      <c r="C105" s="30" t="s">
-        <v>636</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A106" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C106" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A107" s="30" t="s">
-        <v>638</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="30" t="s">
-        <v>672</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A108" s="30" t="s">
-        <v>640</v>
-      </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="30" t="s">
-        <v>673</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A109" s="31" t="s">
-        <v>266</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="31" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A110" s="51" t="s">
-        <v>546</v>
-      </c>
-      <c r="B110" s="27"/>
-      <c r="C110" s="51" t="s">
-        <v>547</v>
-      </c>
-      <c r="D110" s="28" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A111" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="B111" s="19"/>
-      <c r="C111" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A112" s="31" t="s">
-        <v>642</v>
-      </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="31" t="s">
-        <v>674</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>643</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A110" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C110" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A111" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="C111" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A112" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A113" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>275</v>
+      <c r="A113" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A114" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="C114" s="16" t="s">
-        <v>620</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>622</v>
+      <c r="A114" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C114" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A115" s="16" t="s">
-        <v>649</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>651</v>
+      <c r="A115" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B115" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A116" s="16" t="s">
-        <v>676</v>
-      </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="16" t="s">
-        <v>677</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>693</v>
+      <c r="A116" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="B116" s="48"/>
+      <c r="C116" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A117" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="B117" s="4"/>
-      <c r="C117" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>278</v>
+      <c r="A117" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
       <c r="A118" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B118" s="35" t="s">
-        <v>280</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="B118" s="3"/>
       <c r="C118" s="30" t="s">
-        <v>281</v>
+        <v>670</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>282</v>
+        <v>638</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
       <c r="A119" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="B119" s="3"/>
       <c r="C119" s="30" t="s">
-        <v>285</v>
+        <v>671</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>286</v>
+        <v>640</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A120" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="B120" s="20"/>
-      <c r="C120" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>288</v>
+      <c r="A120" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="19"/>
+      <c r="C120" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C121" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>470</v>
+      <c r="A121" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="B121" s="27"/>
+      <c r="C121" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="D121" s="28" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B122" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C122" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>180</v>
+      <c r="A122" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="19"/>
+      <c r="C122" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="D122" s="14" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="B123" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="C123" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>292</v>
-      </c>
+      <c r="A123" s="31" t="s">
+        <v>728</v>
+      </c>
+      <c r="B123" s="60" t="s">
+        <v>730</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>729</v>
+      </c>
+      <c r="D123" s="14"/>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1">
       <c r="A124" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>294</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="B124" s="19"/>
       <c r="C124" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>296</v>
+        <v>672</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="51" t="s">
-        <v>549</v>
-      </c>
-      <c r="B125" s="29"/>
-      <c r="C125" s="51" t="s">
-        <v>550</v>
-      </c>
-      <c r="D125" s="28" t="s">
-        <v>551</v>
+      <c r="A125" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B126" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C126" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>300</v>
+      <c r="A126" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>601</v>
+      <c r="A127" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A128" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>602</v>
+      <c r="A128" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C129" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>308</v>
+      <c r="A129" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="D130" s="33" t="s">
-        <v>312</v>
+      <c r="A130" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="C130" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B131" s="4"/>
-      <c r="C131" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>606</v>
-      </c>
+      <c r="A131" s="30" t="s">
+        <v>727</v>
+      </c>
+      <c r="B131" s="35"/>
+      <c r="C131" s="30" t="s">
+        <v>726</v>
+      </c>
+      <c r="D131" s="2"/>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1">
       <c r="A132" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B132" s="35" t="s">
-        <v>316</v>
+        <v>283</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>284</v>
       </c>
       <c r="C132" s="30" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C133" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>322</v>
+      <c r="A133" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="20"/>
+      <c r="C133" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1">
       <c r="A134" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B134" s="35" t="s">
-        <v>324</v>
+        <v>468</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="C134" s="30" t="s">
-        <v>325</v>
+        <v>468</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>326</v>
+        <v>470</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="30" customHeight="1">
-      <c r="A136" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B136" s="5"/>
-      <c r="C136" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>332</v>
+      <c r="A135" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B135" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C135" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A136" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="C136" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="B137" s="5"/>
-      <c r="C137" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>335</v>
+      <c r="A137" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C137" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="B138" s="2"/>
-      <c r="C138" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>603</v>
+      <c r="A138" s="51" t="s">
+        <v>548</v>
+      </c>
+      <c r="B138" s="29"/>
+      <c r="C138" s="51" t="s">
+        <v>549</v>
+      </c>
+      <c r="D138" s="28" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="B139" s="39"/>
-      <c r="C139" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>340</v>
+      <c r="A139" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="B139" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C139" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>343</v>
+      <c r="A140" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>346</v>
+      <c r="A141" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
       <c r="A142" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B142" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="C142" s="30" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>604</v>
+        <v>308</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B143" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="C143" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>352</v>
+      <c r="A143" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D143" s="33" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A144" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B144" s="26"/>
-      <c r="C144" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D144" s="14" t="s">
-        <v>355</v>
+      <c r="A144" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1">
       <c r="A145" s="30" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="C145" s="30" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B146" s="26"/>
-      <c r="C146" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="D146" s="14" t="s">
-        <v>361</v>
+      <c r="A146" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C146" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B147" s="26"/>
-      <c r="C147" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="D147" s="14" t="s">
-        <v>364</v>
-      </c>
+      <c r="A147" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="B147" s="48" t="s">
+        <v>721</v>
+      </c>
+      <c r="C147" s="30" t="s">
+        <v>720</v>
+      </c>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
       <c r="A148" s="30" t="s">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="C148" s="30" t="s">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>368</v>
+        <v>326</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B149" s="35"/>
-      <c r="C149" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A150" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="B150" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="C150" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>375</v>
+      <c r="A149" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B149" s="5"/>
+      <c r="C149" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="30" customHeight="1">
+      <c r="A150" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" s="5"/>
+      <c r="C150" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B151" s="4"/>
+        <v>333</v>
+      </c>
+      <c r="B151" s="5"/>
       <c r="C151" s="16" t="s">
-        <v>377</v>
+        <v>334</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>378</v>
+        <v>335</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
       <c r="A152" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>380</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="B152" s="2"/>
       <c r="C152" s="30" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>382</v>
+        <v>602</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="C153" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>386</v>
+      <c r="A153" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="39"/>
+      <c r="C153" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="B154" s="3"/>
-      <c r="C154" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>585</v>
+      <c r="A154" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="5"/>
+      <c r="C154" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="30" t="s">
-        <v>664</v>
-      </c>
-      <c r="B155" s="3"/>
-      <c r="C155" s="30" t="s">
-        <v>665</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>692</v>
+      <c r="A155" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="5"/>
+      <c r="C155" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1">
       <c r="A156" s="30" t="s">
-        <v>663</v>
-      </c>
-      <c r="B156" s="35" t="s">
-        <v>388</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="B156" s="2"/>
       <c r="C156" s="30" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>390</v>
+        <v>603</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>394</v>
+      <c r="A157" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="B157" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="C157" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="B158" s="39"/>
-      <c r="C158" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>397</v>
+      <c r="A158" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B158" s="26"/>
+      <c r="C158" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D158" s="14" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="C159" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>401</v>
+      <c r="A159" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B160" s="3"/>
-      <c r="C160" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>605</v>
+      <c r="A160" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B160" s="26"/>
+      <c r="C160" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D160" s="14" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B161" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="C161" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="D161" s="21" t="s">
-        <v>406</v>
+      <c r="A161" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B161" s="26"/>
+      <c r="C161" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="D161" s="14" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="B162" s="39"/>
-      <c r="C162" s="54" t="s">
-        <v>408</v>
-      </c>
-      <c r="D162" s="21" t="s">
-        <v>586</v>
+      <c r="A162" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>366</v>
+      </c>
+      <c r="C162" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="55" t="s">
-        <v>409</v>
-      </c>
-      <c r="B163" s="4"/>
-      <c r="C163" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>587</v>
+      <c r="A163" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B163" s="35"/>
+      <c r="C163" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1">
       <c r="A164" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B164" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>373</v>
+      </c>
       <c r="C164" s="30" t="s">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>588</v>
+        <v>375</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B165" s="2"/>
-      <c r="C165" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>589</v>
+      <c r="A165" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
       <c r="A166" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>416</v>
+        <v>379</v>
+      </c>
+      <c r="B166" s="35" t="s">
+        <v>380</v>
       </c>
       <c r="C166" s="30" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="B167" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="C167" s="56" t="s">
-        <v>421</v>
+      <c r="A167" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B167" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="C167" s="30" t="s">
+        <v>385</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>422</v>
+        <v>386</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
       <c r="A168" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="B168" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="B168" s="3"/>
       <c r="C168" s="30" t="s">
-        <v>424</v>
+        <v>387</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C169" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D169" s="33" t="s">
-        <v>428</v>
+      <c r="A169" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B169" s="3"/>
+      <c r="C169" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C170" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>432</v>
+      <c r="A170" s="30" t="s">
+        <v>661</v>
+      </c>
+      <c r="B170" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="C170" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B171" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="C171" s="30" t="s">
-        <v>584</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>435</v>
+      <c r="A171" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="B171" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C172" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>439</v>
+      <c r="A172" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B172" s="39"/>
+      <c r="C172" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C173" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>443</v>
+      <c r="A173" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C173" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1">
       <c r="A174" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B174" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="B174" s="3"/>
       <c r="C174" s="30" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="30" t="s">
-        <v>446</v>
-      </c>
-      <c r="B175" s="2"/>
-      <c r="C175" s="30" t="s">
-        <v>447</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>592</v>
+      <c r="A175" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B175" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C175" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D175" s="21" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="B176" s="14"/>
-      <c r="C176" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>666</v>
+      <c r="A176" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="B176" s="39"/>
+      <c r="C176" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D176" s="21" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="B177" s="14"/>
-      <c r="C177" s="31" t="s">
-        <v>555</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>556</v>
+      <c r="A177" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B177" s="4"/>
+      <c r="C177" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="B178" s="14"/>
-      <c r="C178" s="31" t="s">
-        <v>558</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>559</v>
+      <c r="A178" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="B178" s="2"/>
+      <c r="C178" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="B179" s="14"/>
-      <c r="C179" s="31" t="s">
-        <v>561</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>562</v>
+      <c r="A179" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="B179" s="2"/>
+      <c r="C179" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A180" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="B180" s="14"/>
-      <c r="C180" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="D180" s="14" t="s">
-        <v>565</v>
+      <c r="A180" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C180" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="B181" s="14"/>
-      <c r="C181" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>568</v>
+      <c r="A181" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B181" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C181" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A182" s="31" t="s">
-        <v>448</v>
-      </c>
-      <c r="B182" s="48" t="s">
-        <v>498</v>
-      </c>
-      <c r="C182" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="D182" s="14" t="s">
-        <v>450</v>
+      <c r="A182" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="B182" s="2"/>
+      <c r="C182" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
       <c r="A183" s="16" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>454</v>
+        <v>427</v>
+      </c>
+      <c r="D183" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
       <c r="A184" s="16" t="s">
-        <v>647</v>
-      </c>
-      <c r="B184" s="4"/>
+        <v>429</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="C184" s="16" t="s">
-        <v>648</v>
+        <v>431</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>691</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
       <c r="A185" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>456</v>
+        <v>433</v>
+      </c>
+      <c r="B185" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="C185" s="30" t="s">
-        <v>457</v>
+        <v>583</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>462</v>
+      <c r="A186" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C186" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
       <c r="A187" s="30" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="C187" s="30" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="B188" s="20"/>
-      <c r="C188" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>690</v>
+      <c r="A188" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B188" s="2"/>
+      <c r="C188" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="C189" s="31" t="s">
-        <v>571</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>582</v>
+      <c r="A189" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="B189" s="2"/>
+      <c r="C189" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1">
       <c r="A190" s="31" t="s">
+        <v>551</v>
+      </c>
+      <c r="B190" s="14"/>
+      <c r="C190" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="D190" s="14" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A191" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="B191" s="14"/>
+      <c r="C191" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="D191" s="14" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A192" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B192" s="14"/>
+      <c r="C192" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="D192" s="14" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A193" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="B193" s="14"/>
+      <c r="C193" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="D193" s="14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A194" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="B194" s="14"/>
+      <c r="C194" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="D194" s="14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A195" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B195" s="14"/>
+      <c r="C195" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A196" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B196" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="C196" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A197" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C197" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A198" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="D198" s="5"/>
+    </row>
+    <row r="199" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A199" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B199" s="4"/>
+      <c r="C199" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A200" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C200" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A201" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A202" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C202" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A203" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B203" s="20"/>
+      <c r="C203" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A204" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C204" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A205" s="31" t="s">
+        <v>571</v>
+      </c>
+      <c r="B205" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="C205" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="C190" s="31" t="s">
-        <v>574</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="16" t="s">
+      <c r="D205" s="6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A206" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="B191" s="20"/>
-      <c r="C191" s="16" t="s">
+      <c r="B206" s="20"/>
+      <c r="C206" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="16" t="s">
-        <v>653</v>
-      </c>
-      <c r="B192" s="20"/>
-      <c r="C192" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="16" t="s">
+      <c r="D206" s="5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A207" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B207" s="20"/>
+      <c r="C207" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A208" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="B208" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="C208" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A210" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B193" s="20" t="s">
-        <v>683</v>
-      </c>
-      <c r="C193" s="16" t="s">
-        <v>682</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C194" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A195" s="30" t="s">
-        <v>686</v>
-      </c>
-      <c r="B195" s="3" t="s">
+      <c r="B210" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C195" s="30" t="s">
+      <c r="C210" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="D210" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A196" s="2" t="s">
+    <row r="211" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A211" s="30" t="s">
+        <v>736</v>
+      </c>
+      <c r="B211" s="3"/>
+      <c r="C211" s="30" t="s">
+        <v>737</v>
+      </c>
+      <c r="D211" s="2"/>
+    </row>
+    <row r="212" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A212" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B212" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C212" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="D212" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A197" s="2" t="s">
+    <row r="213" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A213" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B197" s="35" t="s">
+      <c r="B213" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C213" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="D213" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A198" s="58" t="s">
+    <row r="214" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A214" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B214" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C198" s="31" t="s">
+      <c r="C214" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D198" s="6" t="s">
+      <c r="D214" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="216" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="217" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="218" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="219" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="220" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -6959,153 +7235,177 @@
     <row r="1126" ht="15.75" customHeight="1"/>
     <row r="1127" ht="15.75" customHeight="1"/>
     <row r="1128" ht="15.75" customHeight="1"/>
+    <row r="1129" ht="15.75" customHeight="1"/>
+    <row r="1130" ht="15.75" customHeight="1"/>
+    <row r="1131" ht="15.75" customHeight="1"/>
+    <row r="1132" ht="15.75" customHeight="1"/>
+    <row r="1133" ht="15.75" customHeight="1"/>
+    <row r="1134" ht="15.75" customHeight="1"/>
+    <row r="1135" ht="15.75" customHeight="1"/>
+    <row r="1136" ht="15.75" customHeight="1"/>
+    <row r="1137" ht="15.75" customHeight="1"/>
+    <row r="1138" ht="15.75" customHeight="1"/>
+    <row r="1139" ht="15.75" customHeight="1"/>
+    <row r="1140" ht="15.75" customHeight="1"/>
+    <row r="1141" ht="15.75" customHeight="1"/>
+    <row r="1142" ht="15.75" customHeight="1"/>
+    <row r="1143" ht="15.75" customHeight="1"/>
+    <row r="1144" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B194" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B20" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D20" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B25" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B28" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B29" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D29" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B30" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B31" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B35" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D35" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B36" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B39" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B40" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B41" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B44" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D45" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B47" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D47" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B48" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B49" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B52" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B53" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B54" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B55" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B56" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B58" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B59" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B60" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B61" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B62" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B63" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D63" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B64" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B66" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B68" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B69" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D69" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B70" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D74" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B75" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D75" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B80" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B82" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B83" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B88" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D88" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B89" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B91" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B92" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B99" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B100" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B101" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B103" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B113" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B118" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B119" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B122" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B123" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B124" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D124" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B126" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B129" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B130" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D130" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B132" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B133" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B134" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B143" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B145" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B148" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B150" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B152" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B153" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B156" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B157" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B159" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D159" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B161" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B166" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B167" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B169" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D169" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B170" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B171" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B172" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B173" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B183" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B185" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B186" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B187" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B121" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B195" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B57" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B196" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B197" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B81" r:id="rId113" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B104" r:id="rId114" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B182" r:id="rId115" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
-    <hyperlink ref="B4" r:id="rId116" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
-    <hyperlink ref="D4" r:id="rId117" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
-    <hyperlink ref="B6" r:id="rId118" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
-    <hyperlink ref="D6" r:id="rId119" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B33" r:id="rId120" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D33" r:id="rId121" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B67" r:id="rId122" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D67" r:id="rId123" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B72" r:id="rId124" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D72" r:id="rId125" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B76" r:id="rId126" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D76" r:id="rId127" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B77" r:id="rId128" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D77" r:id="rId129" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B96" r:id="rId130" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B189" r:id="rId131" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D189" r:id="rId132" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B190" r:id="rId133" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D190" r:id="rId134" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B198" r:id="rId135" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D198" r:id="rId136" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B19" r:id="rId137" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B14" r:id="rId138" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B51" r:id="rId139" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B22" r:id="rId140" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B209" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D22" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B23" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B26" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B31" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B32" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B33" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D33" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B34" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B35" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B36" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B39" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B43" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B45" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B47" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B50" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B51" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D51" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B52" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B54" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D54" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B55" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B56" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B57" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B62" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B63" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B65" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B66" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B67" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B68" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B69" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B70" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D70" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B71" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B73" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B76" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D79" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B84" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D84" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B85" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D85" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B88" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B90" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D90" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B92" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B93" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B98" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D98" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B99" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B101" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B102" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B110" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B111" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B112" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B114" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B125" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B130" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B132" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B135" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B136" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B137" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D137" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B139" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B142" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B143" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D143" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B145" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B146" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B148" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B157" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B159" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B162" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B164" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B166" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B167" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B170" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B171" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B173" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D173" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B175" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B180" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B181" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B183" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D183" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B184" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B185" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B186" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B187" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B197" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B200" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B201" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B202" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B134" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B210" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B64" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B212" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B213" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B91" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B115" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B196" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="D6" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
+    <hyperlink ref="B8" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
+    <hyperlink ref="D8" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
+    <hyperlink ref="B37" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D37" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B74" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D74" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B82" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D82" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B86" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D86" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B87" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D87" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B107" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B204" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D204" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B205" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D205" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B214" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D214" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B21" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B16" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B58" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B24" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B6" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
+    <hyperlink ref="B3" r:id="rId139" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
+    <hyperlink ref="B80" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B79" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B77" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B53" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B46" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B147" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B78" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B123" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B104" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId141"/>
+    <tablePart r:id="rId149"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235E6BA3-E40C-3B47-820A-40B7B44344BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB02B54-7265-D54B-96E7-38218984E15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="746">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2823,6 +2823,30 @@
   </si>
   <si>
     <t>UniversitaetBelgrad</t>
+  </si>
+  <si>
+    <t>Balkanbund</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1277681929</t>
+  </si>
+  <si>
+    <t>HandelskammerBelgrad</t>
+  </si>
+  <si>
+    <t>HandelskammerSofia</t>
+  </si>
+  <si>
+    <t>Kaufmannschaft Belgrad</t>
+  </si>
+  <si>
+    <t>KaufmannschaftBelgrad</t>
+  </si>
+  <si>
+    <t>Reichsrat/Abgeordnetenhauses/Ausschuss für die Angelegenheiten Bosniens und der Herzegowina</t>
+  </si>
+  <si>
+    <t>Bosnienausschuss</t>
   </si>
 </sst>
 </file>
@@ -3061,7 +3085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3164,7 +3188,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3260,7 +3283,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D208" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D211" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3469,7 +3492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1144"/>
+  <dimension ref="A1:Z1147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3530,2800 +3553,2833 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>501</v>
-      </c>
+      <c r="A5" s="30" t="s">
+        <v>738</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>739</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>738</v>
+      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>503</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="B6" s="19"/>
       <c r="C6" s="31" t="s">
-        <v>722</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>575</v>
+        <v>500</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="B7" s="23"/>
+        <v>502</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>503</v>
+      </c>
       <c r="C7" s="31" t="s">
-        <v>505</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>506</v>
+        <v>722</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="31" t="s">
-        <v>507</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>508</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="B8" s="23"/>
       <c r="C8" s="31" t="s">
-        <v>509</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>576</v>
+        <v>505</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="31" t="s">
-        <v>510</v>
-      </c>
-      <c r="B9" s="19"/>
+        <v>507</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>508</v>
+      </c>
       <c r="C9" s="31" t="s">
-        <v>511</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>512</v>
+        <v>509</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="31" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="31" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="31" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>518</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>610</v>
+        <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>611</v>
+        <v>9</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>612</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>613</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>653</v>
+        <v>610</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>655</v>
+        <v>611</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>656</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>676</v>
+        <v>656</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="16" t="s">
         <v>633</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B17" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C17" s="16" t="s">
         <v>631</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>677</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="31" t="s">
         <v>626</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B19" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C19" s="31" t="s">
         <v>627</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>628</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C21" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D21" s="33" t="s">
         <v>644</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="31" t="s">
-        <v>616</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>617</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>679</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>617</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>679</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B23" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C23" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>678</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="B24" s="59" t="s">
-        <v>608</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>607</v>
+        <v>22</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>609</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>608</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="16" t="s">
         <v>622</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>624</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="30" t="s">
+    <row r="27" spans="1:4">
+      <c r="A27" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C27" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="C28" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16" t="s">
-        <v>709</v>
+        <v>32</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="16" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="16"/>
+      <c r="C30" s="16" t="s">
+        <v>740</v>
+      </c>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C33" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="31" t="s">
+    <row r="34" spans="1:4">
+      <c r="A34" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B34" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C34" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="30" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C35" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="16">
-      <c r="A35" s="7" t="s">
+    <row r="36" spans="1:4" ht="16">
+      <c r="A36" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="16" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C37" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>521</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>577</v>
-      </c>
-    </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="31" t="s">
-        <v>665</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>667</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>694</v>
-      </c>
+      <c r="A38" s="16" t="s">
+        <v>742</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="D38" s="5"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>667</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B41" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C41" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="30" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C42" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A41" s="30" t="s">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A43" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="30" t="s">
+      <c r="B43" s="2"/>
+      <c r="C43" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A42" s="30" t="s">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A44" s="30" t="s">
         <v>668</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C44" s="30" t="s">
         <v>471</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="9" t="s">
+    <row r="45" spans="1:4">
+      <c r="A45" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B45" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D45" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="9" t="s">
+    <row r="46" spans="1:4">
+      <c r="A46" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="9" t="s">
+      <c r="B46" s="34"/>
+      <c r="C46" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D46" s="9" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="30" t="s">
-        <v>714</v>
-      </c>
-      <c r="B46" s="48" t="s">
-        <v>715</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>716</v>
-      </c>
-      <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>72</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>593</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="36"/>
+        <v>714</v>
+      </c>
+      <c r="B48" s="48" t="s">
+        <v>715</v>
+      </c>
       <c r="C48" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>594</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="36"/>
+      <c r="C50" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30" t="s">
+      <c r="B51" s="30"/>
+      <c r="C51" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B55" s="48" t="s">
         <v>712</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="D53" s="7"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="37" t="s">
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="33" t="s">
+      <c r="B56" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C56" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D56" s="10" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B56" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B58" s="61" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="B58" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="38" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="B62" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="40" t="s">
+      <c r="C62" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="16" t="s">
+    <row r="63" spans="1:4">
+      <c r="A63" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C63" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="30" t="s">
+    <row r="64" spans="1:4">
+      <c r="A64" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="B62" s="35" t="s">
+      <c r="B64" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C64" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>574</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="65" spans="1:26">
       <c r="A65" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A66" s="30" t="s">
+        <v>574</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26">
+      <c r="A67" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="48" t="s">
+      <c r="B67" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C67" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:26">
-      <c r="A66" s="41" t="s">
+    <row r="68" spans="1:26">
+      <c r="A68" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="42" t="s">
+      <c r="B68" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="41" t="s">
+      <c r="C68" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D68" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="13"/>
-      <c r="P66" s="13"/>
-      <c r="Q66" s="13"/>
-      <c r="R66" s="13"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="13"/>
-      <c r="U66" s="13"/>
-      <c r="V66" s="13"/>
-      <c r="W66" s="13"/>
-      <c r="X66" s="13"/>
-      <c r="Y66" s="13"/>
-      <c r="Z66" s="13"/>
-    </row>
-    <row r="67" spans="1:26" ht="16">
-      <c r="A67" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="68" spans="1:26" ht="16">
-      <c r="A68" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="13"/>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="13"/>
+      <c r="U68" s="13"/>
+      <c r="V68" s="13"/>
+      <c r="W68" s="13"/>
+      <c r="X68" s="13"/>
+      <c r="Y68" s="13"/>
+      <c r="Z68" s="13"/>
     </row>
     <row r="69" spans="1:26" ht="16">
       <c r="A69" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" ht="16">
+      <c r="A70" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" ht="16">
+      <c r="A71" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B71" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D71" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="70" spans="1:26">
-      <c r="A70" s="16" t="s">
+    <row r="72" spans="1:26">
+      <c r="A72" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="59" t="s">
+      <c r="B72" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C72" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D70" s="33" t="s">
+      <c r="D72" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="1:26">
-      <c r="A71" s="30" t="s">
+    <row r="73" spans="1:26">
+      <c r="A73" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="35" t="s">
+      <c r="B73" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C73" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:26">
-      <c r="A72" s="30" t="s">
+    <row r="74" spans="1:26">
+      <c r="A74" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="30" t="s">
+      <c r="B74" s="3"/>
+      <c r="C74" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>596</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26">
-      <c r="A73" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C73" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26">
-      <c r="A74" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>525</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="75" spans="1:26">
       <c r="A75" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26">
+      <c r="A76" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26">
+      <c r="A77" s="31" t="s">
         <v>717</v>
       </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="31" t="s">
+      <c r="B77" s="6"/>
+      <c r="C77" s="31" t="s">
         <v>718</v>
       </c>
-      <c r="D75" s="6"/>
-    </row>
-    <row r="76" spans="1:26">
-      <c r="A76" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26">
-      <c r="A77" s="30" t="s">
-        <v>706</v>
-      </c>
-      <c r="B77" s="48" t="s">
-        <v>707</v>
-      </c>
-      <c r="C77" s="30" t="s">
-        <v>708</v>
-      </c>
-      <c r="D77" s="2"/>
+      <c r="D77" s="6"/>
     </row>
     <row r="78" spans="1:26">
       <c r="A78" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26">
+      <c r="A79" s="30" t="s">
+        <v>706</v>
+      </c>
+      <c r="B79" s="48" t="s">
+        <v>707</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>708</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="1:26">
+      <c r="A80" s="30" t="s">
         <v>723</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B80" s="48" t="s">
         <v>724</v>
       </c>
-      <c r="C78" s="30" t="s">
+      <c r="C80" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="D78" s="2"/>
-    </row>
-    <row r="79" spans="1:26">
-      <c r="A79" s="43" t="s">
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="B79" s="32" t="s">
+      <c r="B81" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C81" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D81" s="15" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="80" spans="1:26">
-      <c r="A80" s="44" t="s">
+    <row r="82" spans="1:4">
+      <c r="A82" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B82" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C82" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D82" s="7" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="B81" s="19"/>
-      <c r="C81" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="D81" s="24" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>531</v>
-      </c>
-      <c r="D82" s="26" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="31" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B83" s="19"/>
       <c r="C83" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="D83" s="24" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="B85" s="19"/>
+      <c r="C85" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="D85" s="24" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="30" t="s">
+    <row r="86" spans="1:4">
+      <c r="A86" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C84" s="30" t="s">
+      <c r="C86" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="D84" s="35" t="s">
+      <c r="D86" s="35" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="16" t="s">
+    <row r="87" spans="1:4">
+      <c r="A87" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="45" t="s">
+      <c r="B87" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C87" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="D85" s="33" t="s">
+      <c r="D87" s="33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="30">
-      <c r="A86" s="31" t="s">
+    <row r="88" spans="1:4" ht="30">
+      <c r="A88" s="31" t="s">
         <v>535</v>
       </c>
-      <c r="B86" s="46" t="s">
+      <c r="B88" s="46" t="s">
         <v>536</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C88" s="31" t="s">
         <v>537</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D88" s="6" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="30">
-      <c r="A87" s="31" t="s">
+    <row r="89" spans="1:4" ht="30">
+      <c r="A89" s="31" t="s">
         <v>538</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>539</v>
       </c>
-      <c r="C87" s="31" t="s">
+      <c r="C89" s="31" t="s">
         <v>540</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D89" s="6" t="s">
         <v>580</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B88" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C88" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B90" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B90" s="47" t="s">
+      <c r="B92" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C92" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D92" s="33" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="B91" s="48" t="s">
-        <v>494</v>
-      </c>
-      <c r="C91" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="16">
-      <c r="A92" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B92" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C92" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
+      </c>
+      <c r="B93" s="48" t="s">
+        <v>494</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>206</v>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="16">
+      <c r="A94" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B95" s="30"/>
+        <v>200</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="C95" s="30" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>597</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B96" s="16"/>
       <c r="C96" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26">
+      <c r="A97" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26">
+      <c r="A98" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D98" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:26">
-      <c r="A97" s="16" t="s">
+    <row r="99" spans="1:26">
+      <c r="A99" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16" t="s">
+      <c r="B99" s="16"/>
+      <c r="C99" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D99" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="98" spans="1:26">
-      <c r="A98" s="31" t="s">
+    <row r="100" spans="1:26">
+      <c r="A100" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B100" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C98" s="31" t="s">
+      <c r="C100" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D100" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A99" s="49" t="s">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A101" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B101" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C99" s="49" t="s">
+      <c r="C101" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D101" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
-      <c r="L99" s="13"/>
-      <c r="M99" s="13"/>
-      <c r="N99" s="13"/>
-      <c r="O99" s="13"/>
-      <c r="P99" s="13"/>
-      <c r="Q99" s="13"/>
-      <c r="R99" s="13"/>
-      <c r="S99" s="13"/>
-      <c r="T99" s="13"/>
-      <c r="U99" s="13"/>
-      <c r="V99" s="13"/>
-      <c r="W99" s="13"/>
-      <c r="X99" s="13"/>
-      <c r="Y99" s="13"/>
-      <c r="Z99" s="13"/>
-    </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A100" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="B100" s="37"/>
-      <c r="C100" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A101" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="B101" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="D101" s="5"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="13"/>
+      <c r="L101" s="13"/>
+      <c r="M101" s="13"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="13"/>
+      <c r="P101" s="13"/>
+      <c r="Q101" s="13"/>
+      <c r="R101" s="13"/>
+      <c r="S101" s="13"/>
+      <c r="T101" s="13"/>
+      <c r="U101" s="13"/>
+      <c r="V101" s="13"/>
+      <c r="W101" s="13"/>
+      <c r="X101" s="13"/>
+      <c r="Y101" s="13"/>
+      <c r="Z101" s="13"/>
     </row>
     <row r="102" spans="1:26" ht="15.75" customHeight="1">
       <c r="A102" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B102" s="37"/>
+      <c r="C102" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A103" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D103" s="5"/>
+    </row>
+    <row r="104" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A104" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="50" t="s">
+      <c r="B104" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C104" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A103" s="38" t="s">
+      <c r="D104" s="5"/>
+    </row>
+    <row r="105" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A105" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="40"/>
-      <c r="C103" s="40" t="s">
+      <c r="B105" s="40"/>
+      <c r="C105" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D105" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A104" s="62" t="s">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A106" s="37" t="s">
         <v>733</v>
       </c>
-      <c r="B104" s="48" t="s">
+      <c r="B106" s="48" t="s">
         <v>734</v>
       </c>
-      <c r="C104" s="62" t="s">
+      <c r="C106" s="37" t="s">
         <v>735</v>
       </c>
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A105" s="30" t="s">
+      <c r="D106" s="5"/>
+    </row>
+    <row r="107" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A107" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30" t="s">
+      <c r="B107" s="30"/>
+      <c r="C107" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A106" s="30" t="s">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A108" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="30" t="s">
+      <c r="B108" s="3"/>
+      <c r="C108" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A107" s="31" t="s">
-        <v>541</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="C107" s="31" t="s">
-        <v>543</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A108" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="B108" s="39"/>
-      <c r="C108" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1">
       <c r="A109" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>543</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A110" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B110" s="39"/>
+      <c r="C110" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A111" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="19"/>
-      <c r="C109" s="31" t="s">
+      <c r="B111" s="19"/>
+      <c r="C111" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D111" s="14" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A110" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C110" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A111" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="B111" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="C111" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:26" ht="15.75" customHeight="1">
       <c r="A112" s="30" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C112" s="30" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1">
       <c r="A113" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B113" s="30"/>
+        <v>246</v>
+      </c>
+      <c r="B113" s="48" t="s">
+        <v>247</v>
+      </c>
       <c r="C113" s="30" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>599</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
       <c r="A114" s="30" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
       <c r="A115" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B115" s="48" t="s">
-        <v>496</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B115" s="30"/>
       <c r="C115" s="30" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>497</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
       <c r="A116" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="B116" s="48"/>
+        <v>256</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="C116" s="30" t="s">
-        <v>635</v>
+        <v>258</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>636</v>
+        <v>259</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1">
       <c r="A117" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="B117" s="48" t="s">
+        <v>496</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>265</v>
+        <v>497</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
       <c r="A118" s="30" t="s">
-        <v>637</v>
-      </c>
-      <c r="B118" s="3"/>
+        <v>634</v>
+      </c>
+      <c r="B118" s="48"/>
       <c r="C118" s="30" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
       <c r="A119" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C119" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A120" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="B120" s="3"/>
+      <c r="C120" s="30" t="s">
+        <v>670</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A121" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="30" t="s">
+      <c r="B121" s="3"/>
+      <c r="C121" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>640</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A120" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="B120" s="19"/>
-      <c r="C120" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="51" t="s">
-        <v>545</v>
-      </c>
-      <c r="B121" s="27"/>
-      <c r="C121" s="51" t="s">
-        <v>546</v>
-      </c>
-      <c r="D121" s="28" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1">
       <c r="A122" s="31" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="31" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="31" t="s">
-        <v>728</v>
-      </c>
-      <c r="B123" s="60" t="s">
-        <v>730</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>729</v>
-      </c>
-      <c r="D123" s="14"/>
+      <c r="A123" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="B123" s="27"/>
+      <c r="C123" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="D123" s="28" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1">
       <c r="A124" s="31" t="s">
-        <v>641</v>
+        <v>269</v>
       </c>
       <c r="B124" s="19"/>
       <c r="C124" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A125" s="31" t="s">
+        <v>728</v>
+      </c>
+      <c r="B125" s="60" t="s">
+        <v>730</v>
+      </c>
+      <c r="C125" s="31" t="s">
+        <v>729</v>
+      </c>
+      <c r="D125" s="14"/>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A126" s="31" t="s">
+        <v>641</v>
+      </c>
+      <c r="B126" s="19"/>
+      <c r="C126" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="D124" s="14" t="s">
+      <c r="D126" s="14" t="s">
         <v>700</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C125" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="C126" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1">
       <c r="A127" s="16" t="s">
-        <v>647</v>
+        <v>272</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>650</v>
+        <v>273</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>648</v>
+        <v>274</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>649</v>
+        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1">
       <c r="A128" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="B128" s="4"/>
+        <v>618</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>620</v>
+      </c>
       <c r="C128" s="16" t="s">
-        <v>675</v>
+        <v>619</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>691</v>
+        <v>621</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1">
       <c r="A129" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A130" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A131" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="16" t="s">
+      <c r="B131" s="4"/>
+      <c r="C131" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D131" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B130" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C130" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="30" t="s">
-        <v>727</v>
-      </c>
-      <c r="B131" s="35"/>
-      <c r="C131" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="D131" s="2"/>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1">
       <c r="A132" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
+      </c>
+      <c r="B132" s="35" t="s">
+        <v>280</v>
       </c>
       <c r="C132" s="30" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="B133" s="20"/>
-      <c r="C133" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>288</v>
-      </c>
+      <c r="A133" s="30" t="s">
+        <v>727</v>
+      </c>
+      <c r="B133" s="35"/>
+      <c r="C133" s="30" t="s">
+        <v>726</v>
+      </c>
+      <c r="D133" s="2"/>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1">
       <c r="A134" s="30" t="s">
-        <v>468</v>
+        <v>283</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="C134" s="30" t="s">
-        <v>468</v>
+        <v>285</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>470</v>
+        <v>286</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B135" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C135" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>180</v>
+      <c r="A135" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" s="20"/>
+      <c r="C135" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1">
       <c r="A136" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C136" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A137" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B137" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C137" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A138" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="B138" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C136" s="30" t="s">
+      <c r="C138" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="31" t="s">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B139" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C137" s="31" t="s">
+      <c r="C139" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D139" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="51" t="s">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A140" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B138" s="29"/>
-      <c r="C138" s="51" t="s">
+      <c r="B140" s="29"/>
+      <c r="C140" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="D138" s="28" t="s">
+      <c r="D140" s="28" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B139" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C139" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1">
       <c r="A141" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
+      </c>
+      <c r="B141" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C141" s="30" t="s">
+        <v>299</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>601</v>
+        <v>300</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
       <c r="A142" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A143" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A144" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B144" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C142" s="30" t="s">
+      <c r="C144" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D144" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="16" t="s">
+    <row r="145" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A145" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B145" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C143" s="16" t="s">
+      <c r="C145" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="D143" s="33" t="s">
+      <c r="D145" s="33" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A144" s="16" t="s">
+    <row r="146" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A146" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B144" s="4"/>
-      <c r="C144" s="16" t="s">
+      <c r="B146" s="4"/>
+      <c r="C146" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D146" s="5" t="s">
         <v>605</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B145" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C145" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C146" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
       <c r="A147" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="B147" s="48" t="s">
-        <v>721</v>
+        <v>315</v>
+      </c>
+      <c r="B147" s="35" t="s">
+        <v>316</v>
       </c>
       <c r="C147" s="30" t="s">
-        <v>720</v>
-      </c>
-      <c r="D147" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
       <c r="A148" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C148" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A149" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="B149" s="48" t="s">
+        <v>721</v>
+      </c>
+      <c r="C149" s="30" t="s">
+        <v>720</v>
+      </c>
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A150" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="35" t="s">
+      <c r="B150" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="C148" s="30" t="s">
+      <c r="C150" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D150" s="2" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="30" customHeight="1">
-      <c r="A150" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B150" s="5"/>
-      <c r="C150" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="16" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="30" customHeight="1">
+      <c r="A152" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="5"/>
+      <c r="C152" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A153" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B153" s="5"/>
+      <c r="C153" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D151" s="5" t="s">
+      <c r="D153" s="5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="30" t="s">
+    <row r="154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A154" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="2"/>
-      <c r="C152" s="30" t="s">
+      <c r="B154" s="2"/>
+      <c r="C154" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D154" s="2" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="38" t="s">
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="39"/>
-      <c r="C153" s="40" t="s">
+      <c r="B155" s="39"/>
+      <c r="C155" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="D153" s="11" t="s">
+      <c r="D155" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="16" t="s">
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="5"/>
-      <c r="C154" s="16" t="s">
+      <c r="B156" s="5"/>
+      <c r="C156" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="D154" s="5" t="s">
+      <c r="D156" s="5" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="16" t="s">
+    <row r="157" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A157" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="5"/>
-      <c r="C155" s="16" t="s">
+      <c r="B157" s="5"/>
+      <c r="C157" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D157" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="30" t="s">
+    <row r="158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A158" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="30" t="s">
+      <c r="B158" s="2"/>
+      <c r="C158" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D158" s="2" t="s">
         <v>603</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B157" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="C157" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B158" s="26"/>
-      <c r="C158" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D158" s="14" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
       <c r="A159" s="30" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C159" s="30" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1">
       <c r="A160" s="31" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B160" s="26"/>
       <c r="C160" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D160" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="C161" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A162" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="26"/>
+      <c r="C162" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="D160" s="14" t="s">
+      <c r="D162" s="14" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="31" t="s">
+    <row r="163" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A163" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="B161" s="26"/>
-      <c r="C161" s="31" t="s">
+      <c r="B163" s="26"/>
+      <c r="C163" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="D161" s="14" t="s">
+      <c r="D163" s="14" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B162" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="C162" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B163" s="35"/>
-      <c r="C163" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1">
       <c r="A164" s="30" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B164" s="35" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C164" s="30" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B165" s="4"/>
-      <c r="C165" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>378</v>
+      <c r="A165" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B165" s="35"/>
+      <c r="C165" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
       <c r="A166" s="30" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B166" s="35" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C166" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B167" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="C167" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>386</v>
+      <c r="A167" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B167" s="4"/>
+      <c r="C167" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
       <c r="A168" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B168" s="3"/>
+        <v>379</v>
+      </c>
+      <c r="B168" s="35" t="s">
+        <v>380</v>
+      </c>
       <c r="C168" s="30" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>584</v>
+        <v>382</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
       <c r="A169" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="B169" s="3"/>
+        <v>383</v>
+      </c>
+      <c r="B169" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C169" s="30" t="s">
-        <v>663</v>
+        <v>385</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>690</v>
+        <v>386</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
       <c r="A170" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="B170" s="3"/>
+      <c r="C170" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A171" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B171" s="3"/>
+      <c r="C171" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A172" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="B170" s="35" t="s">
+      <c r="B172" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="C170" s="30" t="s">
+      <c r="C172" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="D170" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="44" t="s">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A173" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="B171" s="59" t="s">
+      <c r="B173" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="C171" s="7" t="s">
+      <c r="C173" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D171" s="7" t="s">
+      <c r="D173" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="38" t="s">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A174" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="B172" s="39"/>
-      <c r="C172" s="40" t="s">
+      <c r="B174" s="39"/>
+      <c r="C174" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="D172" s="11" t="s">
+      <c r="D174" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="31" t="s">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A175" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B175" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C173" s="31" t="s">
+      <c r="C175" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="D173" s="6" t="s">
+      <c r="D175" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="30" t="s">
+    <row r="176" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A176" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="B174" s="3"/>
-      <c r="C174" s="30" t="s">
+      <c r="B176" s="3"/>
+      <c r="C176" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="D176" s="2" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="52" t="s">
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="52" t="s">
         <v>403</v>
       </c>
-      <c r="B175" s="53" t="s">
+      <c r="B177" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="C175" s="54" t="s">
+      <c r="C177" s="54" t="s">
         <v>405</v>
       </c>
-      <c r="D175" s="21" t="s">
+      <c r="D177" s="21" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="52" t="s">
+    <row r="178" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A178" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B176" s="39"/>
-      <c r="C176" s="54" t="s">
+      <c r="B178" s="39"/>
+      <c r="C178" s="54" t="s">
         <v>408</v>
       </c>
-      <c r="D176" s="21" t="s">
+      <c r="D178" s="21" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="55" t="s">
+    <row r="179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A179" s="55" t="s">
         <v>409</v>
       </c>
-      <c r="B177" s="4"/>
-      <c r="C177" s="55" t="s">
+      <c r="B179" s="4"/>
+      <c r="C179" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="D177" s="9" t="s">
+      <c r="D179" s="9" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B178" s="2"/>
-      <c r="C178" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B179" s="2"/>
-      <c r="C179" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
       <c r="A180" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>416</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="B180" s="2"/>
       <c r="C180" s="30" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>418</v>
+        <v>587</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="B181" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="C181" s="56" t="s">
-        <v>421</v>
+      <c r="A181" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="B181" s="2"/>
+      <c r="C181" s="30" t="s">
+        <v>414</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>422</v>
+        <v>588</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>423</v>
+        <v>744</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>589</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="D182" s="2"/>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A183" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C183" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D183" s="33" t="s">
-        <v>428</v>
+      <c r="A183" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C183" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A184" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C184" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="D184" s="5" t="s">
-        <v>432</v>
+      <c r="A184" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B184" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C184" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
       <c r="A185" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B185" s="35" t="s">
-        <v>434</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="B185" s="2"/>
       <c r="C185" s="30" t="s">
-        <v>583</v>
+        <v>424</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>435</v>
+        <v>589</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C186" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>439</v>
+      <c r="A186" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D186" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C187" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>443</v>
+      <c r="A187" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1">
       <c r="A188" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B188" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="B188" s="35" t="s">
+        <v>434</v>
+      </c>
       <c r="C188" s="30" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>590</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
       <c r="A189" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C189" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A190" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C190" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A191" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B191" s="2"/>
+      <c r="C191" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A192" s="30" t="s">
         <v>446</v>
       </c>
-      <c r="B189" s="2"/>
-      <c r="C189" s="30" t="s">
+      <c r="B192" s="2"/>
+      <c r="C192" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="D192" s="2" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B190" s="14"/>
-      <c r="C190" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D190" s="14" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B191" s="14"/>
-      <c r="C191" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="D191" s="14" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="B192" s="14"/>
-      <c r="C192" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="D192" s="14" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1">
       <c r="A193" s="31" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B193" s="14"/>
       <c r="C193" s="31" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>561</v>
+        <v>664</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1">
       <c r="A194" s="31" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B194" s="14"/>
       <c r="C194" s="31" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
       <c r="A195" s="31" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="B195" s="14"/>
       <c r="C195" s="31" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="B196" s="14"/>
+      <c r="C196" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A197" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="B197" s="14"/>
+      <c r="C197" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="D197" s="14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A198" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B198" s="14"/>
+      <c r="C198" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D198" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A199" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B196" s="48" t="s">
+      <c r="B199" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="C196" s="31" t="s">
+      <c r="C199" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="D196" s="14" t="s">
+      <c r="D199" s="14" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A197" s="16" t="s">
+    <row r="200" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A200" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B200" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C197" s="16" t="s">
+      <c r="C200" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="D197" s="5" t="s">
+      <c r="D200" s="5" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A198" s="16" t="s">
+    <row r="201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A201" s="16" t="s">
         <v>731</v>
       </c>
-      <c r="B198" s="4"/>
-      <c r="C198" s="16" t="s">
+      <c r="B201" s="4"/>
+      <c r="C201" s="16" t="s">
         <v>732</v>
       </c>
-      <c r="D198" s="5"/>
-    </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A199" s="16" t="s">
+      <c r="D201" s="5"/>
+    </row>
+    <row r="202" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A202" s="16" t="s">
         <v>645</v>
       </c>
-      <c r="B199" s="4"/>
-      <c r="C199" s="16" t="s">
+      <c r="B202" s="4"/>
+      <c r="C202" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D199" s="5" t="s">
+      <c r="D202" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A200" s="30" t="s">
+    <row r="203" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A203" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B203" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C200" s="30" t="s">
+      <c r="C203" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="D203" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A201" s="7" t="s">
+    <row r="204" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A204" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B204" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C201" s="7" t="s">
+      <c r="C204" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D201" s="7" t="s">
+      <c r="D204" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A202" s="30" t="s">
+    <row r="205" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A205" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B205" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C202" s="30" t="s">
+      <c r="C205" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="D205" s="2" t="s">
         <v>466</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A203" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="B203" s="20"/>
-      <c r="C203" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A204" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C204" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D204" s="6" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A205" s="31" t="s">
-        <v>571</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="C205" s="31" t="s">
-        <v>573</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1">
       <c r="A206" s="16" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B206" s="20"/>
       <c r="C206" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A207" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C207" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A208" s="31" t="s">
+        <v>571</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="C208" s="31" t="s">
+        <v>573</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A209" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="B209" s="20"/>
+      <c r="C209" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="D206" s="5" t="s">
+      <c r="D209" s="5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A207" s="16" t="s">
+    <row r="210" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A210" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="B207" s="20"/>
-      <c r="C207" s="16" t="s">
+      <c r="B210" s="20"/>
+      <c r="C210" s="16" t="s">
         <v>652</v>
       </c>
-      <c r="D207" s="5" t="s">
+      <c r="D210" s="5" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A208" s="16" t="s">
+    <row r="211" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A211" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B208" s="20" t="s">
+      <c r="B211" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C208" s="16" t="s">
+      <c r="C211" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D208" s="5" t="s">
+      <c r="D211" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="16" t="s">
+    <row r="212" spans="1:4">
+      <c r="A212" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B212" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C209" s="16" t="s">
+      <c r="C212" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D209" s="5" t="s">
+      <c r="D212" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A210" s="30" t="s">
+    <row r="213" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A213" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B213" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C210" s="30" t="s">
+      <c r="C213" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="D213" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A211" s="30" t="s">
+    <row r="214" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A214" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="B211" s="3"/>
-      <c r="C211" s="30" t="s">
+      <c r="B214" s="3"/>
+      <c r="C214" s="30" t="s">
         <v>737</v>
       </c>
-      <c r="D211" s="2"/>
-    </row>
-    <row r="212" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A212" s="2" t="s">
+      <c r="D214" s="2"/>
+    </row>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A215" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B215" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C215" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="D215" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A213" s="2" t="s">
+    <row r="216" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A216" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B213" s="35" t="s">
+      <c r="B216" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C216" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="D216" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A214" s="58" t="s">
+    <row r="217" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A217" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B214" s="6" t="s">
+      <c r="B217" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C214" s="31" t="s">
+      <c r="C217" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D214" s="6" t="s">
+      <c r="D217" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="218" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="219" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="220" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7251,161 +7307,165 @@
     <row r="1142" ht="15.75" customHeight="1"/>
     <row r="1143" ht="15.75" customHeight="1"/>
     <row r="1144" ht="15.75" customHeight="1"/>
+    <row r="1145" ht="15.75" customHeight="1"/>
+    <row r="1146" ht="15.75" customHeight="1"/>
+    <row r="1147" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B209" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D22" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B23" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B26" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B31" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B32" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B33" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D33" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B34" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B35" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B36" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B39" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B43" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B45" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B47" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B50" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B51" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D51" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B52" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B54" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D54" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B55" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B56" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B57" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B62" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B63" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B65" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B66" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B67" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B68" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B69" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B70" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D70" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B71" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B73" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B76" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D79" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B84" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D84" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B85" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D85" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B88" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B90" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D90" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B92" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B93" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B98" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D98" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B99" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B101" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B102" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B110" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B111" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B112" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B114" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B125" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B130" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B132" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B135" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B136" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B137" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D137" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B139" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B142" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B143" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D143" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B145" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B146" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B148" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B157" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B159" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B162" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B164" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B166" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B167" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B170" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B171" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B173" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D173" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B175" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B180" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B181" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B183" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D183" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B184" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B185" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B186" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B187" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B197" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B200" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B201" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B202" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B134" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B210" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B64" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B212" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B213" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B91" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B115" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B196" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
-    <hyperlink ref="D6" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
-    <hyperlink ref="B8" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
-    <hyperlink ref="D8" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B37" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D37" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B74" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D74" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B82" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D82" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B86" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D86" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B87" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D87" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B107" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B204" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D204" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B205" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D205" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B214" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D214" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B21" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B16" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B58" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B24" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
-    <hyperlink ref="B6" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
+    <hyperlink ref="B13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B212" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D23" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B24" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B27" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B28" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B32" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B33" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B34" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D34" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B35" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B36" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B37" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B41" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B42" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B47" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B49" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B52" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B53" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D53" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B54" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B56" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D56" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B57" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B58" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B59" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B61" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B62" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B63" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B64" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B65" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B67" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B68" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B69" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B70" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B71" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B72" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D72" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B73" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B75" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B78" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D81" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B86" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D86" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B87" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D87" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B90" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B92" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D92" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B94" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B95" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B100" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D100" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B101" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B103" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B104" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B112" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B113" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B114" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B116" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B127" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B132" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B134" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B137" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B138" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B139" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D139" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B141" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B144" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B145" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D145" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B147" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B148" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B150" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B159" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B161" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B164" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B166" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B168" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B169" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B172" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B173" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B175" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D175" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B177" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B183" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B184" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B186" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D186" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B187" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B188" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B189" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B190" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B200" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B203" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B204" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B205" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B136" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B213" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B66" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B215" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B216" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B93" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B117" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B199" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
+    <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
+    <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
+    <hyperlink ref="B39" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D39" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B76" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D76" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B84" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D84" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B88" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D88" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B89" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D89" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B109" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B207" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D207" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B208" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D208" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B217" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D217" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B22" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B17" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B60" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B25" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B7" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="B3" r:id="rId139" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
-    <hyperlink ref="B80" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B79" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B77" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
-    <hyperlink ref="B53" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
-    <hyperlink ref="B46" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B147" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
-    <hyperlink ref="B78" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B123" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B104" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B82" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B81" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B79" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B55" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B48" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B149" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B80" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B125" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B106" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B5" r:id="rId149" tooltip="https://d-nb.info/gnd/1277681929" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId149"/>
+    <tablePart r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB02B54-7265-D54B-96E7-38218984E15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B358C5-F7F3-6343-8999-AF145A88F86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="747">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2847,6 +2847,9 @@
   </si>
   <si>
     <t>Bosnienausschuss</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Balkanbund" ref="https://d-nb.info/gnd/1277681929"&gt;</t>
   </si>
 </sst>
 </file>
@@ -3562,7 +3565,9 @@
       <c r="C5" s="30" t="s">
         <v>738</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="14" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="31" t="s">
@@ -7460,7 +7465,7 @@
     <hyperlink ref="B80" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
     <hyperlink ref="B125" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
     <hyperlink ref="B106" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
-    <hyperlink ref="B5" r:id="rId149" tooltip="https://d-nb.info/gnd/1277681929" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
+    <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B358C5-F7F3-6343-8999-AF145A88F86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2513D0D2-D3AE-9245-B709-6D05581784D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="752">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2850,6 +2850,21 @@
   </si>
   <si>
     <t>&lt;orgName key="Balkanbund" ref="https://d-nb.info/gnd/1277681929"&gt;</t>
+  </si>
+  <si>
+    <t>Fichtenhain</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1032216875</t>
+  </si>
+  <si>
+    <t>Rheinische Provinzial-Fürsorgeerziehungsanstalt Fichtenhain</t>
+  </si>
+  <si>
+    <t>Presse/Dan (kulturno politički časopis)</t>
+  </si>
+  <si>
+    <t>Dan</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3191,6 +3206,7 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3286,7 +3302,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D211" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D213" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3495,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1147"/>
+  <dimension ref="A1:Z1149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -4837,1556 +4853,1576 @@
     </row>
     <row r="99" spans="1:26">
       <c r="A99" s="16" t="s">
-        <v>614</v>
+        <v>750</v>
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="D99" s="5"/>
+    </row>
+    <row r="100" spans="1:26">
+      <c r="A100" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="D99" s="5" t="s">
+      <c r="D100" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="100" spans="1:26">
-      <c r="A100" s="31" t="s">
+    <row r="101" spans="1:26">
+      <c r="A101" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B101" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="31" t="s">
+      <c r="C101" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D101" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A101" s="49" t="s">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A102" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B102" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C101" s="49" t="s">
+      <c r="C102" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D102" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="13"/>
-      <c r="L101" s="13"/>
-      <c r="M101" s="13"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="13"/>
-      <c r="P101" s="13"/>
-      <c r="Q101" s="13"/>
-      <c r="R101" s="13"/>
-      <c r="S101" s="13"/>
-      <c r="T101" s="13"/>
-      <c r="U101" s="13"/>
-      <c r="V101" s="13"/>
-      <c r="W101" s="13"/>
-      <c r="X101" s="13"/>
-      <c r="Y101" s="13"/>
-      <c r="Z101" s="13"/>
-    </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A102" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="B102" s="37"/>
-      <c r="C102" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>222</v>
-      </c>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+      <c r="K102" s="13"/>
+      <c r="L102" s="13"/>
+      <c r="M102" s="13"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="13"/>
+      <c r="P102" s="13"/>
+      <c r="Q102" s="13"/>
+      <c r="R102" s="13"/>
+      <c r="S102" s="13"/>
+      <c r="T102" s="13"/>
+      <c r="U102" s="13"/>
+      <c r="V102" s="13"/>
+      <c r="W102" s="13"/>
+      <c r="X102" s="13"/>
+      <c r="Y102" s="13"/>
+      <c r="Z102" s="13"/>
     </row>
     <row r="103" spans="1:26" ht="15.75" customHeight="1">
       <c r="A103" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" s="50" t="s">
-        <v>224</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B103" s="37"/>
       <c r="C103" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="D103" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1">
       <c r="A104" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B104" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D104" s="5"/>
+    </row>
+    <row r="105" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A105" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="B104" s="50" t="s">
+      <c r="B105" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C105" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A105" s="38" t="s">
+      <c r="D105" s="5"/>
+    </row>
+    <row r="106" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A106" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="40"/>
-      <c r="C105" s="40" t="s">
+      <c r="B106" s="40"/>
+      <c r="C106" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D105" s="5" t="s">
+      <c r="D106" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A106" s="37" t="s">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A107" s="37" t="s">
         <v>733</v>
       </c>
-      <c r="B106" s="48" t="s">
+      <c r="B107" s="48" t="s">
         <v>734</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C107" s="37" t="s">
         <v>735</v>
       </c>
-      <c r="D106" s="5"/>
-    </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A107" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="B107" s="30"/>
-      <c r="C107" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>598</v>
-      </c>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1">
       <c r="A108" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A109" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="30" t="s">
+      <c r="B109" s="3"/>
+      <c r="C109" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A109" s="31" t="s">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A110" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B110" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="C109" s="31" t="s">
+      <c r="C110" s="31" t="s">
         <v>543</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D110" s="14" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A110" s="38" t="s">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A111" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B110" s="39"/>
-      <c r="C110" s="40" t="s">
+      <c r="B111" s="39"/>
+      <c r="C111" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D111" s="11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A111" s="31" t="s">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A112" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="B111" s="19"/>
-      <c r="C111" s="31" t="s">
+      <c r="B112" s="19"/>
+      <c r="C112" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D111" s="14" t="s">
+      <c r="D112" s="14" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A112" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C112" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1">
       <c r="A113" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="B113" s="48" t="s">
-        <v>247</v>
+        <v>242</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="C113" s="30" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1">
       <c r="A114" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
+      </c>
+      <c r="B114" s="48" t="s">
+        <v>247</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
       <c r="A115" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B115" s="30"/>
+        <v>250</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="C115" s="30" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>599</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
       <c r="A116" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B116" s="30"/>
       <c r="C116" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>259</v>
+        <v>599</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1">
       <c r="A117" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B117" s="48" t="s">
-        <v>496</v>
+        <v>256</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>497</v>
+        <v>259</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
       <c r="A118" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="B118" s="48"/>
+        <v>260</v>
+      </c>
+      <c r="B118" s="48" t="s">
+        <v>496</v>
+      </c>
       <c r="C118" s="30" t="s">
-        <v>635</v>
+        <v>261</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>636</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
       <c r="A119" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="B119" s="48"/>
       <c r="C119" s="30" t="s">
-        <v>264</v>
+        <v>635</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>265</v>
+        <v>636</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1">
       <c r="A120" s="30" t="s">
-        <v>637</v>
-      </c>
-      <c r="B120" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="C120" s="30" t="s">
-        <v>670</v>
+        <v>264</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>638</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1">
       <c r="A121" s="30" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="30" t="s">
+        <v>670</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A122" s="30" t="s">
+        <v>639</v>
+      </c>
+      <c r="B122" s="3"/>
+      <c r="C122" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="31" t="s">
+    <row r="123" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A123" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="B122" s="19"/>
-      <c r="C122" s="31" t="s">
+      <c r="B123" s="19"/>
+      <c r="C123" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D123" s="14" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="51" t="s">
+    <row r="124" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A124" s="51" t="s">
         <v>545</v>
       </c>
-      <c r="B123" s="27"/>
-      <c r="C123" s="51" t="s">
+      <c r="B124" s="27"/>
+      <c r="C124" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="D123" s="28" t="s">
+      <c r="D124" s="28" t="s">
         <v>547</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A124" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="B124" s="19"/>
-      <c r="C124" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1">
       <c r="A125" s="31" t="s">
-        <v>728</v>
-      </c>
-      <c r="B125" s="60" t="s">
-        <v>730</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="B125" s="19"/>
       <c r="C125" s="31" t="s">
-        <v>729</v>
-      </c>
-      <c r="D125" s="14"/>
+        <v>270</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1">
       <c r="A126" s="31" t="s">
+        <v>728</v>
+      </c>
+      <c r="B126" s="60" t="s">
+        <v>730</v>
+      </c>
+      <c r="C126" s="31" t="s">
+        <v>729</v>
+      </c>
+      <c r="D126" s="14"/>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A127" s="31" t="s">
         <v>641</v>
       </c>
-      <c r="B126" s="19"/>
-      <c r="C126" s="31" t="s">
+      <c r="B127" s="19"/>
+      <c r="C127" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="D126" s="14" t="s">
+      <c r="D127" s="14" t="s">
         <v>700</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C127" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1">
       <c r="A128" s="16" t="s">
-        <v>618</v>
+        <v>272</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>620</v>
+        <v>273</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>619</v>
+        <v>274</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>621</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1">
       <c r="A129" s="16" t="s">
-        <v>647</v>
+        <v>618</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>648</v>
+        <v>619</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>649</v>
+        <v>621</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1">
       <c r="A130" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="B130" s="4"/>
+        <v>647</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>650</v>
+      </c>
       <c r="C130" s="16" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>691</v>
+        <v>649</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1">
       <c r="A131" s="16" t="s">
-        <v>276</v>
+        <v>674</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A132" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D132" s="5" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B132" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C132" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1">
       <c r="A133" s="30" t="s">
-        <v>727</v>
-      </c>
-      <c r="B133" s="35"/>
+        <v>279</v>
+      </c>
+      <c r="B133" s="35" t="s">
+        <v>280</v>
+      </c>
       <c r="C133" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="D133" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1">
       <c r="A134" s="30" t="s">
+        <v>727</v>
+      </c>
+      <c r="B134" s="35"/>
+      <c r="C134" s="30" t="s">
+        <v>726</v>
+      </c>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A135" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B135" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C134" s="30" t="s">
+      <c r="C135" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D135" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="16" t="s">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A136" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B135" s="20"/>
-      <c r="C135" s="16" t="s">
+      <c r="B136" s="20"/>
+      <c r="C136" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D136" s="5" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A136" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C136" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1">
       <c r="A137" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B137" s="35" t="s">
-        <v>178</v>
+        <v>468</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="C137" s="30" t="s">
-        <v>179</v>
+        <v>468</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>180</v>
+        <v>470</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1">
       <c r="A138" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B138" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C138" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B138" s="22" t="s">
+      <c r="B139" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C138" s="30" t="s">
+      <c r="C139" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D139" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="31" t="s">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A140" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B140" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C139" s="31" t="s">
+      <c r="C140" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D140" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="51" t="s">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A141" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B140" s="29"/>
-      <c r="C140" s="51" t="s">
+      <c r="B141" s="29"/>
+      <c r="C141" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="D140" s="28" t="s">
+      <c r="D141" s="28" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C141" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
       <c r="A142" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
+      </c>
+      <c r="B142" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C142" s="30" t="s">
+        <v>299</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1">
       <c r="A143" s="30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
       <c r="A144" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A145" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B145" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C144" s="30" t="s">
+      <c r="C145" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D145" s="2" t="s">
         <v>308</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C145" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="D145" s="33" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
       <c r="A146" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D146" s="33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A147" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="16" t="s">
+      <c r="B147" s="4"/>
+      <c r="C147" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D147" s="5" t="s">
         <v>605</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B147" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C147" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
       <c r="A148" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
+      </c>
+      <c r="B148" s="35" t="s">
+        <v>316</v>
       </c>
       <c r="C148" s="30" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
       <c r="A149" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="B149" s="48" t="s">
-        <v>721</v>
+        <v>319</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="C149" s="30" t="s">
-        <v>720</v>
-      </c>
-      <c r="D149" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
       <c r="A150" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="B150" s="48" t="s">
+        <v>721</v>
+      </c>
+      <c r="C150" s="30" t="s">
+        <v>720</v>
+      </c>
+      <c r="D150" s="2"/>
+    </row>
+    <row r="151" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A151" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B150" s="35" t="s">
+      <c r="B151" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="C150" s="30" t="s">
+      <c r="C151" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A151" s="16" t="s">
+    <row r="152" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A152" s="16" t="s">
         <v>327</v>
-      </c>
-      <c r="B151" s="5"/>
-      <c r="C151" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="30" customHeight="1">
-      <c r="A152" s="16" t="s">
-        <v>330</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="16" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="16" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A154" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="5"/>
+      <c r="C154" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D153" s="5" t="s">
+      <c r="D154" s="5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="30" t="s">
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B154" s="2"/>
-      <c r="C154" s="30" t="s">
+      <c r="B155" s="2"/>
+      <c r="C155" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D155" s="2" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="38" t="s">
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B155" s="39"/>
-      <c r="C155" s="40" t="s">
+      <c r="B156" s="39"/>
+      <c r="C156" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="D155" s="11" t="s">
+      <c r="D156" s="11" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
       <c r="A157" s="16" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A158" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B158" s="5"/>
+      <c r="C158" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="D157" s="5" t="s">
+      <c r="D158" s="5" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B158" s="2"/>
-      <c r="C158" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
       <c r="A159" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B159" s="2"/>
+      <c r="C159" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A160" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="B159" s="35" t="s">
+      <c r="B160" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="C159" s="30" t="s">
+      <c r="C160" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D160" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="31" t="s">
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="B160" s="26"/>
-      <c r="C160" s="31" t="s">
+      <c r="B161" s="26"/>
+      <c r="C161" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="D160" s="14" t="s">
+      <c r="D161" s="14" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="30" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A162" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="35" t="s">
+      <c r="B162" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="C161" s="30" t="s">
+      <c r="C162" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D162" s="2" t="s">
         <v>359</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B162" s="26"/>
-      <c r="C162" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="D162" s="14" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
       <c r="A163" s="31" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B163" s="26"/>
       <c r="C163" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D163" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A164" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="26"/>
+      <c r="C164" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="D163" s="14" t="s">
+      <c r="D164" s="14" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B164" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="C164" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1">
       <c r="A165" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B165" s="35"/>
+        <v>365</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>366</v>
+      </c>
       <c r="C165" s="30" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
       <c r="A166" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" s="35"/>
+      <c r="C166" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A167" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B166" s="35" t="s">
+      <c r="B167" s="35" t="s">
         <v>373</v>
       </c>
-      <c r="C166" s="30" t="s">
+      <c r="C167" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="16" t="s">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A168" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="B167" s="4"/>
-      <c r="C167" s="16" t="s">
+      <c r="B168" s="4"/>
+      <c r="C168" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="D168" s="5" t="s">
         <v>378</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B168" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="C168" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
       <c r="A169" s="30" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B169" s="35" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
       <c r="A170" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B170" s="3"/>
+        <v>383</v>
+      </c>
+      <c r="B170" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C170" s="30" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>584</v>
+        <v>386</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
       <c r="A171" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="30" t="s">
-        <v>663</v>
+        <v>387</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>690</v>
+        <v>584</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
       <c r="A172" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B172" s="3"/>
+      <c r="C172" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A173" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="B172" s="35" t="s">
+      <c r="B173" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="30" t="s">
+      <c r="C173" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D173" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="44" t="s">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A174" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="B173" s="59" t="s">
+      <c r="B174" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="C173" s="7" t="s">
+      <c r="C174" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D173" s="7" t="s">
+      <c r="D174" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="38" t="s">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A175" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="B174" s="39"/>
-      <c r="C174" s="40" t="s">
+      <c r="B175" s="39"/>
+      <c r="C175" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="D174" s="11" t="s">
+      <c r="D175" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="31" t="s">
+    <row r="176" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A176" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B176" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C175" s="31" t="s">
+      <c r="C176" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="D175" s="6" t="s">
+      <c r="D176" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="30" t="s">
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="B176" s="3"/>
-      <c r="C176" s="30" t="s">
+      <c r="B177" s="3"/>
+      <c r="C177" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="D177" s="2" t="s">
         <v>604</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B177" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="C177" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="D177" s="21" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1">
       <c r="A178" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B178" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C178" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D178" s="21" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A179" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B178" s="39"/>
-      <c r="C178" s="54" t="s">
+      <c r="B179" s="39"/>
+      <c r="C179" s="54" t="s">
         <v>408</v>
       </c>
-      <c r="D178" s="21" t="s">
+      <c r="D179" s="21" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="55" t="s">
+    <row r="180" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A180" s="55" t="s">
         <v>409</v>
       </c>
-      <c r="B179" s="4"/>
-      <c r="C179" s="55" t="s">
+      <c r="B180" s="4"/>
+      <c r="C180" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="D179" s="9" t="s">
+      <c r="D180" s="9" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A180" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B180" s="2"/>
-      <c r="C180" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
       <c r="A181" s="30" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="30" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>744</v>
+        <v>413</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="30" t="s">
-        <v>745</v>
-      </c>
-      <c r="D182" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
       <c r="A183" s="30" t="s">
+        <v>744</v>
+      </c>
+      <c r="B183" s="2"/>
+      <c r="C183" s="30" t="s">
+        <v>745</v>
+      </c>
+      <c r="D183" s="2"/>
+    </row>
+    <row r="184" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A184" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B184" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C183" s="30" t="s">
+      <c r="C184" s="30" t="s">
         <v>417</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="D184" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A184" s="56" t="s">
+    <row r="185" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A185" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="B184" s="57" t="s">
+      <c r="B185" s="57" t="s">
         <v>420</v>
       </c>
-      <c r="C184" s="56" t="s">
+      <c r="C185" s="56" t="s">
         <v>421</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="D185" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A185" s="30" t="s">
+    <row r="186" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A186" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="B185" s="2"/>
-      <c r="C185" s="30" t="s">
+      <c r="B186" s="2"/>
+      <c r="C186" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D186" s="2" t="s">
         <v>589</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C186" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D186" s="33" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
       <c r="A187" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D187" s="33" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A188" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B188" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C187" s="16" t="s">
+      <c r="C188" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="D187" s="5" t="s">
+      <c r="D188" s="5" t="s">
         <v>432</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B188" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="C188" s="30" t="s">
-        <v>583</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
       <c r="A189" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
+      </c>
+      <c r="B189" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="C189" s="30" t="s">
-        <v>438</v>
+        <v>583</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1">
       <c r="A190" s="30" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C190" s="30" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1">
       <c r="A191" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B191" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>441</v>
+      </c>
       <c r="C191" s="30" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>590</v>
+        <v>443</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1">
       <c r="A192" s="30" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A193" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="B193" s="2"/>
+      <c r="C193" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D192" s="2" t="s">
+      <c r="D193" s="2" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B193" s="14"/>
-      <c r="C193" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D193" s="14" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1">
       <c r="A194" s="31" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B194" s="14"/>
       <c r="C194" s="31" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>555</v>
+        <v>664</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
       <c r="A195" s="31" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B195" s="14"/>
       <c r="C195" s="31" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="31" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B196" s="14"/>
       <c r="C196" s="31" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1">
       <c r="A197" s="31" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B197" s="14"/>
       <c r="C197" s="31" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1">
       <c r="A198" s="31" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B198" s="14"/>
       <c r="C198" s="31" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1">
       <c r="A199" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B199" s="14"/>
+      <c r="C199" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D199" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A200" s="31" t="s">
+        <v>749</v>
+      </c>
+      <c r="B200" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="C200" s="31" t="s">
+        <v>747</v>
+      </c>
+      <c r="D200" s="62"/>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A201" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B199" s="48" t="s">
+      <c r="B201" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="C199" s="31" t="s">
+      <c r="C201" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="D199" s="14" t="s">
+      <c r="D201" s="14" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A200" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C200" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D200" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A201" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="B201" s="4"/>
-      <c r="C201" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="D201" s="5"/>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1">
       <c r="A202" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C202" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A203" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="D203" s="5"/>
+    </row>
+    <row r="204" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A204" s="16" t="s">
         <v>645</v>
       </c>
-      <c r="B202" s="4"/>
-      <c r="C202" s="16" t="s">
+      <c r="B204" s="4"/>
+      <c r="C204" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D202" s="5" t="s">
+      <c r="D204" s="5" t="s">
         <v>689</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A203" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C203" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A204" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1">
       <c r="A205" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C205" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A206" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A207" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B207" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C205" s="30" t="s">
+      <c r="C207" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="D207" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A206" s="16" t="s">
+    <row r="208" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A208" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B206" s="20"/>
-      <c r="C206" s="16" t="s">
+      <c r="B208" s="20"/>
+      <c r="C208" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D206" s="5" t="s">
+      <c r="D208" s="5" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A207" s="31" t="s">
+    <row r="209" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A209" s="31" t="s">
         <v>568</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B209" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="C207" s="31" t="s">
+      <c r="C209" s="31" t="s">
         <v>570</v>
       </c>
-      <c r="D207" s="6" t="s">
+      <c r="D209" s="6" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A208" s="31" t="s">
+    <row r="210" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A210" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B210" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C208" s="31" t="s">
+      <c r="C210" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D208" s="6" t="s">
+      <c r="D210" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A209" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B209" s="20"/>
-      <c r="C209" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D209" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A210" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="B210" s="20"/>
-      <c r="C210" s="16" t="s">
-        <v>652</v>
-      </c>
-      <c r="D210" s="5" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1">
       <c r="A211" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="B211" s="20"/>
+      <c r="C211" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A212" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B212" s="20"/>
+      <c r="C212" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A213" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B211" s="20" t="s">
+      <c r="B213" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C211" s="16" t="s">
+      <c r="C213" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D211" s="5" t="s">
+      <c r="D213" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="16" t="s">
+    <row r="214" spans="1:4">
+      <c r="A214" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B214" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C212" s="16" t="s">
+      <c r="C214" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D212" s="5" t="s">
+      <c r="D214" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A213" s="30" t="s">
+    <row r="215" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A215" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B215" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C213" s="30" t="s">
+      <c r="C215" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="D215" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A214" s="30" t="s">
+    <row r="216" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A216" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="B214" s="3"/>
-      <c r="C214" s="30" t="s">
+      <c r="B216" s="3"/>
+      <c r="C216" s="30" t="s">
         <v>737</v>
       </c>
-      <c r="D214" s="2"/>
-    </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A215" s="2" t="s">
+      <c r="D216" s="2"/>
+    </row>
+    <row r="217" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A217" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B217" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C217" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="D217" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A216" s="2" t="s">
+    <row r="218" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A218" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B216" s="35" t="s">
+      <c r="B218" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C218" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="D218" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A217" s="58" t="s">
+    <row r="219" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A219" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="6" t="s">
+      <c r="B219" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C217" s="31" t="s">
+      <c r="C219" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D217" s="6" t="s">
+      <c r="D219" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="220" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="221" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="222" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7315,11 +7351,13 @@
     <row r="1145" ht="15.75" customHeight="1"/>
     <row r="1146" ht="15.75" customHeight="1"/>
     <row r="1147" ht="15.75" customHeight="1"/>
+    <row r="1148" ht="15.75" customHeight="1"/>
+    <row r="1149" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B212" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B214" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -7376,60 +7414,60 @@
     <hyperlink ref="D92" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="B94" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
     <hyperlink ref="B95" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B100" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D100" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B101" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B103" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B104" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B112" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B113" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B114" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B116" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B127" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B132" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B134" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B137" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B138" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B139" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D139" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B141" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B144" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B145" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D145" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B147" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B148" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B150" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B159" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B161" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B164" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B166" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B168" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B169" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B172" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B173" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B175" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D175" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B177" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B183" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B184" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B186" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D186" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B187" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B188" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B189" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B190" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B200" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B203" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B204" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B205" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B136" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B213" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B101" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D101" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B102" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B104" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B105" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B113" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B114" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B115" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B117" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B128" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B133" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B135" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B138" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B139" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B140" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D140" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B142" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B145" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B146" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D146" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B148" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B149" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B151" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B160" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B162" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B165" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B167" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B169" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B170" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B173" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B174" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B176" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D176" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B178" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B184" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B185" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B187" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D187" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B188" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B189" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B190" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B191" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B202" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B205" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B206" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B207" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B137" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B215" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
     <hyperlink ref="B66" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B215" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B216" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B217" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B218" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
     <hyperlink ref="B93" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B117" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B199" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B118" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B201" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
@@ -7443,13 +7481,13 @@
     <hyperlink ref="D88" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
     <hyperlink ref="B89" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
     <hyperlink ref="D89" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B109" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B207" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D207" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B208" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D208" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B217" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D217" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B110" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B209" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D209" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B210" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D210" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B219" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D219" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B22" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
     <hyperlink ref="B17" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
     <hyperlink ref="B60" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
@@ -7461,10 +7499,10 @@
     <hyperlink ref="B79" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
     <hyperlink ref="B55" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
     <hyperlink ref="B48" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B149" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B150" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
     <hyperlink ref="B80" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B125" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B106" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B126" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B107" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
     <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2513D0D2-D3AE-9245-B709-6D05581784D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F93741-AB0B-4148-90AA-EDA82AA2AABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="788">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2762,9 +2762,6 @@
     <t>LandtagBosnien</t>
   </si>
   <si>
-    <t>Nationalmuseum Belgrad</t>
-  </si>
-  <si>
     <t>NationalmuseumBelgrad</t>
   </si>
   <si>
@@ -2865,6 +2862,117 @@
   </si>
   <si>
     <t>Dan</t>
+  </si>
+  <si>
+    <t>Presse/Augsburger Postzeitung</t>
+  </si>
+  <si>
+    <t>AugsburgerPostzeitung</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4565992-8</t>
+  </si>
+  <si>
+    <t>Presse/Wissenschaftliche Mitteilungen aus Bosnien und der Hercegowina</t>
+  </si>
+  <si>
+    <t>MitteilungenBosnien</t>
+  </si>
+  <si>
+    <t>Presse/Corriere della sera</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4208422-2</t>
+  </si>
+  <si>
+    <t>CorriereDellaSera</t>
+  </si>
+  <si>
+    <t>Kurhaus Bad Homburg</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1217662820</t>
+  </si>
+  <si>
+    <t>KurhausHomburg</t>
+  </si>
+  <si>
+    <t>Presse/Le Figaro</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1086695437</t>
+  </si>
+  <si>
+    <t>Figaro</t>
+  </si>
+  <si>
+    <t>Fürstenhof Wiesbaden</t>
+  </si>
+  <si>
+    <t>FuerstenhofFrankfurt</t>
+  </si>
+  <si>
+    <t>Internationale Luftschiffahrt-Ausstellung Frankfurt (ILA)</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/10140329-X</t>
+  </si>
+  <si>
+    <t>Ila</t>
+  </si>
+  <si>
+    <t>Landesbank für Bosnien und Herzegowina</t>
+  </si>
+  <si>
+    <t>LandesbankBosnien</t>
+  </si>
+  <si>
+    <t>Museum/Nationalmuseum Belgrad</t>
+  </si>
+  <si>
+    <t>Museum/Römisch-Germanisches Zentralmuseum</t>
+  </si>
+  <si>
+    <t>RoemischGermanischesMuseum</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4028138-3</t>
+  </si>
+  <si>
+    <t>Museum/Museum Wiesbaden</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/2039331-3</t>
+  </si>
+  <si>
+    <t>MuseumWiesbaden</t>
+  </si>
+  <si>
+    <t>SenckenbergischesMuseum</t>
+  </si>
+  <si>
+    <t>Museum/Senkenberg Naturmuseum</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/2019952-1</t>
+  </si>
+  <si>
+    <t>Palazzo Quirinale</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/5255442-9</t>
+  </si>
+  <si>
+    <t>Quirinal</t>
+  </si>
+  <si>
+    <t>Welby Commission (Royal Commission on the Administration of Expenditure of India)</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/5064574-2</t>
+  </si>
+  <si>
+    <t>RoyalCommission</t>
   </si>
 </sst>
 </file>
@@ -3103,7 +3211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3207,6 +3315,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3302,7 +3411,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D213" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D225" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3511,7 +3620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1149"/>
+  <dimension ref="A1:Z1161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3573,16 +3682,16 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="30" t="s">
+        <v>737</v>
+      </c>
+      <c r="B5" s="48" t="s">
         <v>738</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>739</v>
-      </c>
       <c r="C5" s="30" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3605,7 +3714,7 @@
         <v>503</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>575</v>
@@ -3828,2622 +3937,2758 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A24" s="31" t="s">
+        <v>765</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="31" t="s">
+        <v>766</v>
+      </c>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>608</v>
+        <v>20</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>607</v>
+        <v>22</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>609</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="B26" s="59" t="s">
+        <v>608</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="16" t="s">
         <v>622</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B27" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C27" s="16" t="s">
         <v>624</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="30" t="s">
+    <row r="28" spans="1:4">
+      <c r="A28" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C28" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="C29" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="16" t="s">
-        <v>709</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="16" t="s">
-        <v>740</v>
-      </c>
-      <c r="D30" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="16" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="16" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="D32" s="5"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="31" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B35" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C35" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="30" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C36" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="16">
-      <c r="A36" s="7" t="s">
+    <row r="37" spans="1:4" ht="16">
+      <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D37" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="16" t="s">
+    <row r="38" spans="1:4" ht="16">
+      <c r="A38" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="16" t="s">
+    <row r="40" spans="1:4">
+      <c r="A40" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="16" t="s">
         <v>742</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="16" t="s">
-        <v>743</v>
-      </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>521</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="31" t="s">
-        <v>665</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>667</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>694</v>
-      </c>
+      <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>667</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B43" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C43" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="30" t="s">
+    <row r="44" spans="1:4">
+      <c r="A44" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C44" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A43" s="30" t="s">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A45" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="30" t="s">
+      <c r="B45" s="2"/>
+      <c r="C45" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A44" s="30" t="s">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A46" s="30" t="s">
+        <v>759</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>761</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A47" s="30" t="s">
         <v>668</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C47" s="30" t="s">
         <v>471</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="9" t="s">
+    <row r="48" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A48" s="30" t="s">
+        <v>770</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="30" t="s">
+        <v>771</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B49" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D49" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="9" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="9" t="s">
+      <c r="B50" s="34"/>
+      <c r="C50" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>699</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="30" t="s">
-        <v>714</v>
-      </c>
-      <c r="B48" s="48" t="s">
-        <v>715</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>716</v>
-      </c>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="36"/>
-      <c r="C50" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="30" t="s">
+        <v>714</v>
+      </c>
+      <c r="B52" s="48" t="s">
+        <v>715</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>716</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="36"/>
+      <c r="C54" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30" t="s">
+      <c r="B55" s="30"/>
+      <c r="C55" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="7" t="s">
+    <row r="56" spans="1:4">
+      <c r="A56" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B56" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D56" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="7" t="s">
+    <row r="57" spans="1:4">
+      <c r="A57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D57" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="7" t="s">
+    <row r="58" spans="1:4">
+      <c r="A58" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="7" t="s">
+    <row r="59" spans="1:4">
+      <c r="A59" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="B55" s="48" t="s">
+      <c r="B59" s="48" t="s">
         <v>712</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="37" t="s">
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B60" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C56" s="37" t="s">
+      <c r="C60" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D60" s="10" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B57" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B58" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="B59" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B60" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="38" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C61" s="40" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26">
+      <c r="A65" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26">
+      <c r="A66" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="B66" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="40" t="s">
+      <c r="C66" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="16" t="s">
+    <row r="67" spans="1:26">
+      <c r="A67" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="30" t="s">
+    <row r="68" spans="1:26">
+      <c r="A68" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="B64" s="35" t="s">
+      <c r="B68" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C68" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:26">
-      <c r="A65" s="30" t="s">
+    <row r="69" spans="1:26">
+      <c r="A69" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C69" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A66" s="30" t="s">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A70" s="30" t="s">
         <v>574</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C66" s="30" t="s">
+      <c r="C70" s="30" t="s">
         <v>483</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="67" spans="1:26">
-      <c r="A67" s="30" t="s">
+    <row r="71" spans="1:26">
+      <c r="A71" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="B67" s="48" t="s">
+      <c r="B71" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C71" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="68" spans="1:26">
-      <c r="A68" s="41" t="s">
+    <row r="72" spans="1:26">
+      <c r="A72" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B68" s="42" t="s">
+      <c r="B72" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C68" s="41" t="s">
+      <c r="C72" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D72" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
-      <c r="P68" s="13"/>
-      <c r="Q68" s="13"/>
-      <c r="R68" s="13"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="13"/>
-      <c r="U68" s="13"/>
-      <c r="V68" s="13"/>
-      <c r="W68" s="13"/>
-      <c r="X68" s="13"/>
-      <c r="Y68" s="13"/>
-      <c r="Z68" s="13"/>
-    </row>
-    <row r="69" spans="1:26" ht="16">
-      <c r="A69" s="37" t="s">
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
+      <c r="R72" s="13"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="13"/>
+      <c r="U72" s="13"/>
+      <c r="V72" s="13"/>
+      <c r="W72" s="13"/>
+      <c r="X72" s="13"/>
+      <c r="Y72" s="13"/>
+      <c r="Z72" s="13"/>
+    </row>
+    <row r="73" spans="1:26" ht="16">
+      <c r="A73" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B73" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D73" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="16">
-      <c r="A70" s="37" t="s">
+    <row r="74" spans="1:26" ht="16">
+      <c r="A74" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C74" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D74" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="16">
-      <c r="A71" s="37" t="s">
+    <row r="75" spans="1:26" ht="16">
+      <c r="A75" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B75" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C75" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D75" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:26">
-      <c r="A72" s="16" t="s">
+    <row r="76" spans="1:26">
+      <c r="A76" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B72" s="59" t="s">
+      <c r="B76" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C76" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="D76" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="73" spans="1:26">
-      <c r="A73" s="30" t="s">
+    <row r="77" spans="1:26">
+      <c r="A77" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B73" s="35" t="s">
+      <c r="B77" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="C73" s="30" t="s">
+      <c r="C77" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="74" spans="1:26">
-      <c r="A74" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26">
-      <c r="A75" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26">
-      <c r="A76" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>525</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26">
-      <c r="A77" s="31" t="s">
-        <v>717</v>
-      </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="31" t="s">
-        <v>718</v>
-      </c>
-      <c r="D77" s="6"/>
     </row>
     <row r="78" spans="1:26">
       <c r="A78" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="B78" s="35" t="s">
-        <v>167</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B78" s="3"/>
       <c r="C78" s="30" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>169</v>
+        <v>596</v>
       </c>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="30" t="s">
-        <v>706</v>
-      </c>
-      <c r="B79" s="48" t="s">
-        <v>707</v>
-      </c>
-      <c r="C79" s="30" t="s">
-        <v>708</v>
-      </c>
-      <c r="D79" s="2"/>
+      <c r="A79" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="30" t="s">
-        <v>723</v>
-      </c>
-      <c r="B80" s="48" t="s">
-        <v>724</v>
-      </c>
-      <c r="C80" s="30" t="s">
-        <v>725</v>
-      </c>
-      <c r="D80" s="2"/>
+      <c r="A80" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="B81" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>692</v>
-      </c>
+      <c r="A81" s="31" t="s">
+        <v>772</v>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="31" t="s">
+        <v>717</v>
+      </c>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="A82" s="31" t="s">
+        <v>773</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>774</v>
+      </c>
+      <c r="D82" s="6"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="B83" s="19"/>
+        <v>780</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>781</v>
+      </c>
       <c r="C83" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="D83" s="24" t="s">
-        <v>528</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="D83" s="6"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="B84" s="25" t="s">
-        <v>530</v>
+        <v>776</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>777</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>531</v>
-      </c>
-      <c r="D84" s="26" t="s">
-        <v>532</v>
-      </c>
+        <v>778</v>
+      </c>
+      <c r="D84" s="6"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>534</v>
+      <c r="A85" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>178</v>
+        <v>706</v>
+      </c>
+      <c r="B86" s="48" t="s">
+        <v>707</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D86" s="35" t="s">
-        <v>180</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="D86" s="2"/>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B87" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D87" s="33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="30">
-      <c r="A88" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="B88" s="46" t="s">
-        <v>536</v>
-      </c>
-      <c r="C88" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="30">
-      <c r="A89" s="31" t="s">
-        <v>538</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>540</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>580</v>
+      <c r="A87" s="30" t="s">
+        <v>722</v>
+      </c>
+      <c r="B87" s="48" t="s">
+        <v>723</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>724</v>
+      </c>
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B90" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>186</v>
+      <c r="A90" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="B90" s="19"/>
+      <c r="C90" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="D90" s="24" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>189</v>
+      <c r="A91" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B92" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>193</v>
+      <c r="A92" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B92" s="19"/>
+      <c r="C92" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="D92" s="24" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="B93" s="48" t="s">
-        <v>494</v>
+        <v>177</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="16">
-      <c r="A94" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B94" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C94" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C95" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>206</v>
+        <v>179</v>
+      </c>
+      <c r="D93" s="35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D94" s="33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="30">
+      <c r="A95" s="31" t="s">
+        <v>535</v>
+      </c>
+      <c r="B95" s="46" t="s">
+        <v>536</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="30">
+      <c r="A96" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>540</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="97" spans="1:26">
-      <c r="A97" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B97" s="30"/>
-      <c r="C97" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>597</v>
+      <c r="A97" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B97" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:26">
       <c r="A98" s="16" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="16" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:26">
       <c r="A99" s="16" t="s">
-        <v>750</v>
-      </c>
-      <c r="B99" s="16"/>
+        <v>751</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>753</v>
+      </c>
       <c r="C99" s="16" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D99" s="5"/>
     </row>
     <row r="100" spans="1:26">
       <c r="A100" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26">
+      <c r="A101" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" ht="16">
+      <c r="A102" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26">
+      <c r="A103" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C103" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26">
+      <c r="A104" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26">
+      <c r="A105" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26">
+      <c r="A106" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26">
+      <c r="A107" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="D107" s="5"/>
+    </row>
+    <row r="108" spans="1:26">
+      <c r="A108" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="D108" s="5"/>
+    </row>
+    <row r="109" spans="1:26">
+      <c r="A109" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16" t="s">
+      <c r="B109" s="16"/>
+      <c r="C109" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D109" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="101" spans="1:26">
-      <c r="A101" s="31" t="s">
+    <row r="110" spans="1:26">
+      <c r="A110" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B110" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C110" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D110" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A102" s="49" t="s">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A111" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B111" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C102" s="49" t="s">
+      <c r="C111" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D111" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-      <c r="K102" s="13"/>
-      <c r="L102" s="13"/>
-      <c r="M102" s="13"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="13"/>
-      <c r="P102" s="13"/>
-      <c r="Q102" s="13"/>
-      <c r="R102" s="13"/>
-      <c r="S102" s="13"/>
-      <c r="T102" s="13"/>
-      <c r="U102" s="13"/>
-      <c r="V102" s="13"/>
-      <c r="W102" s="13"/>
-      <c r="X102" s="13"/>
-      <c r="Y102" s="13"/>
-      <c r="Z102" s="13"/>
-    </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A103" s="37" t="s">
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="13"/>
+      <c r="N111" s="13"/>
+      <c r="O111" s="13"/>
+      <c r="P111" s="13"/>
+      <c r="Q111" s="13"/>
+      <c r="R111" s="13"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="13"/>
+      <c r="U111" s="13"/>
+      <c r="V111" s="13"/>
+      <c r="W111" s="13"/>
+      <c r="X111" s="13"/>
+      <c r="Y111" s="13"/>
+      <c r="Z111" s="13"/>
+    </row>
+    <row r="112" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A112" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="B103" s="37"/>
-      <c r="C103" s="37" t="s">
+      <c r="B112" s="37"/>
+      <c r="C112" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="D112" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A104" s="37" t="s">
+    <row r="113" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A113" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="B104" s="50" t="s">
+      <c r="B113" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C113" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="D104" s="5"/>
-    </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A105" s="37" t="s">
+      <c r="D113" s="5"/>
+    </row>
+    <row r="114" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A114" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="B105" s="50" t="s">
+      <c r="B114" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C114" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D105" s="5"/>
-    </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A106" s="38" t="s">
+      <c r="D114" s="5"/>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A115" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B106" s="40"/>
-      <c r="C106" s="40" t="s">
+      <c r="B115" s="40"/>
+      <c r="C115" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D115" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A107" s="37" t="s">
+    <row r="116" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A116" s="63" t="s">
+        <v>762</v>
+      </c>
+      <c r="B116" s="63" t="s">
+        <v>763</v>
+      </c>
+      <c r="C116" s="63" t="s">
+        <v>764</v>
+      </c>
+      <c r="D116" s="5"/>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A117" s="37" t="s">
+        <v>732</v>
+      </c>
+      <c r="B117" s="48" t="s">
         <v>733</v>
       </c>
-      <c r="B107" s="48" t="s">
+      <c r="C117" s="37" t="s">
         <v>734</v>
       </c>
-      <c r="C107" s="37" t="s">
-        <v>735</v>
-      </c>
-      <c r="D107" s="5"/>
-    </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A108" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="B108" s="30"/>
-      <c r="C108" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A109" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A110" s="31" t="s">
-        <v>541</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="C110" s="31" t="s">
-        <v>543</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A111" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="B111" s="39"/>
-      <c r="C111" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A112" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A113" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C113" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A114" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="B114" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="C114" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A115" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C115" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A116" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B116" s="30"/>
-      <c r="C116" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A117" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C117" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>259</v>
-      </c>
+      <c r="D117" s="5"/>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1">
       <c r="A118" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B118" s="48" t="s">
-        <v>496</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="B118" s="30"/>
       <c r="C118" s="30" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>497</v>
+        <v>598</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1">
       <c r="A119" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" s="3"/>
+      <c r="C119" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A120" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C120" s="31" t="s">
+        <v>543</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A121" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B121" s="39"/>
+      <c r="C121" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A122" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B122" s="19"/>
+      <c r="C122" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="D122" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A123" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A124" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A125" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C125" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A126" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A127" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A128" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B128" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="C128" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A129" s="30" t="s">
         <v>634</v>
       </c>
-      <c r="B119" s="48"/>
-      <c r="C119" s="30" t="s">
+      <c r="B129" s="48"/>
+      <c r="C129" s="30" t="s">
         <v>635</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D129" s="2" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A120" s="30" t="s">
+    <row r="130" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A130" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B130" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C120" s="30" t="s">
+      <c r="C130" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="30" t="s">
+    <row r="131" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A131" s="30" t="s">
         <v>637</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="30" t="s">
+      <c r="B131" s="3"/>
+      <c r="C131" s="30" t="s">
         <v>670</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="30" t="s">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A132" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="30" t="s">
+      <c r="B132" s="3"/>
+      <c r="C132" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="31" t="s">
+    <row r="133" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A133" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="B123" s="19"/>
-      <c r="C123" s="31" t="s">
+      <c r="B133" s="19"/>
+      <c r="C133" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D123" s="14" t="s">
+      <c r="D133" s="14" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A124" s="51" t="s">
+    <row r="134" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A134" s="51" t="s">
         <v>545</v>
       </c>
-      <c r="B124" s="27"/>
-      <c r="C124" s="51" t="s">
+      <c r="B134" s="27"/>
+      <c r="C134" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="D124" s="28" t="s">
+      <c r="D134" s="28" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="31" t="s">
+    <row r="135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A135" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="B125" s="19"/>
-      <c r="C125" s="31" t="s">
+      <c r="B135" s="19"/>
+      <c r="C135" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="D125" s="14" t="s">
+      <c r="D135" s="14" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="31" t="s">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A136" s="31" t="s">
+        <v>727</v>
+      </c>
+      <c r="B136" s="60" t="s">
+        <v>729</v>
+      </c>
+      <c r="C136" s="31" t="s">
         <v>728</v>
       </c>
-      <c r="B126" s="60" t="s">
-        <v>730</v>
-      </c>
-      <c r="C126" s="31" t="s">
-        <v>729</v>
-      </c>
-      <c r="D126" s="14"/>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="31" t="s">
+      <c r="D136" s="14"/>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A137" s="31" t="s">
         <v>641</v>
       </c>
-      <c r="B127" s="19"/>
-      <c r="C127" s="31" t="s">
+      <c r="B137" s="19"/>
+      <c r="C137" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="D127" s="14" t="s">
+      <c r="D137" s="14" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A128" s="16" t="s">
+    <row r="138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A138" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B138" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="16" t="s">
+      <c r="C138" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D138" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="16" t="s">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="16" t="s">
         <v>618</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B139" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="C129" s="16" t="s">
+      <c r="C139" s="16" t="s">
         <v>619</v>
       </c>
-      <c r="D129" s="5" t="s">
+      <c r="D139" s="5" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A140" s="16" t="s">
         <v>647</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B140" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="C130" s="16" t="s">
+      <c r="C140" s="16" t="s">
         <v>648</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="D140" s="5" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="16" t="s">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A141" s="16" t="s">
         <v>674</v>
       </c>
-      <c r="B131" s="4"/>
-      <c r="C131" s="16" t="s">
+      <c r="B141" s="4"/>
+      <c r="C141" s="16" t="s">
         <v>675</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D141" s="5" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="16" t="s">
+    <row r="142" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A142" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="B132" s="4"/>
-      <c r="C132" s="16" t="s">
+      <c r="B142" s="4"/>
+      <c r="C142" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D142" s="5" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B133" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C133" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A134" s="30" t="s">
-        <v>727</v>
-      </c>
-      <c r="B134" s="35"/>
-      <c r="C134" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="D134" s="2"/>
-    </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C135" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A136" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="B136" s="20"/>
-      <c r="C136" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C137" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B138" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C138" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="B139" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C140" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="51" t="s">
-        <v>548</v>
-      </c>
-      <c r="B141" s="29"/>
-      <c r="C141" s="51" t="s">
-        <v>549</v>
-      </c>
-      <c r="D141" s="28" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A142" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B142" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C142" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1">
       <c r="A143" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2" t="s">
-        <v>302</v>
+        <v>279</v>
+      </c>
+      <c r="B143" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="C143" s="30" t="s">
+        <v>281</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>600</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
       <c r="A144" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>601</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="B144" s="35"/>
+      <c r="C144" s="30" t="s">
+        <v>755</v>
+      </c>
+      <c r="D144" s="2"/>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1">
       <c r="A145" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>306</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="B145" s="35"/>
       <c r="C145" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>308</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="D145" s="2"/>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C146" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="D146" s="33" t="s">
-        <v>312</v>
-      </c>
+      <c r="A146" s="30" t="s">
+        <v>782</v>
+      </c>
+      <c r="B146" s="35" t="s">
+        <v>783</v>
+      </c>
+      <c r="C146" s="30" t="s">
+        <v>784</v>
+      </c>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B147" s="4"/>
-      <c r="C147" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>605</v>
+      <c r="A147" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C147" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B148" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C148" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>318</v>
+      <c r="A148" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B148" s="20"/>
+      <c r="C148" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
       <c r="A149" s="30" t="s">
-        <v>319</v>
+        <v>468</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>320</v>
+        <v>469</v>
       </c>
       <c r="C149" s="30" t="s">
-        <v>321</v>
+        <v>468</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>322</v>
+        <v>470</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
       <c r="A150" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="B150" s="48" t="s">
-        <v>721</v>
+        <v>179</v>
+      </c>
+      <c r="B150" s="35" t="s">
+        <v>178</v>
       </c>
       <c r="C150" s="30" t="s">
-        <v>720</v>
-      </c>
-      <c r="D150" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B151" s="35" t="s">
-        <v>324</v>
+        <v>289</v>
+      </c>
+      <c r="B151" s="22" t="s">
+        <v>290</v>
       </c>
       <c r="C151" s="30" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B152" s="5"/>
-      <c r="C152" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="30" customHeight="1">
-      <c r="A153" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B153" s="5"/>
-      <c r="C153" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>332</v>
+      <c r="A152" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C152" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A153" s="51" t="s">
+        <v>548</v>
+      </c>
+      <c r="B153" s="29"/>
+      <c r="C153" s="51" t="s">
+        <v>549</v>
+      </c>
+      <c r="D153" s="28" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="B154" s="5"/>
-      <c r="C154" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>335</v>
+      <c r="A154" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C154" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1">
       <c r="A155" s="30" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="B155" s="2"/>
-      <c r="C155" s="30" t="s">
-        <v>337</v>
+      <c r="C155" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="B156" s="39"/>
-      <c r="C156" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>340</v>
+      <c r="A156" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>343</v>
+      <c r="A157" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C157" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1">
       <c r="A158" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B158" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>310</v>
+      </c>
       <c r="C158" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>346</v>
+        <v>311</v>
+      </c>
+      <c r="D158" s="33" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>603</v>
+      <c r="A159" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1">
       <c r="A160" s="30" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="C160" s="30" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B161" s="26"/>
-      <c r="C161" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D161" s="14" t="s">
-        <v>355</v>
+      <c r="A161" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1">
       <c r="A162" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="B162" s="35" t="s">
-        <v>357</v>
+        <v>718</v>
+      </c>
+      <c r="B162" s="48" t="s">
+        <v>720</v>
       </c>
       <c r="C162" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="D162" s="2"/>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B163" s="26"/>
-      <c r="C163" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="D163" s="14" t="s">
-        <v>361</v>
+      <c r="A163" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B164" s="26"/>
-      <c r="C164" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="D164" s="14" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B165" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="C165" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>368</v>
+      <c r="A164" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B164" s="5"/>
+      <c r="C164" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="30" customHeight="1">
+      <c r="A165" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B165" s="5"/>
+      <c r="C165" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A166" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B166" s="35"/>
-      <c r="C166" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>371</v>
+      <c r="A166" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B166" s="5"/>
+      <c r="C166" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
       <c r="A167" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="B167" s="35" t="s">
-        <v>373</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="B167" s="2"/>
       <c r="C167" s="30" t="s">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>375</v>
+        <v>602</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B168" s="4"/>
-      <c r="C168" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>378</v>
+      <c r="A168" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" s="39"/>
+      <c r="C168" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B169" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="C169" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>382</v>
+      <c r="A169" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B169" s="5"/>
+      <c r="C169" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B170" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="C170" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>386</v>
+      <c r="A170" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B170" s="5"/>
+      <c r="C170" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1">
       <c r="A171" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B171" s="3"/>
+        <v>347</v>
+      </c>
+      <c r="B171" s="2"/>
       <c r="C171" s="30" t="s">
-        <v>387</v>
+        <v>348</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
       <c r="A172" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="B172" s="3"/>
+        <v>349</v>
+      </c>
+      <c r="B172" s="35" t="s">
+        <v>350</v>
+      </c>
       <c r="C172" s="30" t="s">
-        <v>663</v>
+        <v>351</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>690</v>
+        <v>352</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="30" t="s">
-        <v>661</v>
-      </c>
-      <c r="B173" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="C173" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>390</v>
+      <c r="A173" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B173" s="26"/>
+      <c r="C173" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D173" s="14" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="B174" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>394</v>
+      <c r="A174" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B174" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="C174" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="B175" s="39"/>
-      <c r="C175" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>397</v>
+      <c r="A175" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B175" s="26"/>
+      <c r="C175" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D175" s="14" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
       <c r="A176" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>399</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B176" s="26"/>
       <c r="C176" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>401</v>
+        <v>363</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1">
       <c r="A177" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B177" s="3"/>
+        <v>365</v>
+      </c>
+      <c r="B177" s="35" t="s">
+        <v>366</v>
+      </c>
       <c r="C177" s="30" t="s">
-        <v>492</v>
+        <v>367</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>604</v>
+        <v>368</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B178" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="C178" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="D178" s="21" t="s">
-        <v>406</v>
+      <c r="A178" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B178" s="35"/>
+      <c r="C178" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="B179" s="39"/>
-      <c r="C179" s="54" t="s">
-        <v>408</v>
-      </c>
-      <c r="D179" s="21" t="s">
-        <v>585</v>
+      <c r="A179" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="B179" s="35" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A180" s="55" t="s">
-        <v>409</v>
+      <c r="A180" s="16" t="s">
+        <v>376</v>
       </c>
       <c r="B180" s="4"/>
-      <c r="C180" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>586</v>
+      <c r="C180" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
       <c r="A181" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B181" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="B181" s="35" t="s">
+        <v>380</v>
+      </c>
       <c r="C181" s="30" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>587</v>
+        <v>382</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B182" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="B182" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C182" s="30" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>588</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
       <c r="A183" s="30" t="s">
-        <v>744</v>
-      </c>
-      <c r="B183" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="B183" s="3"/>
       <c r="C183" s="30" t="s">
-        <v>745</v>
-      </c>
-      <c r="D183" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
       <c r="A184" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>416</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="B184" s="3"/>
       <c r="C184" s="30" t="s">
-        <v>417</v>
+        <v>663</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>418</v>
+        <v>690</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A185" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="B185" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="C185" s="56" t="s">
-        <v>421</v>
+      <c r="A185" s="30" t="s">
+        <v>661</v>
+      </c>
+      <c r="B185" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="C185" s="30" t="s">
+        <v>389</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="B186" s="2"/>
-      <c r="C186" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>589</v>
+      <c r="A186" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="B186" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C187" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D187" s="33" t="s">
-        <v>428</v>
+      <c r="A187" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B187" s="39"/>
+      <c r="C187" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C188" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>432</v>
+      <c r="A188" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C188" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
       <c r="A189" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B189" s="35" t="s">
-        <v>434</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="B189" s="3"/>
       <c r="C189" s="30" t="s">
-        <v>583</v>
+        <v>492</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>435</v>
+        <v>604</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C190" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>439</v>
+      <c r="A190" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B190" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C190" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D190" s="21" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C191" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>443</v>
+      <c r="A191" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="B191" s="39"/>
+      <c r="C191" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D191" s="21" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B192" s="2"/>
-      <c r="C192" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>590</v>
+      <c r="A192" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1">
       <c r="A193" s="30" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="30" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A194" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B194" s="14"/>
-      <c r="C194" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D194" s="14" t="s">
-        <v>664</v>
+      <c r="A194" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="B194" s="2"/>
+      <c r="C194" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A195" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B195" s="14"/>
-      <c r="C195" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="D195" s="14" t="s">
-        <v>555</v>
-      </c>
+      <c r="A195" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B195" s="2"/>
+      <c r="C195" s="30" t="s">
+        <v>744</v>
+      </c>
+      <c r="D195" s="2"/>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A196" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="B196" s="14"/>
-      <c r="C196" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="D196" s="14" t="s">
-        <v>558</v>
+      <c r="A196" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C196" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A197" s="31" t="s">
-        <v>559</v>
-      </c>
-      <c r="B197" s="14"/>
-      <c r="C197" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="D197" s="14" t="s">
-        <v>561</v>
+      <c r="A197" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B197" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C197" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A198" s="31" t="s">
-        <v>562</v>
-      </c>
-      <c r="B198" s="14"/>
-      <c r="C198" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="D198" s="14" t="s">
-        <v>564</v>
+      <c r="A198" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A199" s="31" t="s">
-        <v>565</v>
-      </c>
-      <c r="B199" s="14"/>
-      <c r="C199" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="D199" s="14" t="s">
-        <v>567</v>
+      <c r="A199" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C199" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D199" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A200" s="31" t="s">
-        <v>749</v>
-      </c>
-      <c r="B200" s="14" t="s">
-        <v>748</v>
-      </c>
-      <c r="C200" s="31" t="s">
-        <v>747</v>
-      </c>
-      <c r="D200" s="62"/>
+      <c r="A200" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C200" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A201" s="31" t="s">
-        <v>448</v>
-      </c>
-      <c r="B201" s="48" t="s">
-        <v>498</v>
-      </c>
-      <c r="C201" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="D201" s="14" t="s">
-        <v>450</v>
+      <c r="A201" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="B201" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="C201" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A202" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C202" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D202" s="5" t="s">
-        <v>454</v>
+      <c r="A202" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C202" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A203" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="B203" s="4"/>
-      <c r="C203" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="D203" s="5"/>
+      <c r="A203" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C203" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A204" s="16" t="s">
-        <v>645</v>
-      </c>
-      <c r="B204" s="4"/>
-      <c r="C204" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="D204" s="5" t="s">
-        <v>689</v>
+      <c r="A204" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B204" s="2"/>
+      <c r="C204" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1">
       <c r="A205" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>456</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="B205" s="2"/>
       <c r="C205" s="30" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>458</v>
+        <v>591</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A206" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>462</v>
+      <c r="A206" s="31" t="s">
+        <v>551</v>
+      </c>
+      <c r="B206" s="14"/>
+      <c r="C206" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="D206" s="14" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A207" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C207" s="30" t="s">
-        <v>465</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>466</v>
+      <c r="A207" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="B207" s="14"/>
+      <c r="C207" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="D207" s="14" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A208" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="B208" s="20"/>
-      <c r="C208" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="D208" s="5" t="s">
-        <v>688</v>
+      <c r="A208" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B208" s="14"/>
+      <c r="C208" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="D208" s="14" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1">
       <c r="A209" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>569</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="B209" s="14"/>
       <c r="C209" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D209" s="6" t="s">
-        <v>581</v>
+        <v>560</v>
+      </c>
+      <c r="D209" s="14" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1">
       <c r="A210" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="B210" s="14"/>
+      <c r="C210" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="D210" s="14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A211" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B211" s="14"/>
+      <c r="C211" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D211" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A212" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="B212" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="C212" s="31" t="s">
+        <v>746</v>
+      </c>
+      <c r="D212" s="62"/>
+    </row>
+    <row r="213" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A213" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B213" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="C213" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="D213" s="14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A214" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C214" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A215" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D215" s="5"/>
+    </row>
+    <row r="216" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A216" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A217" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C217" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A218" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D218" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A219" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C219" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A220" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B220" s="20"/>
+      <c r="C220" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A221" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C221" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A222" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B222" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C210" s="31" t="s">
+      <c r="C222" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D210" s="6" t="s">
+      <c r="D222" s="6" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A211" s="16" t="s">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A223" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="B211" s="20"/>
-      <c r="C211" s="16" t="s">
+      <c r="B223" s="20"/>
+      <c r="C223" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="D211" s="5" t="s">
+      <c r="D223" s="5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A212" s="16" t="s">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A224" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="B212" s="20"/>
-      <c r="C212" s="16" t="s">
+      <c r="B224" s="20"/>
+      <c r="C224" s="16" t="s">
         <v>652</v>
       </c>
-      <c r="D212" s="5" t="s">
+      <c r="D224" s="5" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A213" s="16" t="s">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A225" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B213" s="20" t="s">
+      <c r="B225" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C213" s="16" t="s">
+      <c r="C225" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D213" s="5" t="s">
+      <c r="D225" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="16" t="s">
+    <row r="226" spans="1:4">
+      <c r="A226" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B226" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C214" s="16" t="s">
+      <c r="C226" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D214" s="5" t="s">
+      <c r="D226" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A215" s="30" t="s">
+    <row r="227" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A227" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B227" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C215" s="30" t="s">
+      <c r="C227" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="D227" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A216" s="30" t="s">
+    <row r="228" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A228" s="30" t="s">
+        <v>735</v>
+      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="B216" s="3"/>
-      <c r="C216" s="30" t="s">
-        <v>737</v>
-      </c>
-      <c r="D216" s="2"/>
-    </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A217" s="2" t="s">
+      <c r="D228" s="2"/>
+    </row>
+    <row r="229" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A229" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B229" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="D229" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A218" s="2" t="s">
+    <row r="230" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A230" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B218" s="35" t="s">
+      <c r="B230" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="C230" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="D230" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A219" s="58" t="s">
+    <row r="231" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A231" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B219" s="6" t="s">
+      <c r="B231" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C219" s="31" t="s">
+      <c r="C231" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D219" s="6" t="s">
+      <c r="D231" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A232" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B232" t="s">
+        <v>786</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="234" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="235" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="236" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="237" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="238" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="239" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="240" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
     <row r="243" ht="15.75" customHeight="1"/>
@@ -7353,156 +7598,168 @@
     <row r="1147" ht="15.75" customHeight="1"/>
     <row r="1148" ht="15.75" customHeight="1"/>
     <row r="1149" ht="15.75" customHeight="1"/>
+    <row r="1150" ht="15.75" customHeight="1"/>
+    <row r="1151" ht="15.75" customHeight="1"/>
+    <row r="1152" ht="15.75" customHeight="1"/>
+    <row r="1153" ht="15.75" customHeight="1"/>
+    <row r="1154" ht="15.75" customHeight="1"/>
+    <row r="1155" ht="15.75" customHeight="1"/>
+    <row r="1156" ht="15.75" customHeight="1"/>
+    <row r="1157" ht="15.75" customHeight="1"/>
+    <row r="1158" ht="15.75" customHeight="1"/>
+    <row r="1159" ht="15.75" customHeight="1"/>
+    <row r="1160" ht="15.75" customHeight="1"/>
+    <row r="1161" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B214" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B226" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="D23" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B24" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B27" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B28" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B32" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B33" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B34" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D34" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B35" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B36" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B37" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B25" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B28" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B29" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B33" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B34" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B35" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D35" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B36" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B37" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B39" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="B20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B41" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B42" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B47" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B49" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B52" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B53" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D53" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B54" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B56" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D56" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B57" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B58" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B59" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B61" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B62" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B63" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B64" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B65" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B67" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B68" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B69" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B70" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B71" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B72" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D72" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B73" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B75" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B78" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D81" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B86" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D86" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B87" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D87" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B90" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B92" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D92" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B94" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B95" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B101" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D101" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B102" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B104" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B105" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B113" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B114" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B115" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B117" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B128" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B133" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B135" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B138" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B139" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B140" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D140" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B142" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B145" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B146" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D146" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B148" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B149" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B151" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B160" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B162" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B165" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B167" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B169" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B170" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B173" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B174" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B176" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D176" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B178" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B184" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B185" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B187" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D187" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B188" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B189" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B190" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B191" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B202" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B205" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B206" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B207" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B137" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B215" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B66" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B217" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B218" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B93" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B118" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B201" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B43" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D43" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B44" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B49" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B51" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B53" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B57" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D57" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B58" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B60" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D60" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B61" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B62" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B63" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B65" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B66" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B67" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B68" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B69" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B71" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B72" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B73" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B74" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B75" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B76" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D76" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B77" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B79" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B85" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D88" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B93" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D93" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B94" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D94" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B97" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B100" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D100" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B102" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B103" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B110" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D110" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B111" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B113" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B114" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B123" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B124" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B125" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B127" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B138" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B143" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B147" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B150" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B151" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B152" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D152" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B154" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B157" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B158" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D158" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B160" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B161" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B163" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B172" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B174" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B177" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B179" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B181" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B182" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B185" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B186" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B188" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D188" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B190" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B196" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B197" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B199" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D199" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B200" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B201" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B202" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B203" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B214" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B217" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B218" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B219" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B149" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B227" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B70" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B229" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B230" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B101" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B128" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B213" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B39" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D39" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B76" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D76" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B84" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D84" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B88" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D88" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B89" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D89" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B110" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B209" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D209" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B210" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D210" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B219" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D219" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B41" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D41" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B80" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D80" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B91" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D91" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B95" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D95" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B96" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D96" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B120" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B221" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D221" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B222" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D222" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B231" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D231" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B22" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
     <hyperlink ref="B17" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B60" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B25" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B64" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B26" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
     <hyperlink ref="B7" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="B3" r:id="rId139" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
-    <hyperlink ref="B82" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B81" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B79" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
-    <hyperlink ref="B55" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
-    <hyperlink ref="B48" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B150" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
-    <hyperlink ref="B80" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B126" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B107" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B89" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B88" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B86" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B59" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B52" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B162" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B87" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B136" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B117" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
     <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F93741-AB0B-4148-90AA-EDA82AA2AABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5839A2B-2D53-E745-9D97-48450E3B5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="790">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2973,6 +2973,12 @@
   </si>
   <si>
     <t>RoyalCommission</t>
+  </si>
+  <si>
+    <t>Volksstimme</t>
+  </si>
+  <si>
+    <t>Presse/Volksstimme (Mannheim)</t>
   </si>
 </sst>
 </file>
@@ -3211,7 +3217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3315,7 +3321,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3411,7 +3416,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D225" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D226" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3620,7 +3625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1161"/>
+  <dimension ref="A1:Z1162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -4288,7 +4293,7 @@
       <c r="A51" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B51" s="48" t="s">
         <v>72</v>
       </c>
       <c r="C51" s="30" t="s">
@@ -5185,13 +5190,13 @@
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A116" s="63" t="s">
+      <c r="A116" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="B116" s="63" t="s">
+      <c r="B116" s="37" t="s">
         <v>763</v>
       </c>
-      <c r="C116" s="63" t="s">
+      <c r="C116" s="37" t="s">
         <v>764</v>
       </c>
       <c r="D116" s="5"/>
@@ -5518,1170 +5523,1179 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
       <c r="A142" s="16" t="s">
-        <v>276</v>
+        <v>789</v>
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="D142" s="5"/>
+    </row>
+    <row r="143" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A143" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="D143" s="5" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B143" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C143" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1">
       <c r="A144" s="30" t="s">
-        <v>754</v>
-      </c>
-      <c r="B144" s="35"/>
+        <v>279</v>
+      </c>
+      <c r="B144" s="35" t="s">
+        <v>280</v>
+      </c>
       <c r="C144" s="30" t="s">
-        <v>755</v>
-      </c>
-      <c r="D144" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1">
       <c r="A145" s="30" t="s">
-        <v>726</v>
+        <v>754</v>
       </c>
       <c r="B145" s="35"/>
       <c r="C145" s="30" t="s">
-        <v>725</v>
+        <v>755</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
       <c r="A146" s="30" t="s">
-        <v>782</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>783</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="B146" s="35"/>
       <c r="C146" s="30" t="s">
-        <v>784</v>
+        <v>725</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
       <c r="A147" s="30" t="s">
+        <v>782</v>
+      </c>
+      <c r="B147" s="35" t="s">
+        <v>783</v>
+      </c>
+      <c r="C147" s="30" t="s">
+        <v>784</v>
+      </c>
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A148" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B148" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C147" s="30" t="s">
+      <c r="C148" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="16" t="s">
+    <row r="149" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A149" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B148" s="20"/>
-      <c r="C148" s="16" t="s">
+      <c r="B149" s="20"/>
+      <c r="C149" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D149" s="5" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C149" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
       <c r="A150" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B150" s="35" t="s">
-        <v>178</v>
+        <v>468</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="C150" s="30" t="s">
-        <v>179</v>
+        <v>468</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>180</v>
+        <v>470</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
       <c r="A151" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B151" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C151" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A152" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B151" s="22" t="s">
+      <c r="B152" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C151" s="30" t="s">
+      <c r="C152" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="D152" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="31" t="s">
+    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A153" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B153" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C152" s="31" t="s">
+      <c r="C153" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D153" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="51" t="s">
+    <row r="154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A154" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B153" s="29"/>
-      <c r="C153" s="51" t="s">
+      <c r="B154" s="29"/>
+      <c r="C154" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="D153" s="28" t="s">
+      <c r="D154" s="28" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C154" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1">
       <c r="A155" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
+      </c>
+      <c r="B155" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C155" s="30" t="s">
+        <v>299</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1">
       <c r="A156" s="30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B156" s="2"/>
       <c r="C156" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
       <c r="A157" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A158" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B158" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C157" s="30" t="s">
+      <c r="C158" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D158" s="2" t="s">
         <v>308</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C158" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="D158" s="33" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1">
       <c r="A159" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D159" s="33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A160" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B159" s="4"/>
-      <c r="C159" s="16" t="s">
+      <c r="B160" s="4"/>
+      <c r="C160" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D159" s="5" t="s">
+      <c r="D160" s="5" t="s">
         <v>605</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B160" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C160" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1">
       <c r="A161" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
+      </c>
+      <c r="B161" s="35" t="s">
+        <v>316</v>
       </c>
       <c r="C161" s="30" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1">
       <c r="A162" s="30" t="s">
-        <v>718</v>
-      </c>
-      <c r="B162" s="48" t="s">
-        <v>720</v>
+        <v>319</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="C162" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="D162" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
       <c r="A163" s="30" t="s">
+        <v>718</v>
+      </c>
+      <c r="B163" s="48" t="s">
+        <v>720</v>
+      </c>
+      <c r="C163" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A164" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B163" s="35" t="s">
+      <c r="B164" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="C163" s="30" t="s">
+      <c r="C164" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D164" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="16" t="s">
+    <row r="165" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A165" s="16" t="s">
         <v>327</v>
-      </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="30" customHeight="1">
-      <c r="A165" s="16" t="s">
-        <v>330</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="16" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="30" customHeight="1">
       <c r="A166" s="16" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A167" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B167" s="5"/>
+      <c r="C167" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D166" s="5" t="s">
+      <c r="D167" s="5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="30" t="s">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A168" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B167" s="2"/>
-      <c r="C167" s="30" t="s">
+      <c r="B168" s="2"/>
+      <c r="C168" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D168" s="2" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="38" t="s">
+    <row r="169" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A169" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B168" s="39"/>
-      <c r="C168" s="40" t="s">
+      <c r="B169" s="39"/>
+      <c r="C169" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="D168" s="11" t="s">
+      <c r="D169" s="11" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B169" s="5"/>
-      <c r="C169" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1">
       <c r="A170" s="16" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A171" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" s="5"/>
+      <c r="C171" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D171" s="5" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B171" s="2"/>
-      <c r="C171" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1">
       <c r="A172" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B172" s="2"/>
+      <c r="C172" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A173" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="B172" s="35" t="s">
+      <c r="B173" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="C172" s="30" t="s">
+      <c r="C173" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D173" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="31" t="s">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A174" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="B173" s="26"/>
-      <c r="C173" s="31" t="s">
+      <c r="B174" s="26"/>
+      <c r="C174" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="D173" s="14" t="s">
+      <c r="D174" s="14" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="30" t="s">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A175" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="B174" s="35" t="s">
+      <c r="B175" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="C174" s="30" t="s">
+      <c r="C175" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="D175" s="2" t="s">
         <v>359</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B175" s="26"/>
-      <c r="C175" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
       <c r="A176" s="31" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B176" s="26"/>
       <c r="C176" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B177" s="26"/>
+      <c r="C177" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="D176" s="14" t="s">
+      <c r="D177" s="14" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B177" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="C177" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1">
       <c r="A178" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B178" s="35"/>
+        <v>365</v>
+      </c>
+      <c r="B178" s="35" t="s">
+        <v>366</v>
+      </c>
       <c r="C178" s="30" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1">
       <c r="A179" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B179" s="35"/>
+      <c r="C179" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A180" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B179" s="35" t="s">
+      <c r="B180" s="35" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="30" t="s">
+      <c r="C180" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="D180" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A180" s="16" t="s">
+    <row r="181" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A181" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="B180" s="4"/>
-      <c r="C180" s="16" t="s">
+      <c r="B181" s="4"/>
+      <c r="C181" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="D180" s="5" t="s">
+      <c r="D181" s="5" t="s">
         <v>378</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B181" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="C181" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B182" s="35" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C182" s="30" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
       <c r="A183" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B183" s="3"/>
+        <v>383</v>
+      </c>
+      <c r="B183" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C183" s="30" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>584</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
       <c r="A184" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="30" t="s">
-        <v>663</v>
+        <v>387</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>690</v>
+        <v>584</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
       <c r="A185" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B185" s="3"/>
+      <c r="C185" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A186" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="B185" s="35" t="s">
+      <c r="B186" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="C185" s="30" t="s">
+      <c r="C186" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D186" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A186" s="44" t="s">
+    <row r="187" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A187" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="B186" s="59" t="s">
+      <c r="B187" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="C186" s="7" t="s">
+      <c r="C187" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D186" s="7" t="s">
+      <c r="D187" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="38" t="s">
+    <row r="188" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A188" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="B187" s="39"/>
-      <c r="C187" s="40" t="s">
+      <c r="B188" s="39"/>
+      <c r="C188" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="D187" s="11" t="s">
+      <c r="D188" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="31" t="s">
+    <row r="189" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A189" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B189" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C188" s="31" t="s">
+      <c r="C189" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="D188" s="6" t="s">
+      <c r="D189" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="30" t="s">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A190" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="30" t="s">
+      <c r="B190" s="3"/>
+      <c r="C190" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="D190" s="2" t="s">
         <v>604</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B190" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="C190" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="D190" s="21" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1">
       <c r="A191" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B191" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C191" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D191" s="21" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A192" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B191" s="39"/>
-      <c r="C191" s="54" t="s">
+      <c r="B192" s="39"/>
+      <c r="C192" s="54" t="s">
         <v>408</v>
       </c>
-      <c r="D191" s="21" t="s">
+      <c r="D192" s="21" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="55" t="s">
+    <row r="193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A193" s="55" t="s">
         <v>409</v>
       </c>
-      <c r="B192" s="4"/>
-      <c r="C192" s="55" t="s">
+      <c r="B193" s="4"/>
+      <c r="C193" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="D192" s="9" t="s">
+      <c r="D193" s="9" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B193" s="2"/>
-      <c r="C193" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1">
       <c r="A194" s="30" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="30" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
       <c r="A195" s="30" t="s">
-        <v>743</v>
+        <v>413</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="30" t="s">
-        <v>744</v>
-      </c>
-      <c r="D195" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B196" s="2"/>
+      <c r="C196" s="30" t="s">
+        <v>744</v>
+      </c>
+      <c r="D196" s="2"/>
+    </row>
+    <row r="197" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A197" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B197" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C196" s="30" t="s">
+      <c r="C197" s="30" t="s">
         <v>417</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="D197" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A197" s="56" t="s">
+    <row r="198" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A198" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="B197" s="57" t="s">
+      <c r="B198" s="57" t="s">
         <v>420</v>
       </c>
-      <c r="C197" s="56" t="s">
+      <c r="C198" s="56" t="s">
         <v>421</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="D198" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A198" s="30" t="s">
+    <row r="199" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A199" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="B198" s="2"/>
-      <c r="C198" s="30" t="s">
+      <c r="B199" s="2"/>
+      <c r="C199" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="D199" s="2" t="s">
         <v>589</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A199" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C199" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D199" s="33" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1">
       <c r="A200" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C200" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D200" s="33" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A201" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B201" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C200" s="16" t="s">
+      <c r="C201" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="D200" s="5" t="s">
+      <c r="D201" s="5" t="s">
         <v>432</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A201" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B201" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="C201" s="30" t="s">
-        <v>583</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1">
       <c r="A202" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
+      </c>
+      <c r="B202" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="C202" s="30" t="s">
-        <v>438</v>
+        <v>583</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1">
       <c r="A203" s="30" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C203" s="30" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1">
       <c r="A204" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B204" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>441</v>
+      </c>
       <c r="C204" s="30" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>590</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1">
       <c r="A205" s="30" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A206" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="B206" s="2"/>
+      <c r="C206" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="D206" s="2" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A206" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B206" s="14"/>
-      <c r="C206" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D206" s="14" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1">
       <c r="A207" s="31" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B207" s="14"/>
       <c r="C207" s="31" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>555</v>
+        <v>664</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1">
       <c r="A208" s="31" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B208" s="14"/>
       <c r="C208" s="31" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1">
       <c r="A209" s="31" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B209" s="14"/>
       <c r="C209" s="31" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1">
       <c r="A210" s="31" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B210" s="14"/>
       <c r="C210" s="31" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1">
       <c r="A211" s="31" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B211" s="14"/>
       <c r="C211" s="31" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1">
       <c r="A212" s="31" t="s">
-        <v>748</v>
-      </c>
-      <c r="B212" s="14" t="s">
-        <v>747</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="B212" s="14"/>
       <c r="C212" s="31" t="s">
-        <v>746</v>
-      </c>
-      <c r="D212" s="62"/>
+        <v>566</v>
+      </c>
+      <c r="D212" s="14" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1">
       <c r="A213" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="B213" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="C213" s="31" t="s">
+        <v>746</v>
+      </c>
+      <c r="D213" s="62"/>
+    </row>
+    <row r="214" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A214" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B213" s="48" t="s">
+      <c r="B214" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="C213" s="31" t="s">
+      <c r="C214" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="D213" s="14" t="s">
+      <c r="D214" s="14" t="s">
         <v>450</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A214" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C214" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D214" s="5" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1">
       <c r="A215" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B215" s="4"/>
+        <v>451</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="C215" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="D215" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1">
       <c r="A216" s="16" t="s">
-        <v>645</v>
+        <v>730</v>
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D216" s="5"/>
+    </row>
+    <row r="217" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A217" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D216" s="5" t="s">
+      <c r="D217" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A217" s="30" t="s">
+    <row r="218" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A218" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B218" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C217" s="30" t="s">
+      <c r="C218" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="D218" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A218" s="7" t="s">
+    <row r="219" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A219" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B219" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C218" s="7" t="s">
+      <c r="C219" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D218" s="7" t="s">
+      <c r="D219" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A219" s="30" t="s">
+    <row r="220" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A220" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B220" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C219" s="30" t="s">
+      <c r="C220" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="D220" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A220" s="16" t="s">
+    <row r="221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A221" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B220" s="20"/>
-      <c r="C220" s="16" t="s">
+      <c r="B221" s="20"/>
+      <c r="C221" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D220" s="5" t="s">
+      <c r="D221" s="5" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A221" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C221" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D221" s="6" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1">
       <c r="A222" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C222" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A223" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B222" s="6" t="s">
+      <c r="B223" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C222" s="31" t="s">
+      <c r="C223" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D222" s="6" t="s">
+      <c r="D223" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A223" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B223" s="20"/>
-      <c r="C223" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1">
       <c r="A224" s="16" t="s">
-        <v>651</v>
+        <v>476</v>
       </c>
       <c r="B224" s="20"/>
       <c r="C224" s="16" t="s">
-        <v>652</v>
+        <v>477</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1">
       <c r="A225" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B225" s="20"/>
+      <c r="C225" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A226" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B225" s="20" t="s">
+      <c r="B226" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C225" s="16" t="s">
+      <c r="C226" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D225" s="5" t="s">
+      <c r="D226" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
-      <c r="A226" s="16" t="s">
+    <row r="227" spans="1:4">
+      <c r="A227" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B227" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C226" s="16" t="s">
+      <c r="C227" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D226" s="5" t="s">
+      <c r="D227" s="5" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A227" s="30" t="s">
-        <v>684</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C227" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1">
       <c r="A228" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C228" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A229" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B228" s="3"/>
-      <c r="C228" s="30" t="s">
+      <c r="B229" s="3"/>
+      <c r="C229" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D228" s="2"/>
-    </row>
-    <row r="229" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A229" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>487</v>
-      </c>
+      <c r="D229" s="2"/>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1">
       <c r="A230" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A231" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B230" s="35" t="s">
+      <c r="B231" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D231" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A231" s="58" t="s">
+    <row r="232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A232" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B231" s="6" t="s">
+      <c r="B232" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C231" s="31" t="s">
+      <c r="C232" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D231" s="6" t="s">
+      <c r="D232" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A232" s="2" t="s">
+    <row r="233" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A233" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B233" t="s">
         <v>786</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C233" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="234" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="235" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="236" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7610,11 +7624,12 @@
     <row r="1159" ht="15.75" customHeight="1"/>
     <row r="1160" ht="15.75" customHeight="1"/>
     <row r="1161" ht="15.75" customHeight="1"/>
+    <row r="1162" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B226" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B227" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -7681,50 +7696,50 @@
     <hyperlink ref="B125" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="B127" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
     <hyperlink ref="B138" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B143" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B147" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B150" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B151" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B152" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D152" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B154" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B157" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B158" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D158" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B160" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B161" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B163" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B172" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B174" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B177" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B179" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B181" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B182" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B185" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B186" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B188" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D188" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B190" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B196" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B197" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B199" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D199" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B200" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B201" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B202" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B203" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B214" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B217" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B218" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B219" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B149" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B227" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B144" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B148" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B151" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B152" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B153" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D153" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B155" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B158" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B159" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D159" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B161" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B162" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B164" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B173" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B175" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B178" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B180" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B182" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B183" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B186" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B187" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B189" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D189" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B191" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B197" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B198" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B200" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D200" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B201" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B202" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B203" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B204" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B215" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B218" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B219" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B220" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B150" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B228" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
     <hyperlink ref="B70" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B229" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B230" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B230" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B231" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
     <hyperlink ref="B101" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
     <hyperlink ref="B128" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B213" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B214" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
@@ -7739,12 +7754,12 @@
     <hyperlink ref="B96" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
     <hyperlink ref="D96" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
     <hyperlink ref="B120" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B221" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D221" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B222" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D222" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B231" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D231" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B222" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D222" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B223" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D223" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B232" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D232" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B22" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
     <hyperlink ref="B17" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
     <hyperlink ref="B64" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
@@ -7756,7 +7771,7 @@
     <hyperlink ref="B86" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
     <hyperlink ref="B59" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
     <hyperlink ref="B52" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B162" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B163" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
     <hyperlink ref="B87" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
     <hyperlink ref="B136" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
     <hyperlink ref="B117" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5839A2B-2D53-E745-9D97-48450E3B5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0034667B-3555-A444-89F0-58EC92BD9DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0034667B-3555-A444-89F0-58EC92BD9DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A35CA3C-6911-6F44-9734-6E6C323F1446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="798">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -2979,6 +2979,30 @@
   </si>
   <si>
     <t>Presse/Volksstimme (Mannheim)</t>
+  </si>
+  <si>
+    <t>Canadian Pacific Railway</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4227424-2</t>
+  </si>
+  <si>
+    <t>CanadianPacificRailway</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="CanadianPacificRailway" ref="https://d-nb.info/gnd/4227424-2"&gt;</t>
+  </si>
+  <si>
+    <t>C. Czarnikow</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/270174-1</t>
+  </si>
+  <si>
+    <t>CCzarnikow</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="CCzarnikow" ref="https://d-nb.info/gnd/270174-1"&gt;</t>
   </si>
 </sst>
 </file>
@@ -3130,7 +3154,7 @@
       <name val="Calibri, sans-serif"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3159,6 +3183,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB9CFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3217,7 +3247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3321,6 +3351,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3416,7 +3449,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D226" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D228" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3625,7 +3658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1162"/>
+  <dimension ref="A1:Z1164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3635,7 +3668,7 @@
     <col min="5" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16">
+    <row r="1" spans="1:25" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3649,7 +3682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:25">
       <c r="A2" s="30" t="s">
         <v>4</v>
       </c>
@@ -3663,7 +3696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:25">
       <c r="A3" s="30" t="s">
         <v>703</v>
       </c>
@@ -3675,7 +3708,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:25">
       <c r="A4" s="30" t="s">
         <v>704</v>
       </c>
@@ -3685,7 +3718,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:25">
       <c r="A5" s="30" t="s">
         <v>737</v>
       </c>
@@ -3699,7 +3732,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:25">
       <c r="A6" s="31" t="s">
         <v>499</v>
       </c>
@@ -3711,7 +3744,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:25">
       <c r="A7" s="31" t="s">
         <v>502</v>
       </c>
@@ -3725,7 +3758,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:25">
       <c r="A8" s="31" t="s">
         <v>504</v>
       </c>
@@ -3737,7 +3770,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:25">
       <c r="A9" s="31" t="s">
         <v>507</v>
       </c>
@@ -3751,7 +3784,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:25">
       <c r="A10" s="31" t="s">
         <v>510</v>
       </c>
@@ -3763,7 +3796,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:25">
       <c r="A11" s="31" t="s">
         <v>513</v>
       </c>
@@ -3775,2929 +3808,2997 @@
         <v>515</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:25">
+      <c r="A12" s="63" t="s">
+        <v>790</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>791</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>792</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>793</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="31" t="s">
         <v>516</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="31" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D13" s="14" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
+    <row r="14" spans="1:25">
+      <c r="A14" s="63" t="s">
+        <v>794</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>795</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>796</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>797</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
+    <row r="16" spans="1:25">
+      <c r="A16" s="16" t="s">
         <v>610</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C16" s="16" t="s">
         <v>612</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>613</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>653</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="16" t="s">
-        <v>657</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="16" t="s">
         <v>633</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B19" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C19" s="16" t="s">
         <v>631</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="31" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B20" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C20" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="31" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="31" t="s">
         <v>626</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B21" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C21" s="31" t="s">
         <v>627</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="16" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="16" t="s">
         <v>630</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D22" s="33" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="16" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D23" s="33" t="s">
         <v>644</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="31" t="s">
-        <v>616</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>617</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>679</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>617</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>679</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="31" t="s">
         <v>765</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="31" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="31" t="s">
         <v>766</v>
       </c>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="B26" s="59" t="s">
-        <v>608</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>607</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>609</v>
-      </c>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="16" t="s">
-        <v>622</v>
+        <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>623</v>
+        <v>21</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>624</v>
+        <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>625</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>27</v>
+      <c r="A28" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>608</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16" t="s">
-        <v>28</v>
+        <v>622</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>623</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>31</v>
+        <v>625</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>34</v>
+      <c r="A30" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="16" t="s">
-        <v>709</v>
-      </c>
-      <c r="B31" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="C31" s="16" t="s">
-        <v>739</v>
-      </c>
-      <c r="D31" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="16" t="s">
-        <v>710</v>
+        <v>32</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="16" t="s">
-        <v>740</v>
-      </c>
-      <c r="D32" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="B33" s="4"/>
       <c r="C33" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>739</v>
+      </c>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="16" t="s">
+        <v>710</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="16" t="s">
+        <v>740</v>
+      </c>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="31" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B37" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C37" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="30" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C38" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="16">
-      <c r="A37" s="7" t="s">
+    <row r="39" spans="1:4" ht="16">
+      <c r="A39" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D39" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16">
-      <c r="A38" s="7" t="s">
+    <row r="40" spans="1:4" ht="16">
+      <c r="A40" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="16" t="s">
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="16" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" s="16" t="s">
         <v>741</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="16" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="16" t="s">
         <v>742</v>
       </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>521</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="31" t="s">
-        <v>665</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>667</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>694</v>
-      </c>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>667</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B45" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C45" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="30" t="s">
+    <row r="46" spans="1:4">
+      <c r="A46" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C46" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>759</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>761</v>
-      </c>
-      <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>668</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>669</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="30" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>695</v>
+        <v>592</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1">
       <c r="A48" s="30" t="s">
+        <v>759</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>761</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A49" s="30" t="s">
+        <v>668</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A50" s="30" t="s">
         <v>770</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="30" t="s">
+      <c r="B50" s="2"/>
+      <c r="C50" s="30" t="s">
         <v>771</v>
       </c>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="9" t="s">
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="34" t="s">
+      <c r="B51" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C51" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D51" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="9" t="s">
+    <row r="52" spans="1:4">
+      <c r="A52" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B50" s="34"/>
-      <c r="C50" s="9" t="s">
+      <c r="B52" s="34"/>
+      <c r="C52" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D52" s="9" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="30" t="s">
-        <v>714</v>
-      </c>
-      <c r="B52" s="48" t="s">
-        <v>715</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>716</v>
-      </c>
-      <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>72</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>593</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="36"/>
+        <v>714</v>
+      </c>
+      <c r="B54" s="48" t="s">
+        <v>715</v>
+      </c>
       <c r="C54" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>594</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="36"/>
+      <c r="C56" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30" t="s">
+      <c r="B57" s="30"/>
+      <c r="C57" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>595</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="B59" s="48" t="s">
+      <c r="B61" s="48" t="s">
         <v>712</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C61" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="37" t="s">
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="B62" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C60" s="37" t="s">
+      <c r="C62" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D62" s="10" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B62" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="61" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="B64" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:26">
       <c r="A65" s="38" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:26">
       <c r="A66" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B66" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26">
+      <c r="A67" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26">
+      <c r="A68" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B66" s="39" t="s">
+      <c r="B68" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C66" s="40" t="s">
+      <c r="C68" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="1:26">
-      <c r="A67" s="16" t="s">
+    <row r="69" spans="1:26">
+      <c r="A69" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C69" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="68" spans="1:26">
-      <c r="A68" s="30" t="s">
+    <row r="70" spans="1:26">
+      <c r="A70" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="B68" s="35" t="s">
+      <c r="B70" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C68" s="30" t="s">
+      <c r="C70" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="69" spans="1:26">
-      <c r="A69" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>574</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="71" spans="1:26">
       <c r="A71" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A72" s="30" t="s">
+        <v>574</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26">
+      <c r="A73" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="B71" s="48" t="s">
+      <c r="B73" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C73" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:26">
-      <c r="A72" s="41" t="s">
+    <row r="74" spans="1:26">
+      <c r="A74" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B72" s="42" t="s">
+      <c r="B74" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C72" s="41" t="s">
+      <c r="C74" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D74" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="13"/>
-      <c r="Q72" s="13"/>
-      <c r="R72" s="13"/>
-      <c r="S72" s="13"/>
-      <c r="T72" s="13"/>
-      <c r="U72" s="13"/>
-      <c r="V72" s="13"/>
-      <c r="W72" s="13"/>
-      <c r="X72" s="13"/>
-      <c r="Y72" s="13"/>
-      <c r="Z72" s="13"/>
-    </row>
-    <row r="73" spans="1:26" ht="16">
-      <c r="A73" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26" ht="16">
-      <c r="A74" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>148</v>
-      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="13"/>
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+      <c r="X74" s="13"/>
+      <c r="Y74" s="13"/>
+      <c r="Z74" s="13"/>
     </row>
     <row r="75" spans="1:26" ht="16">
       <c r="A75" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" ht="16">
+      <c r="A76" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" ht="16">
+      <c r="A77" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B77" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D77" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="76" spans="1:26">
-      <c r="A76" s="16" t="s">
+    <row r="78" spans="1:26">
+      <c r="A78" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B76" s="59" t="s">
+      <c r="B78" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C78" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D78" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:26">
-      <c r="A77" s="30" t="s">
+    <row r="79" spans="1:26">
+      <c r="A79" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="B79" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="C77" s="30" t="s">
+      <c r="C79" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="78" spans="1:26">
-      <c r="A78" s="30" t="s">
+    <row r="80" spans="1:26">
+      <c r="A80" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="30" t="s">
+      <c r="B80" s="3"/>
+      <c r="C80" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>596</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26">
-      <c r="A79" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="80" spans="1:26">
-      <c r="A80" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>525</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="31" t="s">
-        <v>772</v>
-      </c>
-      <c r="B81" s="6"/>
+        <v>162</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="C81" s="31" t="s">
-        <v>717</v>
-      </c>
-      <c r="D81" s="6"/>
+        <v>164</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="31" t="s">
-        <v>773</v>
+        <v>523</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>775</v>
+        <v>524</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>774</v>
-      </c>
-      <c r="D82" s="6"/>
+        <v>525</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="31" t="s">
-        <v>780</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>781</v>
-      </c>
+        <v>772</v>
+      </c>
+      <c r="B83" s="6"/>
       <c r="C83" s="31" t="s">
-        <v>779</v>
+        <v>717</v>
       </c>
       <c r="D83" s="6"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="31" t="s">
+        <v>773</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>774</v>
+      </c>
+      <c r="D84" s="6"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="31" t="s">
+        <v>780</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="D85" s="6"/>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="31" t="s">
         <v>776</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B86" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C86" s="31" t="s">
         <v>778</v>
       </c>
-      <c r="D84" s="6"/>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="B85" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="30" t="s">
-        <v>706</v>
-      </c>
-      <c r="B86" s="48" t="s">
-        <v>707</v>
-      </c>
-      <c r="C86" s="30" t="s">
-        <v>708</v>
-      </c>
-      <c r="D86" s="2"/>
+      <c r="D86" s="6"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="30" t="s">
+        <v>706</v>
+      </c>
+      <c r="B88" s="48" t="s">
+        <v>707</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>708</v>
+      </c>
+      <c r="D88" s="2"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="30" t="s">
         <v>722</v>
       </c>
-      <c r="B87" s="48" t="s">
+      <c r="B89" s="48" t="s">
         <v>723</v>
       </c>
-      <c r="C87" s="30" t="s">
+      <c r="C89" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="D87" s="2"/>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="43" t="s">
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="B88" s="32" t="s">
+      <c r="B90" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C90" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D90" s="15" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="44" t="s">
+    <row r="91" spans="1:4">
+      <c r="A91" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B91" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C91" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D91" s="7" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="D90" s="24" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="B91" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>531</v>
-      </c>
-      <c r="D91" s="26" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="31" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B92" s="19"/>
       <c r="C92" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="D92" s="24" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="D92" s="24" t="s">
+      <c r="B94" s="19"/>
+      <c r="C94" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="D94" s="24" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="30" t="s">
+    <row r="95" spans="1:4">
+      <c r="A95" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B95" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C93" s="30" t="s">
+      <c r="C95" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="D93" s="35" t="s">
+      <c r="D95" s="35" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="16" t="s">
+    <row r="96" spans="1:4">
+      <c r="A96" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B94" s="45" t="s">
+      <c r="B96" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C96" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="D94" s="33" t="s">
+      <c r="D96" s="33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="30">
-      <c r="A95" s="31" t="s">
+    <row r="97" spans="1:4" ht="30">
+      <c r="A97" s="31" t="s">
         <v>535</v>
       </c>
-      <c r="B95" s="46" t="s">
+      <c r="B97" s="46" t="s">
         <v>536</v>
       </c>
-      <c r="C95" s="31" t="s">
+      <c r="C97" s="31" t="s">
         <v>537</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D97" s="6" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="30">
-      <c r="A96" s="31" t="s">
+    <row r="98" spans="1:4" ht="30">
+      <c r="A98" s="31" t="s">
         <v>538</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>539</v>
       </c>
-      <c r="C96" s="31" t="s">
+      <c r="C98" s="31" t="s">
         <v>540</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D98" s="6" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="97" spans="1:26">
-      <c r="A97" s="16" t="s">
+    <row r="99" spans="1:4">
+      <c r="A99" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="B97" s="45" t="s">
+      <c r="B99" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C99" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D97" s="5" t="s">
+      <c r="D99" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="98" spans="1:26">
-      <c r="A98" s="16" t="s">
+    <row r="100" spans="1:4">
+      <c r="A100" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16" t="s">
+      <c r="B100" s="16"/>
+      <c r="C100" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D100" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="99" spans="1:26">
-      <c r="A99" s="16" t="s">
+    <row r="101" spans="1:4">
+      <c r="A101" s="16" t="s">
         <v>751</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B101" s="16" t="s">
         <v>753</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C101" s="16" t="s">
         <v>752</v>
       </c>
-      <c r="D99" s="5"/>
-    </row>
-    <row r="100" spans="1:26">
-      <c r="A100" s="16" t="s">
+      <c r="D101" s="5"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B100" s="47" t="s">
+      <c r="B102" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C102" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D102" s="33" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="101" spans="1:26">
-      <c r="A101" s="30" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B101" s="48" t="s">
+      <c r="B103" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="C101" s="30" t="s">
+      <c r="C103" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="16">
-      <c r="A102" s="30" t="s">
+    <row r="104" spans="1:4" ht="16">
+      <c r="A104" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="B102" s="36" t="s">
+      <c r="B104" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="C102" s="30" t="s">
+      <c r="C104" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="103" spans="1:26">
-      <c r="A103" s="30" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B105" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C103" s="30" t="s">
+      <c r="C105" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="104" spans="1:26">
-      <c r="A104" s="16" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" s="16" t="s">
         <v>204</v>
-      </c>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26">
-      <c r="A105" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26">
-      <c r="A106" s="16" t="s">
-        <v>209</v>
       </c>
       <c r="B106" s="16"/>
       <c r="C106" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26">
-      <c r="A107" s="16" t="s">
-        <v>756</v>
-      </c>
-      <c r="B107" s="16" t="s">
-        <v>757</v>
-      </c>
-      <c r="C107" s="16" t="s">
-        <v>758</v>
-      </c>
-      <c r="D107" s="5"/>
-    </row>
-    <row r="108" spans="1:26">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" s="16" t="s">
-        <v>749</v>
+        <v>209</v>
       </c>
       <c r="B108" s="16"/>
       <c r="C108" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="D109" s="5"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16" t="s">
         <v>750</v>
       </c>
-      <c r="D108" s="5"/>
-    </row>
-    <row r="109" spans="1:26">
-      <c r="A109" s="16" t="s">
+      <c r="D110" s="5"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16" t="s">
+      <c r="B111" s="16"/>
+      <c r="C111" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="D109" s="5" t="s">
+      <c r="D111" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="110" spans="1:26">
-      <c r="A110" s="31" t="s">
+    <row r="112" spans="1:4">
+      <c r="A112" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B110" s="17" t="s">
+      <c r="B112" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C110" s="31" t="s">
+      <c r="C112" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D112" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A111" s="49" t="s">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A113" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B113" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C111" s="49" t="s">
+      <c r="C113" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="D111" s="18" t="s">
+      <c r="D113" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
-      <c r="J111" s="13"/>
-      <c r="K111" s="13"/>
-      <c r="L111" s="13"/>
-      <c r="M111" s="13"/>
-      <c r="N111" s="13"/>
-      <c r="O111" s="13"/>
-      <c r="P111" s="13"/>
-      <c r="Q111" s="13"/>
-      <c r="R111" s="13"/>
-      <c r="S111" s="13"/>
-      <c r="T111" s="13"/>
-      <c r="U111" s="13"/>
-      <c r="V111" s="13"/>
-      <c r="W111" s="13"/>
-      <c r="X111" s="13"/>
-      <c r="Y111" s="13"/>
-      <c r="Z111" s="13"/>
-    </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A112" s="37" t="s">
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13"/>
+      <c r="J113" s="13"/>
+      <c r="K113" s="13"/>
+      <c r="L113" s="13"/>
+      <c r="M113" s="13"/>
+      <c r="N113" s="13"/>
+      <c r="O113" s="13"/>
+      <c r="P113" s="13"/>
+      <c r="Q113" s="13"/>
+      <c r="R113" s="13"/>
+      <c r="S113" s="13"/>
+      <c r="T113" s="13"/>
+      <c r="U113" s="13"/>
+      <c r="V113" s="13"/>
+      <c r="W113" s="13"/>
+      <c r="X113" s="13"/>
+      <c r="Y113" s="13"/>
+      <c r="Z113" s="13"/>
+    </row>
+    <row r="114" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A114" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="37"/>
-      <c r="C112" s="37" t="s">
+      <c r="B114" s="37"/>
+      <c r="C114" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D114" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A113" s="37" t="s">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A115" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="B113" s="50" t="s">
+      <c r="B115" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="37" t="s">
+      <c r="C115" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="D113" s="5"/>
-    </row>
-    <row r="114" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A114" s="37" t="s">
+      <c r="D115" s="5"/>
+    </row>
+    <row r="116" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A116" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="50" t="s">
+      <c r="B116" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="C116" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D114" s="5"/>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A115" s="38" t="s">
+      <c r="D116" s="5"/>
+    </row>
+    <row r="117" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A117" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B115" s="40"/>
-      <c r="C115" s="40" t="s">
+      <c r="B117" s="40"/>
+      <c r="C117" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D117" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A116" s="37" t="s">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A118" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="B116" s="37" t="s">
+      <c r="B118" s="37" t="s">
         <v>763</v>
       </c>
-      <c r="C116" s="37" t="s">
+      <c r="C118" s="37" t="s">
         <v>764</v>
       </c>
-      <c r="D116" s="5"/>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A117" s="37" t="s">
+      <c r="D118" s="5"/>
+    </row>
+    <row r="119" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A119" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="B117" s="48" t="s">
+      <c r="B119" s="48" t="s">
         <v>733</v>
       </c>
-      <c r="C117" s="37" t="s">
+      <c r="C119" s="37" t="s">
         <v>734</v>
       </c>
-      <c r="D117" s="5"/>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A118" s="30" t="s">
+      <c r="D119" s="5"/>
+    </row>
+    <row r="120" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A120" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B118" s="30"/>
-      <c r="C118" s="30" t="s">
+      <c r="B120" s="30"/>
+      <c r="C120" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D120" s="2" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A119" s="30" t="s">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A121" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="30" t="s">
+      <c r="B121" s="3"/>
+      <c r="C121" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A120" s="31" t="s">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A122" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B122" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="C120" s="31" t="s">
+      <c r="C122" s="31" t="s">
         <v>543</v>
       </c>
-      <c r="D120" s="14" t="s">
+      <c r="D122" s="14" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A121" s="38" t="s">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A123" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B121" s="39"/>
-      <c r="C121" s="40" t="s">
+      <c r="B123" s="39"/>
+      <c r="C123" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D123" s="11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A122" s="31" t="s">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A124" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="B122" s="19"/>
-      <c r="C122" s="31" t="s">
+      <c r="B124" s="19"/>
+      <c r="C124" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D124" s="14" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A123" s="30" t="s">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A125" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B125" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C123" s="30" t="s">
+      <c r="C125" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A124" s="30" t="s">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A126" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="48" t="s">
+      <c r="B126" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="30" t="s">
+      <c r="C126" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D126" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A125" s="30" t="s">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A127" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B127" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C125" s="30" t="s">
+      <c r="C127" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D127" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A126" s="30" t="s">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A128" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="B126" s="30"/>
-      <c r="C126" s="30" t="s">
+      <c r="B128" s="30"/>
+      <c r="C128" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>599</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A127" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C127" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A128" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B128" s="48" t="s">
-        <v>496</v>
-      </c>
-      <c r="C128" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1">
       <c r="A129" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="B129" s="48"/>
+        <v>256</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="C129" s="30" t="s">
-        <v>635</v>
+        <v>258</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>636</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1">
       <c r="A130" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="B130" s="48" t="s">
+        <v>496</v>
       </c>
       <c r="C130" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>265</v>
+        <v>497</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1">
       <c r="A131" s="30" t="s">
-        <v>637</v>
-      </c>
-      <c r="B131" s="3"/>
+        <v>634</v>
+      </c>
+      <c r="B131" s="48"/>
       <c r="C131" s="30" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1">
       <c r="A132" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C132" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A133" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="B133" s="3"/>
+      <c r="C133" s="30" t="s">
+        <v>670</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A134" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="30" t="s">
+      <c r="B134" s="3"/>
+      <c r="C134" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>640</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="B133" s="19"/>
-      <c r="C133" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="D133" s="14" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A134" s="51" t="s">
-        <v>545</v>
-      </c>
-      <c r="B134" s="27"/>
-      <c r="C134" s="51" t="s">
-        <v>546</v>
-      </c>
-      <c r="D134" s="28" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1">
       <c r="A135" s="31" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B135" s="19"/>
       <c r="C135" s="31" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A136" s="31" t="s">
-        <v>727</v>
-      </c>
-      <c r="B136" s="60" t="s">
-        <v>729</v>
-      </c>
-      <c r="C136" s="31" t="s">
-        <v>728</v>
-      </c>
-      <c r="D136" s="14"/>
+      <c r="A136" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="B136" s="27"/>
+      <c r="C136" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="D136" s="28" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1">
       <c r="A137" s="31" t="s">
-        <v>641</v>
+        <v>269</v>
       </c>
       <c r="B137" s="19"/>
       <c r="C137" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A138" s="31" t="s">
+        <v>727</v>
+      </c>
+      <c r="B138" s="60" t="s">
+        <v>729</v>
+      </c>
+      <c r="C138" s="31" t="s">
+        <v>728</v>
+      </c>
+      <c r="D138" s="14"/>
+    </row>
+    <row r="139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A139" s="31" t="s">
+        <v>641</v>
+      </c>
+      <c r="B139" s="19"/>
+      <c r="C139" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="D137" s="14" t="s">
+      <c r="D139" s="14" t="s">
         <v>700</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1">
       <c r="A140" s="16" t="s">
-        <v>647</v>
+        <v>272</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>650</v>
+        <v>273</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>648</v>
+        <v>274</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>649</v>
+        <v>275</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1">
       <c r="A141" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="B141" s="4"/>
+        <v>618</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>620</v>
+      </c>
       <c r="C141" s="16" t="s">
-        <v>675</v>
+        <v>619</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>691</v>
+        <v>621</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1">
       <c r="A142" s="16" t="s">
-        <v>789</v>
-      </c>
-      <c r="B142" s="4"/>
+        <v>647</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>650</v>
+      </c>
       <c r="C142" s="16" t="s">
-        <v>788</v>
-      </c>
-      <c r="D142" s="5"/>
+        <v>648</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1">
       <c r="A143" s="16" t="s">
-        <v>276</v>
+        <v>674</v>
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A144" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="D144" s="5"/>
+    </row>
+    <row r="145" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A145" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D143" s="5" t="s">
+      <c r="D145" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A144" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B144" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="C144" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="30" t="s">
-        <v>754</v>
-      </c>
-      <c r="B145" s="35"/>
-      <c r="C145" s="30" t="s">
-        <v>755</v>
-      </c>
-      <c r="D145" s="2"/>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1">
       <c r="A146" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="B146" s="35"/>
+        <v>279</v>
+      </c>
+      <c r="B146" s="35" t="s">
+        <v>280</v>
+      </c>
       <c r="C146" s="30" t="s">
-        <v>725</v>
-      </c>
-      <c r="D146" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1">
       <c r="A147" s="30" t="s">
-        <v>782</v>
-      </c>
-      <c r="B147" s="35" t="s">
-        <v>783</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="B147" s="35"/>
       <c r="C147" s="30" t="s">
-        <v>784</v>
+        <v>755</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1">
       <c r="A148" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="B148" s="35"/>
       <c r="C148" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>286</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="D148" s="2"/>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="B149" s="20"/>
-      <c r="C149" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>288</v>
-      </c>
+      <c r="A149" s="30" t="s">
+        <v>782</v>
+      </c>
+      <c r="B149" s="35" t="s">
+        <v>783</v>
+      </c>
+      <c r="C149" s="30" t="s">
+        <v>784</v>
+      </c>
+      <c r="D149" s="2"/>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1">
       <c r="A150" s="30" t="s">
-        <v>468</v>
+        <v>283</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="C150" s="30" t="s">
-        <v>468</v>
+        <v>285</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>470</v>
+        <v>286</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A151" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B151" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C151" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>180</v>
+      <c r="A151" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B151" s="20"/>
+      <c r="C151" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1">
       <c r="A152" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C152" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A153" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B153" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C153" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A154" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B152" s="22" t="s">
+      <c r="B154" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C152" s="30" t="s">
+      <c r="C154" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D154" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="31" t="s">
+    <row r="155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A155" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B155" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C153" s="31" t="s">
+      <c r="C155" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D155" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="51" t="s">
+    <row r="156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A156" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B154" s="29"/>
-      <c r="C154" s="51" t="s">
+      <c r="B156" s="29"/>
+      <c r="C156" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="D154" s="28" t="s">
+      <c r="D156" s="28" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B155" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C155" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1">
       <c r="A157" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
+      </c>
+      <c r="B157" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C157" s="30" t="s">
+        <v>299</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>601</v>
+        <v>300</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1">
       <c r="A158" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A159" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A160" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B160" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C158" s="30" t="s">
+      <c r="C160" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D160" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="16" t="s">
+    <row r="161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A161" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B161" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C159" s="16" t="s">
+      <c r="C161" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="D159" s="33" t="s">
+      <c r="D161" s="33" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="16" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A162" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="16" t="s">
+      <c r="B162" s="4"/>
+      <c r="C162" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D160" s="5" t="s">
+      <c r="D162" s="5" t="s">
         <v>605</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B161" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C161" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C162" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1">
       <c r="A163" s="30" t="s">
-        <v>718</v>
-      </c>
-      <c r="B163" s="48" t="s">
-        <v>720</v>
+        <v>315</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>316</v>
       </c>
       <c r="C163" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="D163" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1">
       <c r="A164" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C164" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A165" s="30" t="s">
+        <v>718</v>
+      </c>
+      <c r="B165" s="48" t="s">
+        <v>720</v>
+      </c>
+      <c r="C165" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A166" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B164" s="35" t="s">
+      <c r="B166" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="C164" s="30" t="s">
+      <c r="C166" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="30" customHeight="1">
-      <c r="A166" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B166" s="5"/>
-      <c r="C166" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1">
       <c r="A167" s="16" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="30" customHeight="1">
+      <c r="A168" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B168" s="5"/>
+      <c r="C168" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A169" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B169" s="5"/>
+      <c r="C169" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="D169" s="5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A168" s="30" t="s">
+    <row r="170" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A170" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B168" s="2"/>
-      <c r="C168" s="30" t="s">
+      <c r="B170" s="2"/>
+      <c r="C170" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="38" t="s">
+    <row r="171" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A171" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B169" s="39"/>
-      <c r="C169" s="40" t="s">
+      <c r="B171" s="39"/>
+      <c r="C171" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="D169" s="11" t="s">
+      <c r="D171" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="16" t="s">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A172" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="B170" s="5"/>
-      <c r="C170" s="16" t="s">
+      <c r="B172" s="5"/>
+      <c r="C172" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D172" s="5" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="16" t="s">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A173" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="B171" s="5"/>
-      <c r="C171" s="16" t="s">
+      <c r="B173" s="5"/>
+      <c r="C173" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="D171" s="5" t="s">
+      <c r="D173" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="30" t="s">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A174" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="B172" s="2"/>
-      <c r="C172" s="30" t="s">
+      <c r="B174" s="2"/>
+      <c r="C174" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D174" s="2" t="s">
         <v>603</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B173" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="C173" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B174" s="26"/>
-      <c r="C174" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D174" s="14" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1">
       <c r="A175" s="30" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B175" s="35" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C175" s="30" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1">
       <c r="A176" s="31" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B176" s="26"/>
       <c r="C176" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B177" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="C177" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A178" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B178" s="26"/>
+      <c r="C178" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="D176" s="14" t="s">
+      <c r="D178" s="14" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="31" t="s">
+    <row r="179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A179" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="B177" s="26"/>
-      <c r="C177" s="31" t="s">
+      <c r="B179" s="26"/>
+      <c r="C179" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="D177" s="14" t="s">
+      <c r="D179" s="14" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B178" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="C178" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B179" s="35"/>
-      <c r="C179" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
       <c r="A180" s="30" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B180" s="35" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C180" s="30" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A181" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B181" s="4"/>
-      <c r="C181" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>378</v>
+      <c r="A181" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B181" s="35"/>
+      <c r="C181" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B182" s="35" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C182" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A183" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B183" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>386</v>
+      <c r="A183" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B183" s="4"/>
+      <c r="C183" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1">
       <c r="A184" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B184" s="3"/>
+        <v>379</v>
+      </c>
+      <c r="B184" s="35" t="s">
+        <v>380</v>
+      </c>
       <c r="C184" s="30" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>584</v>
+        <v>382</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
       <c r="A185" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="B185" s="3"/>
+        <v>383</v>
+      </c>
+      <c r="B185" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C185" s="30" t="s">
-        <v>663</v>
+        <v>385</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>690</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
       <c r="A186" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="B186" s="3"/>
+      <c r="C186" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A187" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B187" s="3"/>
+      <c r="C187" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A188" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="B186" s="35" t="s">
+      <c r="B188" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="C186" s="30" t="s">
+      <c r="C188" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="D188" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="44" t="s">
+    <row r="189" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A189" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="B187" s="59" t="s">
+      <c r="B189" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="C187" s="7" t="s">
+      <c r="C189" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D187" s="7" t="s">
+      <c r="D189" s="7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="38" t="s">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A190" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="B188" s="39"/>
-      <c r="C188" s="40" t="s">
+      <c r="B190" s="39"/>
+      <c r="C190" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="D188" s="11" t="s">
+      <c r="D190" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="31" t="s">
+    <row r="191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A191" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B191" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="31" t="s">
+      <c r="C191" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="D189" s="6" t="s">
+      <c r="D191" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="30" t="s">
+    <row r="192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A192" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="B190" s="3"/>
-      <c r="C190" s="30" t="s">
+      <c r="B192" s="3"/>
+      <c r="C192" s="30" t="s">
         <v>492</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="D192" s="2" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="52" t="s">
+    <row r="193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A193" s="52" t="s">
         <v>403</v>
       </c>
-      <c r="B191" s="53" t="s">
+      <c r="B193" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="C191" s="54" t="s">
+      <c r="C193" s="54" t="s">
         <v>405</v>
       </c>
-      <c r="D191" s="21" t="s">
+      <c r="D193" s="21" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="52" t="s">
+    <row r="194" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A194" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B192" s="39"/>
-      <c r="C192" s="54" t="s">
+      <c r="B194" s="39"/>
+      <c r="C194" s="54" t="s">
         <v>408</v>
       </c>
-      <c r="D192" s="21" t="s">
+      <c r="D194" s="21" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="55" t="s">
+    <row r="195" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A195" s="55" t="s">
         <v>409</v>
       </c>
-      <c r="B193" s="4"/>
-      <c r="C193" s="55" t="s">
+      <c r="B195" s="4"/>
+      <c r="C195" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="D193" s="9" t="s">
+      <c r="D195" s="9" t="s">
         <v>586</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A194" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B194" s="2"/>
-      <c r="C194" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A195" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B195" s="2"/>
-      <c r="C195" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="30" t="s">
-        <v>743</v>
+        <v>411</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="30" t="s">
-        <v>744</v>
-      </c>
-      <c r="D196" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1">
       <c r="A197" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>416</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="B197" s="2"/>
       <c r="C197" s="30" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>418</v>
+        <v>588</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A198" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="B198" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="C198" s="56" t="s">
-        <v>421</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>422</v>
-      </c>
+      <c r="A198" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="30" t="s">
+        <v>744</v>
+      </c>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1">
       <c r="A199" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C199" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A200" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B200" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C200" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A201" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="B199" s="2"/>
-      <c r="C199" s="30" t="s">
+      <c r="B201" s="2"/>
+      <c r="C201" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D201" s="2" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A200" s="16" t="s">
+    <row r="202" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A202" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B202" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C200" s="16" t="s">
+      <c r="C202" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="D200" s="33" t="s">
+      <c r="D202" s="33" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A201" s="16" t="s">
+    <row r="203" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A203" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B203" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C201" s="16" t="s">
+      <c r="C203" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="D201" s="5" t="s">
+      <c r="D203" s="5" t="s">
         <v>432</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A202" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B202" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="C202" s="30" t="s">
-        <v>583</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A203" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C203" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1">
       <c r="A204" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
+      </c>
+      <c r="B204" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="C204" s="30" t="s">
-        <v>442</v>
+        <v>583</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1">
       <c r="A205" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B205" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>437</v>
+      </c>
       <c r="C205" s="30" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>590</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1">
       <c r="A206" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C206" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A207" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B207" s="2"/>
+      <c r="C207" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A208" s="30" t="s">
         <v>446</v>
       </c>
-      <c r="B206" s="2"/>
-      <c r="C206" s="30" t="s">
+      <c r="B208" s="2"/>
+      <c r="C208" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="D208" s="2" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A207" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B207" s="14"/>
-      <c r="C207" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D207" s="14" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A208" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B208" s="14"/>
-      <c r="C208" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="D208" s="14" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1">
       <c r="A209" s="31" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B209" s="14"/>
       <c r="C209" s="31" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>558</v>
+        <v>664</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1">
       <c r="A210" s="31" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B210" s="14"/>
       <c r="C210" s="31" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1">
       <c r="A211" s="31" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B211" s="14"/>
       <c r="C211" s="31" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1">
       <c r="A212" s="31" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B212" s="14"/>
       <c r="C212" s="31" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1">
       <c r="A213" s="31" t="s">
-        <v>748</v>
-      </c>
-      <c r="B213" s="14" t="s">
-        <v>747</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="B213" s="14"/>
       <c r="C213" s="31" t="s">
-        <v>746</v>
-      </c>
-      <c r="D213" s="62"/>
+        <v>563</v>
+      </c>
+      <c r="D213" s="14" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1">
       <c r="A214" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B214" s="14"/>
+      <c r="C214" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D214" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A215" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="B215" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="C215" s="31" t="s">
+        <v>746</v>
+      </c>
+      <c r="D215" s="62"/>
+    </row>
+    <row r="216" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A216" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="B214" s="48" t="s">
+      <c r="B216" s="48" t="s">
         <v>498</v>
       </c>
-      <c r="C214" s="31" t="s">
+      <c r="C216" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="D214" s="14" t="s">
+      <c r="D216" s="14" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A215" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C215" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D215" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A216" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B216" s="4"/>
-      <c r="C216" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="D216" s="5"/>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1">
       <c r="A217" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C217" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A218" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D218" s="5"/>
+    </row>
+    <row r="219" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A219" s="16" t="s">
         <v>645</v>
       </c>
-      <c r="B217" s="4"/>
-      <c r="C217" s="16" t="s">
+      <c r="B219" s="4"/>
+      <c r="C219" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D217" s="5" t="s">
+      <c r="D219" s="5" t="s">
         <v>689</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A218" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C218" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A219" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="B219" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D219" s="7" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1">
       <c r="A220" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C220" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A221" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A222" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B222" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C220" s="30" t="s">
+      <c r="C222" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="D222" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A221" s="16" t="s">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A223" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B221" s="20"/>
-      <c r="C221" s="16" t="s">
+      <c r="B223" s="20"/>
+      <c r="C223" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D221" s="5" t="s">
+      <c r="D223" s="5" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A222" s="31" t="s">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A224" s="31" t="s">
         <v>568</v>
       </c>
-      <c r="B222" s="6" t="s">
+      <c r="B224" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="C222" s="31" t="s">
+      <c r="C224" s="31" t="s">
         <v>570</v>
       </c>
-      <c r="D222" s="6" t="s">
+      <c r="D224" s="6" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A223" s="31" t="s">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A225" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B223" s="6" t="s">
+      <c r="B225" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C223" s="31" t="s">
+      <c r="C225" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D223" s="6" t="s">
+      <c r="D225" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A224" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B224" s="20"/>
-      <c r="C224" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D224" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A225" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="B225" s="20"/>
-      <c r="C225" s="16" t="s">
-        <v>652</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1">
       <c r="A226" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="B226" s="20"/>
+      <c r="C226" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A227" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B227" s="20"/>
+      <c r="C227" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A228" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B226" s="20" t="s">
+      <c r="B228" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C226" s="16" t="s">
+      <c r="C228" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D226" s="5" t="s">
+      <c r="D228" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="16" t="s">
+    <row r="229" spans="1:4">
+      <c r="A229" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B229" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C227" s="16" t="s">
+      <c r="C229" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D227" s="5" t="s">
+      <c r="D229" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A228" s="30" t="s">
+    <row r="230" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A230" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B230" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C228" s="30" t="s">
+      <c r="C230" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="D230" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A229" s="30" t="s">
+    <row r="231" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A231" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="30" t="s">
+      <c r="B231" s="3"/>
+      <c r="C231" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D229" s="2"/>
-    </row>
-    <row r="230" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A230" s="2" t="s">
+      <c r="D231" s="2"/>
+    </row>
+    <row r="232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A232" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B232" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C232" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D232" s="2" t="s">
         <v>487</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A231" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B231" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A232" s="58" t="s">
-        <v>478</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="C232" s="31" t="s">
-        <v>480</v>
-      </c>
-      <c r="D232" s="6" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1">
       <c r="A233" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B233" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A234" s="58" t="s">
+        <v>478</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C234" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A235" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B235" t="s">
         <v>786</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C235" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="235" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="236" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="237" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="238" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7625,162 +7726,166 @@
     <row r="1160" ht="15.75" customHeight="1"/>
     <row r="1161" ht="15.75" customHeight="1"/>
     <row r="1162" ht="15.75" customHeight="1"/>
+    <row r="1163" ht="15.75" customHeight="1"/>
+    <row r="1164" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B13" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B227" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D23" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B25" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B28" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B29" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B33" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B34" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B35" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D35" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B36" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B37" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B39" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B43" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D43" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B44" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B49" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B51" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B53" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B57" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D57" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B58" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B60" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D60" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B61" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B62" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B63" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B65" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B66" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B67" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B68" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B69" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B71" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B72" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B73" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B74" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B75" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B76" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D76" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B77" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B79" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B85" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D88" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B93" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D93" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B94" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D94" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B97" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B100" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D100" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B102" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B103" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B110" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D110" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B111" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B113" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B114" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B123" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B124" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B125" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B127" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B138" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B144" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B148" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B151" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B152" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B153" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D153" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B155" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B158" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B159" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D159" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B161" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B162" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B164" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B173" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B175" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B178" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B180" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B182" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B183" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B186" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B187" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B189" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D189" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B191" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B197" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B198" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B200" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D200" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B201" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B202" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B203" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B204" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B215" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B218" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B219" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B220" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B150" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B228" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B70" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B230" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B231" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B101" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B128" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B214" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B229" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D20" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D25" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B27" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B30" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B31" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B35" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B36" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B37" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D37" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B38" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B39" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B41" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B22" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B45" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D45" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B46" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B51" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B53" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B55" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B58" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B62" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D62" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B63" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B64" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B65" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B67" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B68" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B69" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B70" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B71" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B73" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B74" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D78" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B79" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B87" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D90" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B95" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D95" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B96" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D96" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B99" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B102" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D102" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B104" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B105" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B112" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D112" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B113" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B115" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B116" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B125" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B126" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B127" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B129" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B140" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B146" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B150" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B153" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B154" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B155" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D155" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B157" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B160" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B161" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D161" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B163" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B164" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B166" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B175" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B177" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B180" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B182" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B184" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B185" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B188" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B189" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B191" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D191" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B193" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B199" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B200" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B202" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D202" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B203" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B204" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B205" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B206" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B217" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B220" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B221" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B222" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B152" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B230" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B72" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B232" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B233" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B103" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B130" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B216" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B41" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D41" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B80" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D80" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B91" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D91" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B95" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D95" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B96" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D96" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B120" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B222" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D222" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B223" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D223" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B232" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D232" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B22" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B17" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B64" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B26" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B43" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D43" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B82" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D82" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B93" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D93" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B97" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D97" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B98" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D98" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B122" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B224" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D224" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B225" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D225" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B234" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D234" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B24" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B19" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B66" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B28" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
     <hyperlink ref="B7" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="B3" r:id="rId139" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
-    <hyperlink ref="B89" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B88" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B86" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
-    <hyperlink ref="B59" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
-    <hyperlink ref="B52" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B163" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
-    <hyperlink ref="B87" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B136" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B117" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B91" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B90" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B88" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B61" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B54" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B165" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B89" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B138" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B119" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
     <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
+    <hyperlink ref="B12" r:id="rId150" xr:uid="{43DC6B56-B3E7-0644-A678-35C18F005640}"/>
+    <hyperlink ref="B14" r:id="rId151" xr:uid="{96D8BA99-5A2C-084E-8DE9-B98A7ADF8C44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId150"/>
+    <tablePart r:id="rId152"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A35CA3C-6911-6F44-9734-6E6C323F1446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2B7B9F-6566-1847-A6F7-E52CEC005042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="800">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -3003,6 +3003,12 @@
   </si>
   <si>
     <t>&lt;orgName key="CCzarnikow" ref="https://d-nb.info/gnd/270174-1"&gt;</t>
+  </si>
+  <si>
+    <t>Slovenski Jug</t>
+  </si>
+  <si>
+    <t>SlovenskiJug</t>
   </si>
 </sst>
 </file>
@@ -3449,7 +3455,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D228" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D229" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3658,7 +3664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1164"/>
+  <dimension ref="A1:Z1165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -5602,7 +5608,7 @@
       <c r="A142" s="16" t="s">
         <v>647</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="59" t="s">
         <v>650</v>
       </c>
       <c r="C142" s="16" t="s">
@@ -6578,228 +6584,237 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1">
       <c r="A219" s="16" t="s">
-        <v>645</v>
+        <v>798</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="D219" s="5"/>
+    </row>
+    <row r="220" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A220" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D219" s="5" t="s">
+      <c r="D220" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A220" s="30" t="s">
+    <row r="221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A221" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B221" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C220" s="30" t="s">
+      <c r="C221" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="D221" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A221" s="7" t="s">
+    <row r="222" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A222" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B222" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C221" s="7" t="s">
+      <c r="C222" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D221" s="7" t="s">
+      <c r="D222" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A222" s="30" t="s">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A223" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B223" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C222" s="30" t="s">
+      <c r="C223" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="D223" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A223" s="16" t="s">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A224" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B223" s="20"/>
-      <c r="C223" s="16" t="s">
+      <c r="B224" s="20"/>
+      <c r="C224" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D223" s="5" t="s">
+      <c r="D224" s="5" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A224" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C224" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1">
       <c r="A225" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C225" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A226" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B225" s="6" t="s">
+      <c r="B226" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C225" s="31" t="s">
+      <c r="C226" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D225" s="6" t="s">
+      <c r="D226" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A226" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B226" s="20"/>
-      <c r="C226" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1">
       <c r="A227" s="16" t="s">
-        <v>651</v>
+        <v>476</v>
       </c>
       <c r="B227" s="20"/>
       <c r="C227" s="16" t="s">
-        <v>652</v>
+        <v>477</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1">
       <c r="A228" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B228" s="20"/>
+      <c r="C228" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A229" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B228" s="20" t="s">
+      <c r="B229" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C228" s="16" t="s">
+      <c r="C229" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D228" s="5" t="s">
+      <c r="D229" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
-      <c r="A229" s="16" t="s">
+    <row r="230" spans="1:4">
+      <c r="A230" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B230" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C229" s="16" t="s">
+      <c r="C230" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D229" s="5" t="s">
+      <c r="D230" s="5" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A230" s="30" t="s">
-        <v>684</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C230" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1">
       <c r="A231" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C231" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A232" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B231" s="3"/>
-      <c r="C231" s="30" t="s">
+      <c r="B232" s="3"/>
+      <c r="C232" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D231" s="2"/>
-    </row>
-    <row r="232" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A232" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>487</v>
-      </c>
+      <c r="D232" s="2"/>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1">
       <c r="A233" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A234" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B233" s="35" t="s">
+      <c r="B234" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C234" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="D234" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A234" s="58" t="s">
+    <row r="235" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A235" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B234" s="6" t="s">
+      <c r="B235" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C234" s="31" t="s">
+      <c r="C235" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D234" s="6" t="s">
+      <c r="D235" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A235" s="2" t="s">
+    <row r="236" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A236" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B236" t="s">
         <v>786</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C236" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="237" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="238" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="239" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7728,11 +7743,12 @@
     <row r="1162" ht="15.75" customHeight="1"/>
     <row r="1163" ht="15.75" customHeight="1"/>
     <row r="1164" ht="15.75" customHeight="1"/>
+    <row r="1165" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B229" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B230" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D20" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -7832,14 +7848,14 @@
     <hyperlink ref="B205" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
     <hyperlink ref="B206" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
     <hyperlink ref="B217" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B220" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B221" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B222" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B221" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B222" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B223" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
     <hyperlink ref="B152" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B230" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B231" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
     <hyperlink ref="B72" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B232" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B233" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B233" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B234" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
     <hyperlink ref="B103" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
     <hyperlink ref="B130" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
     <hyperlink ref="B216" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
@@ -7857,12 +7873,12 @@
     <hyperlink ref="B98" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
     <hyperlink ref="D98" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
     <hyperlink ref="B122" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B224" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D224" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B225" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D225" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B234" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D234" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B225" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D225" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B226" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D226" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B235" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D235" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B24" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
     <hyperlink ref="B19" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
     <hyperlink ref="B66" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
@@ -7881,11 +7897,12 @@
     <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
     <hyperlink ref="B12" r:id="rId150" xr:uid="{43DC6B56-B3E7-0644-A678-35C18F005640}"/>
     <hyperlink ref="B14" r:id="rId151" xr:uid="{96D8BA99-5A2C-084E-8DE9-B98A7ADF8C44}"/>
+    <hyperlink ref="B142" r:id="rId152" xr:uid="{3C7F0CC8-6291-B845-8271-16779E9DCE6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId152"/>
+    <tablePart r:id="rId153"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2B7B9F-6566-1847-A6F7-E52CEC005042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52796B14-51F5-2841-BD02-1DAF6FDBD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="803">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -3009,6 +3009,15 @@
   </si>
   <si>
     <t>SlovenskiJug</t>
+  </si>
+  <si>
+    <t>Schichau-Werke</t>
+  </si>
+  <si>
+    <t>SchichauWerke</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/7518596-9</t>
   </si>
 </sst>
 </file>
@@ -3455,7 +3464,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D229" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D230" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3664,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1165"/>
+  <dimension ref="A1:Z1166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -6559,263 +6568,274 @@
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A217" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C217" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>454</v>
-      </c>
+      <c r="A217" s="31" t="s">
+        <v>800</v>
+      </c>
+      <c r="B217" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="C217" s="31" t="s">
+        <v>801</v>
+      </c>
+      <c r="D217" s="14"/>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1">
       <c r="A218" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B218" s="4"/>
+        <v>451</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="C218" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="D218" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1">
       <c r="A219" s="16" t="s">
-        <v>798</v>
+        <v>730</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="16" t="s">
-        <v>799</v>
+        <v>731</v>
       </c>
       <c r="D219" s="5"/>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1">
       <c r="A220" s="16" t="s">
-        <v>645</v>
+        <v>798</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="D220" s="5"/>
+    </row>
+    <row r="221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A221" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D220" s="5" t="s">
+      <c r="D221" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A221" s="30" t="s">
+    <row r="222" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A222" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B222" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C221" s="30" t="s">
+      <c r="C222" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="D222" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A222" s="7" t="s">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A223" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B223" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C222" s="7" t="s">
+      <c r="C223" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D222" s="7" t="s">
+      <c r="D223" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A223" s="30" t="s">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A224" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B224" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C223" s="30" t="s">
+      <c r="C224" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="D224" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A224" s="16" t="s">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A225" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B224" s="20"/>
-      <c r="C224" s="16" t="s">
+      <c r="B225" s="20"/>
+      <c r="C225" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D224" s="5" t="s">
+      <c r="D225" s="5" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A225" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C225" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D225" s="6" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1">
       <c r="A226" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C226" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A227" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B226" s="6" t="s">
+      <c r="B227" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C226" s="31" t="s">
+      <c r="C227" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D226" s="6" t="s">
+      <c r="D227" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A227" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B227" s="20"/>
-      <c r="C227" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1">
       <c r="A228" s="16" t="s">
-        <v>651</v>
+        <v>476</v>
       </c>
       <c r="B228" s="20"/>
       <c r="C228" s="16" t="s">
-        <v>652</v>
+        <v>477</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1">
       <c r="A229" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B229" s="20"/>
+      <c r="C229" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A230" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B229" s="20" t="s">
+      <c r="B230" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C229" s="16" t="s">
+      <c r="C230" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D229" s="5" t="s">
+      <c r="D230" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="16" t="s">
+    <row r="231" spans="1:4">
+      <c r="A231" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B231" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C230" s="16" t="s">
+      <c r="C231" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D231" s="5" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A231" s="30" t="s">
-        <v>684</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C231" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1">
       <c r="A232" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C232" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A233" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B232" s="3"/>
-      <c r="C232" s="30" t="s">
+      <c r="B233" s="3"/>
+      <c r="C233" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D232" s="2"/>
-    </row>
-    <row r="233" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A233" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>487</v>
-      </c>
+      <c r="D233" s="2"/>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1">
       <c r="A234" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A235" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B234" s="35" t="s">
+      <c r="B235" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C235" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="D235" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A235" s="58" t="s">
+    <row r="236" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A236" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B235" s="6" t="s">
+      <c r="B236" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C235" s="31" t="s">
+      <c r="C236" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D235" s="6" t="s">
+      <c r="D236" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A236" s="2" t="s">
+    <row r="237" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A237" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B237" t="s">
         <v>786</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="238" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="239" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="240" spans="1:4" ht="15.75" customHeight="1"/>
@@ -7744,11 +7764,12 @@
     <row r="1163" ht="15.75" customHeight="1"/>
     <row r="1164" ht="15.75" customHeight="1"/>
     <row r="1165" ht="15.75" customHeight="1"/>
+    <row r="1166" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B230" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B231" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D20" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -7847,62 +7868,63 @@
     <hyperlink ref="B204" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
     <hyperlink ref="B205" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
     <hyperlink ref="B206" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B217" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B221" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B222" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B223" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B152" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B231" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B72" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B233" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B234" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B103" r:id="rId111" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B130" r:id="rId112" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B216" r:id="rId113" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
-    <hyperlink ref="D7" r:id="rId114" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
-    <hyperlink ref="B9" r:id="rId115" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
-    <hyperlink ref="D9" r:id="rId116" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B43" r:id="rId117" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D43" r:id="rId118" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B82" r:id="rId119" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D82" r:id="rId120" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B93" r:id="rId121" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D93" r:id="rId122" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B97" r:id="rId123" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D97" r:id="rId124" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B98" r:id="rId125" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D98" r:id="rId126" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B122" r:id="rId127" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B225" r:id="rId128" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D225" r:id="rId129" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B226" r:id="rId130" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D226" r:id="rId131" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B235" r:id="rId132" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D235" r:id="rId133" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B24" r:id="rId134" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B19" r:id="rId135" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B66" r:id="rId136" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B28" r:id="rId137" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
-    <hyperlink ref="B7" r:id="rId138" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
-    <hyperlink ref="B3" r:id="rId139" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
-    <hyperlink ref="B91" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B90" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B88" r:id="rId142" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
-    <hyperlink ref="B61" r:id="rId143" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
-    <hyperlink ref="B54" r:id="rId144" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B165" r:id="rId145" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
-    <hyperlink ref="B89" r:id="rId146" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B138" r:id="rId147" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B119" r:id="rId148" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
-    <hyperlink ref="B5" r:id="rId149" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
-    <hyperlink ref="B12" r:id="rId150" xr:uid="{43DC6B56-B3E7-0644-A678-35C18F005640}"/>
-    <hyperlink ref="B14" r:id="rId151" xr:uid="{96D8BA99-5A2C-084E-8DE9-B98A7ADF8C44}"/>
-    <hyperlink ref="B142" r:id="rId152" xr:uid="{3C7F0CC8-6291-B845-8271-16779E9DCE6A}"/>
+    <hyperlink ref="B222" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B223" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B224" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B152" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B232" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B72" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B234" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B235" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B103" r:id="rId110" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B130" r:id="rId111" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B216" r:id="rId112" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="D7" r:id="rId113" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
+    <hyperlink ref="B9" r:id="rId114" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
+    <hyperlink ref="D9" r:id="rId115" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
+    <hyperlink ref="B43" r:id="rId116" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D43" r:id="rId117" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B82" r:id="rId118" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D82" r:id="rId119" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B93" r:id="rId120" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D93" r:id="rId121" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B97" r:id="rId122" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D97" r:id="rId123" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B98" r:id="rId124" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D98" r:id="rId125" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B122" r:id="rId126" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B226" r:id="rId127" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D226" r:id="rId128" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B227" r:id="rId129" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D227" r:id="rId130" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B236" r:id="rId131" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D236" r:id="rId132" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B24" r:id="rId133" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B19" r:id="rId134" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B66" r:id="rId135" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B28" r:id="rId136" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B7" r:id="rId137" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
+    <hyperlink ref="B3" r:id="rId138" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
+    <hyperlink ref="B91" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B90" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B88" r:id="rId141" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B61" r:id="rId142" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B54" r:id="rId143" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B165" r:id="rId144" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B89" r:id="rId145" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B138" r:id="rId146" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B119" r:id="rId147" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B5" r:id="rId148" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
+    <hyperlink ref="B12" r:id="rId149" xr:uid="{43DC6B56-B3E7-0644-A678-35C18F005640}"/>
+    <hyperlink ref="B14" r:id="rId150" xr:uid="{96D8BA99-5A2C-084E-8DE9-B98A7ADF8C44}"/>
+    <hyperlink ref="B142" r:id="rId151" xr:uid="{3C7F0CC8-6291-B845-8271-16779E9DCE6A}"/>
+    <hyperlink ref="B218" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B217" r:id="rId153" tooltip="https://d-nb.info/gnd/7518596-9" xr:uid="{B6754BE5-59A2-9D40-8AF2-E7F344761281}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId153"/>
+    <tablePart r:id="rId154"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52796B14-51F5-2841-BD02-1DAF6FDBD7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF49199-9F95-C24E-877D-D37847C3C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="864">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -3005,19 +3005,202 @@
     <t>&lt;orgName key="CCzarnikow" ref="https://d-nb.info/gnd/270174-1"&gt;</t>
   </si>
   <si>
-    <t>Slovenski Jug</t>
-  </si>
-  <si>
-    <t>SlovenskiJug</t>
-  </si>
-  <si>
-    <t>Schichau-Werke</t>
-  </si>
-  <si>
-    <t>SchichauWerke</t>
-  </si>
-  <si>
-    <t>https://d-nb.info/gnd/7518596-9</t>
+    <t>Children's Aid Society</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/263170-2</t>
+  </si>
+  <si>
+    <t>ChildrensAidSociety</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="ChildrensAidSociety" ref="https://d-nb.info/gnd/263170-2"&gt;</t>
+  </si>
+  <si>
+    <t>Gaiety Theatre London</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/3002172-8</t>
+  </si>
+  <si>
+    <t>GaietyTheatre</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="GaietyTheatre" ref="https://d-nb.info/gnd/3002172-8"&gt;</t>
+  </si>
+  <si>
+    <t>German Aid Society</t>
+  </si>
+  <si>
+    <t>GermanAidSociety</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="GermanAidSociety"&gt;</t>
+  </si>
+  <si>
+    <t>Hamburg-Amerikanische Packetfahrt-Actien-Gesellschaft</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/24169-6</t>
+  </si>
+  <si>
+    <t>HamburgAmerikaLinie </t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HamburgAmerikaLinie " ref="https://d-nb.info/gnd/24169-6"&gt;</t>
+  </si>
+  <si>
+    <t>Hof- und Staatsdruckerei</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/610064-8</t>
+  </si>
+  <si>
+    <t>HofundStaatsdruckerei</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HofundStaatsdruckerei" ref="https://d-nb.info/gnd/610064-8"&gt;</t>
+  </si>
+  <si>
+    <t>Hotel Frontenac</t>
+  </si>
+  <si>
+    <t>HotelFrontenac</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HotelFrontenac"&gt;</t>
+  </si>
+  <si>
+    <t>Hotel Waldorf-Astoria</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4286031-3</t>
+  </si>
+  <si>
+    <t>HotelWaldorfAstoria</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HotelWaldorfAstoria" ref="https://d-nb.info/gnd/4286031-3"&gt;</t>
+  </si>
+  <si>
+    <t>John Worthy School </t>
+  </si>
+  <si>
+    <t>JohnWorthySchool</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="JohnWorthySchool"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="KaufmannschaftBelgrad"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HandelskammerBelgrad"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="HandelskammerSofia"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Louvre" ref="https://d-nb.info/gnd/1006837-5"&gt;</t>
+  </si>
+  <si>
+    <t>Massachusetts General Hospital</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1042702-8</t>
+  </si>
+  <si>
+    <t>MassachusettsGeneralHospital</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="MassachusettsGeneralHospital" ref="https://d-nb.info/gnd/1042702-8"&gt;</t>
+  </si>
+  <si>
+    <t>Ministerien/Finanzministerium Ungarn </t>
+  </si>
+  <si>
+    <t>FinanzministeriumUngarn </t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/270768-8</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="FinanzministeriumUngarn " ref="https://d-nb.info/gnd/270768-8"&gt;</t>
+  </si>
+  <si>
+    <t>Mr. Theoret law publishers</t>
+  </si>
+  <si>
+    <t>MrTheoretlawpublishers</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="MrTheoretlawpublishers"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/Daily Telegraph</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/6006746-9</t>
+  </si>
+  <si>
+    <t>DailyTelegraph</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="DailyTelegraph" ref="https://d-nb.info/gnd/6006746-9"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Temps" ref="https://d-nb.info/gnd/7729567-5"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/L'Indépendance Belge</t>
+  </si>
+  <si>
+    <t>LIndependanceBelge</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="LIndependanceBelge"&gt;</t>
+  </si>
+  <si>
+    <t>Presse/Scribner’s Magazine</t>
+  </si>
+  <si>
+    <t>ScribnersMagazine</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="ScribnersMagazine"&gt;</t>
+  </si>
+  <si>
+    <t>Reichskanzlei</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/4049146-8</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="Reichskanzlei" ref="https://d-nb.info/gnd/4049146-8"&gt;</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/37246-8</t>
+  </si>
+  <si>
+    <t>UniversityPennsylvania</t>
+  </si>
+  <si>
+    <t>Universitäten/University of Pennsylvania</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="UniversityPennsylvania" ref="https://d-nb.info/gnd/37246-8"&gt;</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/1014349-X</t>
+  </si>
+  <si>
+    <t>UniversitaetZagreb</t>
+  </si>
+  <si>
+    <t>Universitäten/Universität Zagreb</t>
+  </si>
+  <si>
+    <t>&lt;orgName key="UniversitaetZagreb" ref="https://d-nb.info/gnd/1014349-X"&gt;</t>
   </si>
 </sst>
 </file>
@@ -3464,7 +3647,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D230" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D244" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3673,7 +3856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1166"/>
+  <dimension ref="A1:Z1182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -3906,2955 +4089,3543 @@
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="A15" s="63" t="s">
+        <v>798</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>799</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>800</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>801</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="16" t="s">
         <v>610</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C17" s="16" t="s">
         <v>612</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="16" t="s">
+    <row r="18" spans="1:25">
+      <c r="A18" s="16" t="s">
         <v>653</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C18" s="16" t="s">
         <v>654</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="16" t="s">
+    <row r="19" spans="1:25">
+      <c r="A19" s="16" t="s">
         <v>657</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C19" s="16" t="s">
         <v>659</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="16" t="s">
+    <row r="20" spans="1:25">
+      <c r="A20" s="16" t="s">
         <v>633</v>
       </c>
-      <c r="B19" s="59" t="s">
+      <c r="B20" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C20" s="16" t="s">
         <v>631</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="31" t="s">
+    <row r="21" spans="1:25">
+      <c r="A21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B21" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="31" t="s">
+    <row r="22" spans="1:25">
+      <c r="A22" s="31" t="s">
         <v>626</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B22" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C22" s="31" t="s">
         <v>627</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="16" t="s">
+    <row r="23" spans="1:25">
+      <c r="A23" s="16" t="s">
         <v>630</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D23" s="33" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="16" t="s">
+    <row r="24" spans="1:25">
+      <c r="A24" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D24" s="33" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="31" t="s">
+    <row r="25" spans="1:25">
+      <c r="A25" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="B24" s="60" t="s">
+      <c r="B25" s="60" t="s">
         <v>617</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C25" s="31" t="s">
         <v>679</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="31" t="s">
+    <row r="26" spans="1:25">
+      <c r="A26" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B26" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C26" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="31" t="s">
+    <row r="27" spans="1:25">
+      <c r="A27" s="31" t="s">
         <v>765</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="31" t="s">
+      <c r="B27" s="32"/>
+      <c r="C27" s="31" t="s">
         <v>766</v>
       </c>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="16" t="s">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="63" t="s">
+        <v>802</v>
+      </c>
+      <c r="B28" s="64" t="s">
+        <v>803</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>804</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>805</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="16" t="s">
+    <row r="30" spans="1:25">
+      <c r="A30" s="16" t="s">
         <v>606</v>
       </c>
-      <c r="B28" s="59" t="s">
+      <c r="B30" s="59" t="s">
         <v>608</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>607</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="16" t="s">
+    <row r="31" spans="1:25">
+      <c r="A31" s="63" t="s">
+        <v>806</v>
+      </c>
+      <c r="B31" s="65"/>
+      <c r="C31" s="63" t="s">
+        <v>807</v>
+      </c>
+      <c r="D31" s="65" t="s">
+        <v>808</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="16" t="s">
         <v>622</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>624</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="30" t="s">
+    <row r="33" spans="1:25">
+      <c r="A33" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C33" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="16" t="s">
+    <row r="34" spans="1:25">
+      <c r="A34" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="16" t="s">
+    <row r="35" spans="1:25">
+      <c r="A35" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="16" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="16" t="s">
+    <row r="36" spans="1:25">
+      <c r="A36" s="16" t="s">
         <v>709</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="16" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="16" t="s">
         <v>739</v>
       </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="16" t="s">
+      <c r="D36" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" s="16" t="s">
         <v>710</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="16" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="16" t="s">
         <v>740</v>
       </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="16" t="s">
+      <c r="D37" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
+      <c r="A38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="16" t="s">
+    <row r="39" spans="1:25">
+      <c r="A39" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="31" t="s">
+    <row r="40" spans="1:25">
+      <c r="A40" s="63" t="s">
+        <v>809</v>
+      </c>
+      <c r="B40" s="64" t="s">
+        <v>810</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>811</v>
+      </c>
+      <c r="D40" s="65" t="s">
+        <v>812</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="A41" s="63" t="s">
+        <v>813</v>
+      </c>
+      <c r="B41" s="64" t="s">
+        <v>814</v>
+      </c>
+      <c r="C41" s="63" t="s">
+        <v>815</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>816</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="A42" s="63" t="s">
+        <v>817</v>
+      </c>
+      <c r="B42" s="65"/>
+      <c r="C42" s="63" t="s">
+        <v>818</v>
+      </c>
+      <c r="D42" s="65" t="s">
+        <v>819</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B43" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C43" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="30" t="s">
+    <row r="44" spans="1:25">
+      <c r="A44" s="63" t="s">
+        <v>820</v>
+      </c>
+      <c r="B44" s="64" t="s">
+        <v>821</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>822</v>
+      </c>
+      <c r="D44" s="65" t="s">
+        <v>823</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C45" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="16">
-      <c r="A39" s="7" t="s">
+    <row r="46" spans="1:25" ht="16">
+      <c r="A46" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B46" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D46" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="16">
-      <c r="A40" s="7" t="s">
+    <row r="47" spans="1:25" ht="16">
+      <c r="A47" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B47" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="16" t="s">
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:25">
+      <c r="A48" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="16" t="s">
+    <row r="49" spans="1:25">
+      <c r="A49" s="63" t="s">
+        <v>824</v>
+      </c>
+      <c r="B49" s="65"/>
+      <c r="C49" s="63" t="s">
+        <v>825</v>
+      </c>
+      <c r="D49" s="65" t="s">
+        <v>826</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="2"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2"/>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" s="16" t="s">
         <v>741</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="16" t="s">
+      <c r="B50" s="4"/>
+      <c r="C50" s="16" t="s">
         <v>742</v>
       </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="31" t="s">
+      <c r="D50" s="5" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" s="31" t="s">
         <v>522</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C51" s="31" t="s">
         <v>521</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D51" s="6" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="31" t="s">
+    <row r="52" spans="1:25">
+      <c r="A52" s="31" t="s">
         <v>665</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B52" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C52" s="31" t="s">
         <v>667</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D52" s="6" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="31" t="s">
+    <row r="53" spans="1:25">
+      <c r="A53" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="C53" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D53" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="30" t="s">
+    <row r="54" spans="1:25">
+      <c r="A54" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C54" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A47" s="30" t="s">
+    <row r="55" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A55" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="30" t="s">
+      <c r="B55" s="2"/>
+      <c r="C55" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A48" s="30" t="s">
+    <row r="56" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A56" s="30" t="s">
         <v>759</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C56" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A49" s="30" t="s">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A57" s="30" t="s">
         <v>668</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C57" s="30" t="s">
         <v>471</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A50" s="30" t="s">
+    <row r="58" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A58" s="30" t="s">
         <v>770</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="30" t="s">
+      <c r="B58" s="2"/>
+      <c r="C58" s="30" t="s">
         <v>771</v>
       </c>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="9" t="s">
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="34" t="s">
+      <c r="B59" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C59" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D59" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="9" t="s">
+    <row r="60" spans="1:25">
+      <c r="A60" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="9" t="s">
+      <c r="B60" s="34"/>
+      <c r="C60" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D60" s="9" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="30" t="s">
+    <row r="61" spans="1:25">
+      <c r="A61" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B61" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C61" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="30" t="s">
+    <row r="62" spans="1:25">
+      <c r="A62" s="30" t="s">
         <v>714</v>
       </c>
-      <c r="B54" s="48" t="s">
+      <c r="B62" s="48" t="s">
         <v>715</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C62" s="30" t="s">
         <v>716</v>
       </c>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="30" t="s">
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C63" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="30" t="s">
+    <row r="64" spans="1:25">
+      <c r="A64" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="36"/>
-      <c r="C56" s="30" t="s">
+      <c r="B64" s="36"/>
+      <c r="C64" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="30" t="s">
+    <row r="65" spans="1:25">
+      <c r="A65" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30" t="s">
+      <c r="B65" s="30"/>
+      <c r="C65" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="7" t="s">
+    <row r="66" spans="1:25">
+      <c r="A66" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D66" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="7" t="s">
+    <row r="67" spans="1:25">
+      <c r="A67" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C67" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D67" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="7" t="s">
+    <row r="68" spans="1:25">
+      <c r="A68" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B68" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D68" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="7" t="s">
+    <row r="69" spans="1:25">
+      <c r="A69" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="B61" s="48" t="s">
+      <c r="B69" s="48" t="s">
         <v>712</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="D61" s="7"/>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="37" t="s">
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B70" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C70" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D70" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="38" t="s">
+    <row r="71" spans="1:25">
+      <c r="A71" s="63" t="s">
+        <v>525</v>
+      </c>
+      <c r="B71" s="64" t="s">
+        <v>524</v>
+      </c>
+      <c r="C71" s="63" t="s">
+        <v>525</v>
+      </c>
+      <c r="D71" s="65" t="s">
+        <v>830</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
+      <c r="Y71" s="2"/>
+    </row>
+    <row r="72" spans="1:25">
+      <c r="A72" s="63" t="s">
+        <v>831</v>
+      </c>
+      <c r="B72" s="64" t="s">
+        <v>832</v>
+      </c>
+      <c r="C72" s="63" t="s">
+        <v>833</v>
+      </c>
+      <c r="D72" s="65" t="s">
+        <v>834</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
+      <c r="Y72" s="2"/>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="B73" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="40" t="s">
+      <c r="C73" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D73" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="38" t="s">
+    <row r="74" spans="1:25">
+      <c r="A74" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="B74" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="40" t="s">
+      <c r="C74" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="65" spans="1:26">
-      <c r="A65" s="38" t="s">
+    <row r="75" spans="1:25">
+      <c r="A75" s="63" t="s">
+        <v>835</v>
+      </c>
+      <c r="B75" s="64" t="s">
+        <v>837</v>
+      </c>
+      <c r="C75" s="63" t="s">
+        <v>836</v>
+      </c>
+      <c r="D75" s="65" t="s">
+        <v>838</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2"/>
+      <c r="W75" s="2"/>
+      <c r="X75" s="2"/>
+      <c r="Y75" s="2"/>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B65" s="39" t="s">
+      <c r="B76" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="40" t="s">
+      <c r="C76" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D76" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="66" spans="1:26">
-      <c r="A66" s="38" t="s">
+    <row r="77" spans="1:25">
+      <c r="A77" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="B66" s="61" t="s">
+      <c r="B77" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="40" t="s">
+      <c r="C77" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D77" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:26">
-      <c r="A67" s="38" t="s">
+    <row r="78" spans="1:25">
+      <c r="A78" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B67" s="39" t="s">
+      <c r="B78" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="40" t="s">
+      <c r="C78" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D78" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:26">
-      <c r="A68" s="38" t="s">
+    <row r="79" spans="1:25">
+      <c r="A79" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B68" s="39" t="s">
+      <c r="B79" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C68" s="40" t="s">
+      <c r="C79" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D79" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:26">
-      <c r="A69" s="16" t="s">
+    <row r="80" spans="1:25">
+      <c r="A80" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B80" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C80" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D80" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:26">
-      <c r="A70" s="30" t="s">
+    <row r="81" spans="1:26">
+      <c r="A81" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B81" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C70" s="30" t="s">
+      <c r="C81" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="1:26">
-      <c r="A71" s="30" t="s">
+    <row r="82" spans="1:26">
+      <c r="A82" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C82" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A72" s="30" t="s">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A83" s="30" t="s">
         <v>574</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C83" s="30" t="s">
         <v>483</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="73" spans="1:26">
-      <c r="A73" s="30" t="s">
+    <row r="84" spans="1:26">
+      <c r="A84" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="B73" s="48" t="s">
+      <c r="B84" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C73" s="30" t="s">
+      <c r="C84" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:26">
-      <c r="A74" s="41" t="s">
+    <row r="85" spans="1:26">
+      <c r="A85" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="42" t="s">
+      <c r="B85" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="C74" s="41" t="s">
+      <c r="C85" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D85" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
-      <c r="P74" s="13"/>
-      <c r="Q74" s="13"/>
-      <c r="R74" s="13"/>
-      <c r="S74" s="13"/>
-      <c r="T74" s="13"/>
-      <c r="U74" s="13"/>
-      <c r="V74" s="13"/>
-      <c r="W74" s="13"/>
-      <c r="X74" s="13"/>
-      <c r="Y74" s="13"/>
-      <c r="Z74" s="13"/>
-    </row>
-    <row r="75" spans="1:26" ht="16">
-      <c r="A75" s="37" t="s">
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="13"/>
+      <c r="L85" s="13"/>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="13"/>
+      <c r="P85" s="13"/>
+      <c r="Q85" s="13"/>
+      <c r="R85" s="13"/>
+      <c r="S85" s="13"/>
+      <c r="T85" s="13"/>
+      <c r="U85" s="13"/>
+      <c r="V85" s="13"/>
+      <c r="W85" s="13"/>
+      <c r="X85" s="13"/>
+      <c r="Y85" s="13"/>
+      <c r="Z85" s="13"/>
+    </row>
+    <row r="86" spans="1:26" ht="16">
+      <c r="A86" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B86" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D86" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="16">
-      <c r="A76" s="37" t="s">
+    <row r="87" spans="1:26" ht="16">
+      <c r="A87" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B87" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="16">
-      <c r="A77" s="37" t="s">
+    <row r="88" spans="1:26" ht="16">
+      <c r="A88" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B88" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D88" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="78" spans="1:26">
-      <c r="A78" s="16" t="s">
+    <row r="89" spans="1:26">
+      <c r="A89" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B78" s="59" t="s">
+      <c r="B89" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C89" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D89" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:26">
-      <c r="A79" s="30" t="s">
+    <row r="90" spans="1:26">
+      <c r="A90" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="35" t="s">
+      <c r="B90" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C90" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="80" spans="1:26">
-      <c r="A80" s="30" t="s">
+    <row r="91" spans="1:26">
+      <c r="A91" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="30" t="s">
+      <c r="B91" s="3"/>
+      <c r="C91" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="31" t="s">
+    <row r="92" spans="1:26">
+      <c r="A92" s="63" t="s">
+        <v>839</v>
+      </c>
+      <c r="B92" s="65"/>
+      <c r="C92" s="63" t="s">
+        <v>840</v>
+      </c>
+      <c r="D92" s="65" t="s">
+        <v>841</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
+      <c r="V92" s="2"/>
+      <c r="W92" s="2"/>
+      <c r="X92" s="2"/>
+      <c r="Y92" s="2"/>
+    </row>
+    <row r="93" spans="1:26">
+      <c r="A93" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B93" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="31" t="s">
+      <c r="C93" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="D81" s="14" t="s">
+      <c r="D93" s="14" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="31" t="s">
+    <row r="94" spans="1:26">
+      <c r="A94" s="31" t="s">
         <v>523</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B94" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="C82" s="31" t="s">
+      <c r="C94" s="31" t="s">
         <v>525</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D94" s="6" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="31" t="s">
+    <row r="95" spans="1:26">
+      <c r="A95" s="31" t="s">
         <v>772</v>
       </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="31" t="s">
+      <c r="B95" s="6"/>
+      <c r="C95" s="31" t="s">
         <v>717</v>
       </c>
-      <c r="D83" s="6"/>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="31" t="s">
+      <c r="D95" s="6"/>
+    </row>
+    <row r="96" spans="1:26">
+      <c r="A96" s="31" t="s">
         <v>773</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B96" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C96" s="31" t="s">
         <v>774</v>
       </c>
-      <c r="D84" s="6"/>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="31" t="s">
+      <c r="D96" s="6"/>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="31" t="s">
         <v>780</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B97" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C97" s="31" t="s">
         <v>779</v>
       </c>
-      <c r="D85" s="6"/>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="31" t="s">
+      <c r="D97" s="6"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="31" t="s">
         <v>776</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B98" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C98" s="31" t="s">
         <v>778</v>
       </c>
-      <c r="D86" s="6"/>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="30" t="s">
+      <c r="D98" s="6"/>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="35" t="s">
+      <c r="B99" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C87" s="30" t="s">
+      <c r="C99" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="30" t="s">
+    <row r="100" spans="1:4">
+      <c r="A100" s="30" t="s">
         <v>706</v>
       </c>
-      <c r="B88" s="48" t="s">
+      <c r="B100" s="48" t="s">
         <v>707</v>
       </c>
-      <c r="C88" s="30" t="s">
+      <c r="C100" s="30" t="s">
         <v>708</v>
       </c>
-      <c r="D88" s="2"/>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="30" t="s">
+      <c r="D100" s="2"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="30" t="s">
         <v>722</v>
       </c>
-      <c r="B89" s="48" t="s">
+      <c r="B101" s="48" t="s">
         <v>723</v>
       </c>
-      <c r="C89" s="30" t="s">
+      <c r="C101" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="D89" s="2"/>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="43" t="s">
+      <c r="D101" s="2"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="B90" s="32" t="s">
+      <c r="B102" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C102" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="D102" s="15" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="44" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B103" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C103" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D103" s="7" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="31" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" s="31" t="s">
         <v>526</v>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="31" t="s">
+      <c r="B104" s="19"/>
+      <c r="C104" s="31" t="s">
         <v>527</v>
       </c>
-      <c r="D92" s="24" t="s">
+      <c r="D104" s="24" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="31" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" s="31" t="s">
         <v>529</v>
       </c>
-      <c r="B93" s="25" t="s">
+      <c r="B105" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="C93" s="31" t="s">
+      <c r="C105" s="31" t="s">
         <v>531</v>
       </c>
-      <c r="D93" s="26" t="s">
+      <c r="D105" s="26" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="31" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="B94" s="19"/>
-      <c r="C94" s="31" t="s">
+      <c r="B106" s="19"/>
+      <c r="C106" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="D94" s="24" t="s">
+      <c r="D106" s="24" t="s">
         <v>534</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C95" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D95" s="35" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B96" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D96" s="33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="30">
-      <c r="A97" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="B97" s="46" t="s">
-        <v>536</v>
-      </c>
-      <c r="C97" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="30">
-      <c r="A98" s="31" t="s">
-        <v>538</v>
-      </c>
-      <c r="B98" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C98" s="31" t="s">
-        <v>540</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B99" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="16" t="s">
-        <v>751</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>753</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>752</v>
-      </c>
-      <c r="D101" s="5"/>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B102" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C102" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D102" s="33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="B103" s="48" t="s">
-        <v>494</v>
-      </c>
-      <c r="C103" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="16">
-      <c r="A104" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B104" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C104" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C105" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B107" s="30"/>
+        <v>177</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="C107" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>597</v>
+        <v>179</v>
+      </c>
+      <c r="D107" s="35" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B108" s="16"/>
+        <v>181</v>
+      </c>
+      <c r="B108" s="45" t="s">
+        <v>182</v>
+      </c>
       <c r="C108" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="16" t="s">
-        <v>756</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>757</v>
-      </c>
-      <c r="C109" s="16" t="s">
-        <v>758</v>
-      </c>
-      <c r="D109" s="5"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="16" t="s">
-        <v>749</v>
-      </c>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16" t="s">
-        <v>750</v>
-      </c>
-      <c r="D110" s="5"/>
+        <v>181</v>
+      </c>
+      <c r="D108" s="33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="30">
+      <c r="A109" s="31" t="s">
+        <v>535</v>
+      </c>
+      <c r="B109" s="46" t="s">
+        <v>536</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="30">
+      <c r="A110" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="C110" s="31" t="s">
+        <v>540</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B111" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26">
+      <c r="A113" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>752</v>
+      </c>
+      <c r="D113" s="5"/>
+    </row>
+    <row r="114" spans="1:26">
+      <c r="A114" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B114" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26">
+      <c r="A115" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="B115" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" ht="16">
+      <c r="A116" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C116" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26">
+      <c r="A117" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C117" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26">
+      <c r="A118" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26">
+      <c r="A119" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26">
+      <c r="A120" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B120" s="16"/>
+      <c r="C120" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26">
+      <c r="A121" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="B121" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="D121" s="5"/>
+    </row>
+    <row r="122" spans="1:26">
+      <c r="A122" s="63" t="s">
+        <v>842</v>
+      </c>
+      <c r="B122" s="64" t="s">
+        <v>843</v>
+      </c>
+      <c r="C122" s="65" t="s">
+        <v>844</v>
+      </c>
+      <c r="D122" s="65" t="s">
+        <v>845</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
+      <c r="T122" s="2"/>
+      <c r="U122" s="2"/>
+      <c r="V122" s="2"/>
+      <c r="W122" s="2"/>
+      <c r="X122" s="2"/>
+      <c r="Y122" s="2"/>
+    </row>
+    <row r="123" spans="1:26">
+      <c r="A123" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="B123" s="16"/>
+      <c r="C123" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="D123" s="5"/>
+    </row>
+    <row r="124" spans="1:26">
+      <c r="A124" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16" t="s">
+      <c r="B124" s="16"/>
+      <c r="C124" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="D111" s="5" t="s">
+      <c r="D124" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="31" t="s">
+    <row r="125" spans="1:26">
+      <c r="A125" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B125" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C112" s="31" t="s">
+      <c r="C125" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D125" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A113" s="49" t="s">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A126" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B126" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C113" s="49" t="s">
+      <c r="C126" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="D113" s="18" t="s">
+      <c r="D126" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
-      <c r="J113" s="13"/>
-      <c r="K113" s="13"/>
-      <c r="L113" s="13"/>
-      <c r="M113" s="13"/>
-      <c r="N113" s="13"/>
-      <c r="O113" s="13"/>
-      <c r="P113" s="13"/>
-      <c r="Q113" s="13"/>
-      <c r="R113" s="13"/>
-      <c r="S113" s="13"/>
-      <c r="T113" s="13"/>
-      <c r="U113" s="13"/>
-      <c r="V113" s="13"/>
-      <c r="W113" s="13"/>
-      <c r="X113" s="13"/>
-      <c r="Y113" s="13"/>
-      <c r="Z113" s="13"/>
-    </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A114" s="37" t="s">
+      <c r="E126" s="13"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
+      <c r="J126" s="13"/>
+      <c r="K126" s="13"/>
+      <c r="L126" s="13"/>
+      <c r="M126" s="13"/>
+      <c r="N126" s="13"/>
+      <c r="O126" s="13"/>
+      <c r="P126" s="13"/>
+      <c r="Q126" s="13"/>
+      <c r="R126" s="13"/>
+      <c r="S126" s="13"/>
+      <c r="T126" s="13"/>
+      <c r="U126" s="13"/>
+      <c r="V126" s="13"/>
+      <c r="W126" s="13"/>
+      <c r="X126" s="13"/>
+      <c r="Y126" s="13"/>
+      <c r="Z126" s="13"/>
+    </row>
+    <row r="127" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A127" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="B114" s="37"/>
-      <c r="C114" s="37" t="s">
+      <c r="B127" s="37"/>
+      <c r="C127" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D127" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A115" s="37" t="s">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A128" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="B115" s="50" t="s">
+      <c r="B128" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="C115" s="37" t="s">
+      <c r="C128" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="D115" s="5"/>
-    </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A116" s="37" t="s">
+      <c r="D128" s="5"/>
+    </row>
+    <row r="129" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A129" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="B116" s="50" t="s">
+      <c r="B129" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C116" s="37" t="s">
+      <c r="C129" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D116" s="5"/>
-    </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A117" s="38" t="s">
+      <c r="D129" s="5"/>
+    </row>
+    <row r="130" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A130" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B117" s="40"/>
-      <c r="C117" s="40" t="s">
+      <c r="B130" s="40"/>
+      <c r="C130" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D130" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A118" s="37" t="s">
+    <row r="131" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A131" s="37" t="s">
         <v>762</v>
       </c>
-      <c r="B118" s="37" t="s">
+      <c r="B131" s="37" t="s">
         <v>763</v>
       </c>
-      <c r="C118" s="37" t="s">
+      <c r="C131" s="37" t="s">
         <v>764</v>
       </c>
-      <c r="D118" s="5"/>
-    </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A119" s="37" t="s">
+      <c r="D131" s="5"/>
+    </row>
+    <row r="132" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A132" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="B119" s="48" t="s">
+      <c r="B132" s="48" t="s">
         <v>733</v>
       </c>
-      <c r="C119" s="37" t="s">
+      <c r="C132" s="37" t="s">
         <v>734</v>
       </c>
-      <c r="D119" s="5"/>
-    </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A120" s="30" t="s">
+      <c r="D132" s="5" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A133" s="63" t="s">
+        <v>847</v>
+      </c>
+      <c r="B133" s="65"/>
+      <c r="C133" s="65" t="s">
+        <v>848</v>
+      </c>
+      <c r="D133" s="65" t="s">
+        <v>849</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="2"/>
+      <c r="R133" s="2"/>
+      <c r="S133" s="2"/>
+      <c r="T133" s="2"/>
+      <c r="U133" s="2"/>
+      <c r="V133" s="2"/>
+      <c r="W133" s="2"/>
+      <c r="X133" s="2"/>
+      <c r="Y133" s="2"/>
+    </row>
+    <row r="134" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A134" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30" t="s">
+      <c r="B134" s="30"/>
+      <c r="C134" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A121" s="30" t="s">
+    <row r="135" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A135" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="30" t="s">
+      <c r="B135" s="3"/>
+      <c r="C135" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D135" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A122" s="31" t="s">
+    <row r="136" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A136" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B136" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="C122" s="31" t="s">
+      <c r="C136" s="31" t="s">
         <v>543</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D136" s="14" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A123" s="38" t="s">
+    <row r="137" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A137" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B123" s="39"/>
-      <c r="C123" s="40" t="s">
+      <c r="B137" s="39"/>
+      <c r="C137" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D137" s="11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A124" s="31" t="s">
+    <row r="138" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A138" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="B124" s="19"/>
-      <c r="C124" s="31" t="s">
+      <c r="B138" s="19"/>
+      <c r="C138" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D124" s="14" t="s">
+      <c r="D138" s="14" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A125" s="30" t="s">
+    <row r="139" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A139" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B139" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C125" s="30" t="s">
+      <c r="C139" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D139" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A126" s="30" t="s">
+    <row r="140" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A140" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="B126" s="48" t="s">
+      <c r="B140" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="C126" s="30" t="s">
+      <c r="C140" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D140" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A127" s="30" t="s">
+    <row r="141" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A141" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B141" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C127" s="30" t="s">
+      <c r="C141" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D141" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A128" s="30" t="s">
+    <row r="142" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A142" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="B128" s="30"/>
-      <c r="C128" s="30" t="s">
+      <c r="B142" s="30"/>
+      <c r="C142" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D142" s="2" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A129" s="30" t="s">
+    <row r="143" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A143" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B143" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="30" t="s">
+      <c r="C143" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D143" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A130" s="30" t="s">
+    <row r="144" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A144" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="B130" s="48" t="s">
+      <c r="B144" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="C130" s="30" t="s">
+      <c r="C144" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D144" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A131" s="30" t="s">
+    <row r="145" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A145" s="30" t="s">
         <v>634</v>
       </c>
-      <c r="B131" s="48"/>
-      <c r="C131" s="30" t="s">
+      <c r="B145" s="48"/>
+      <c r="C145" s="30" t="s">
         <v>635</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D145" s="2" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A132" s="30" t="s">
+    <row r="146" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A146" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B146" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="30" t="s">
+      <c r="C146" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D146" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A133" s="30" t="s">
+    <row r="147" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A147" s="30" t="s">
         <v>637</v>
       </c>
-      <c r="B133" s="3"/>
-      <c r="C133" s="30" t="s">
+      <c r="B147" s="3"/>
+      <c r="C147" s="30" t="s">
         <v>670</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A134" s="30" t="s">
+    <row r="148" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A148" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="B134" s="3"/>
-      <c r="C134" s="30" t="s">
+      <c r="B148" s="3"/>
+      <c r="C148" s="30" t="s">
         <v>671</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A135" s="31" t="s">
+    <row r="149" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A149" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="B135" s="19"/>
-      <c r="C135" s="31" t="s">
+      <c r="B149" s="19"/>
+      <c r="C149" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D135" s="14" t="s">
+      <c r="D149" s="14" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A136" s="51" t="s">
+    <row r="150" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A150" s="51" t="s">
         <v>545</v>
       </c>
-      <c r="B136" s="27"/>
-      <c r="C136" s="51" t="s">
+      <c r="B150" s="27"/>
+      <c r="C150" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="D136" s="28" t="s">
+      <c r="D150" s="28" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A137" s="31" t="s">
+    <row r="151" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A151" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="B137" s="19"/>
-      <c r="C137" s="31" t="s">
+      <c r="B151" s="19"/>
+      <c r="C151" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="D137" s="14" t="s">
+      <c r="D151" s="14" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A138" s="31" t="s">
+    <row r="152" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A152" s="31" t="s">
         <v>727</v>
       </c>
-      <c r="B138" s="60" t="s">
+      <c r="B152" s="60" t="s">
         <v>729</v>
       </c>
-      <c r="C138" s="31" t="s">
+      <c r="C152" s="31" t="s">
         <v>728</v>
       </c>
-      <c r="D138" s="14"/>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A139" s="31" t="s">
+      <c r="D152" s="14"/>
+    </row>
+    <row r="153" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A153" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A154" s="31" t="s">
         <v>641</v>
       </c>
-      <c r="B139" s="19"/>
-      <c r="C139" s="31" t="s">
+      <c r="B154" s="19"/>
+      <c r="C154" s="31" t="s">
         <v>672</v>
       </c>
-      <c r="D139" s="14" t="s">
+      <c r="D154" s="14" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A140" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A141" s="16" t="s">
+    <row r="155" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A155" s="63" t="s">
+        <v>850</v>
+      </c>
+      <c r="B155" s="65"/>
+      <c r="C155" s="63" t="s">
+        <v>851</v>
+      </c>
+      <c r="D155" s="65" t="s">
+        <v>852</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
+      <c r="M155" s="2"/>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
+      <c r="P155" s="2"/>
+      <c r="Q155" s="2"/>
+      <c r="R155" s="2"/>
+      <c r="S155" s="2"/>
+      <c r="T155" s="2"/>
+      <c r="U155" s="2"/>
+      <c r="V155" s="2"/>
+      <c r="W155" s="2"/>
+      <c r="X155" s="2"/>
+      <c r="Y155" s="2"/>
+    </row>
+    <row r="156" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A156" s="16" t="s">
         <v>618</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B156" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="C141" s="16" t="s">
+      <c r="C156" s="16" t="s">
         <v>619</v>
       </c>
-      <c r="D141" s="5" t="s">
+      <c r="D156" s="5" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A142" s="16" t="s">
+    <row r="157" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A157" s="16" t="s">
         <v>647</v>
       </c>
-      <c r="B142" s="59" t="s">
+      <c r="B157" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="C142" s="16" t="s">
+      <c r="C157" s="16" t="s">
         <v>648</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="D157" s="5" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A143" s="16" t="s">
+    <row r="158" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A158" s="16" t="s">
         <v>674</v>
       </c>
-      <c r="B143" s="4"/>
-      <c r="C143" s="16" t="s">
+      <c r="B158" s="4"/>
+      <c r="C158" s="16" t="s">
         <v>675</v>
       </c>
-      <c r="D143" s="5" t="s">
+      <c r="D158" s="5" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A144" s="16" t="s">
+    <row r="159" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A159" s="16" t="s">
         <v>789</v>
       </c>
-      <c r="B144" s="4"/>
-      <c r="C144" s="16" t="s">
+      <c r="B159" s="4"/>
+      <c r="C159" s="16" t="s">
         <v>788</v>
       </c>
-      <c r="D144" s="5"/>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A145" s="16" t="s">
+      <c r="D159" s="5"/>
+    </row>
+    <row r="160" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A160" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="B145" s="4"/>
-      <c r="C145" s="16" t="s">
+      <c r="B160" s="4"/>
+      <c r="C160" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D160" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A146" s="30" t="s">
+    <row r="161" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A161" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="B146" s="35" t="s">
+      <c r="B161" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="C146" s="30" t="s">
+      <c r="C161" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D161" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A147" s="30" t="s">
+    <row r="162" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A162" s="30" t="s">
         <v>754</v>
       </c>
-      <c r="B147" s="35"/>
-      <c r="C147" s="30" t="s">
+      <c r="B162" s="35"/>
+      <c r="C162" s="30" t="s">
         <v>755</v>
       </c>
-      <c r="D147" s="2"/>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A148" s="30" t="s">
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A163" s="30" t="s">
         <v>726</v>
       </c>
-      <c r="B148" s="35"/>
-      <c r="C148" s="30" t="s">
+      <c r="B163" s="35"/>
+      <c r="C163" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="D148" s="2"/>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A149" s="30" t="s">
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A164" s="30" t="s">
         <v>782</v>
       </c>
-      <c r="B149" s="35" t="s">
+      <c r="B164" s="35" t="s">
         <v>783</v>
       </c>
-      <c r="C149" s="30" t="s">
+      <c r="C164" s="30" t="s">
         <v>784</v>
       </c>
-      <c r="D149" s="2"/>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A150" s="30" t="s">
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A165" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B165" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C150" s="30" t="s">
+      <c r="C165" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D165" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A151" s="16" t="s">
+    <row r="166" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A166" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B151" s="20"/>
-      <c r="C151" s="16" t="s">
+      <c r="B166" s="20"/>
+      <c r="C166" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D151" s="5" t="s">
+      <c r="D166" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A152" s="30" t="s">
+    <row r="167" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A167" s="30" t="s">
         <v>468</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B167" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C152" s="30" t="s">
+      <c r="C167" s="30" t="s">
         <v>468</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A153" s="30" t="s">
+    <row r="168" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A168" s="63" t="s">
+        <v>853</v>
+      </c>
+      <c r="B168" s="64" t="s">
+        <v>854</v>
+      </c>
+      <c r="C168" s="63" t="s">
+        <v>853</v>
+      </c>
+      <c r="D168" s="65" t="s">
+        <v>855</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+      <c r="P168" s="2"/>
+      <c r="Q168" s="2"/>
+      <c r="R168" s="2"/>
+      <c r="S168" s="2"/>
+      <c r="T168" s="2"/>
+      <c r="U168" s="2"/>
+      <c r="V168" s="2"/>
+      <c r="W168" s="2"/>
+      <c r="X168" s="2"/>
+      <c r="Y168" s="2"/>
+    </row>
+    <row r="169" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A169" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="B153" s="35" t="s">
+      <c r="B169" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="C153" s="30" t="s">
+      <c r="C169" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D169" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A154" s="30" t="s">
+    <row r="170" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A170" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B154" s="22" t="s">
+      <c r="B170" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="C154" s="30" t="s">
+      <c r="C170" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A155" s="31" t="s">
+    <row r="171" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A171" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B171" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C155" s="31" t="s">
+      <c r="C171" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D171" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A156" s="51" t="s">
+    <row r="172" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A172" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B156" s="29"/>
-      <c r="C156" s="51" t="s">
+      <c r="B172" s="29"/>
+      <c r="C172" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="D156" s="28" t="s">
+      <c r="D172" s="28" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A157" s="30" t="s">
+    <row r="173" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A173" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="B157" s="35" t="s">
+      <c r="B173" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="C157" s="30" t="s">
+      <c r="C173" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D173" s="2" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A158" s="30" t="s">
+    <row r="174" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A174" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2" t="s">
+      <c r="B174" s="2"/>
+      <c r="C174" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D174" s="2" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A159" s="30" t="s">
+    <row r="175" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A175" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2" t="s">
+      <c r="B175" s="2"/>
+      <c r="C175" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D175" s="2" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A160" s="30" t="s">
+    <row r="176" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A176" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B176" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C160" s="30" t="s">
+      <c r="C176" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D176" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A161" s="16" t="s">
+    <row r="177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A177" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B177" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C161" s="16" t="s">
+      <c r="C177" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="D161" s="33" t="s">
+      <c r="D177" s="33" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A162" s="16" t="s">
+    <row r="178" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A178" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="B162" s="4"/>
-      <c r="C162" s="16" t="s">
+      <c r="B178" s="4"/>
+      <c r="C178" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="D162" s="5" t="s">
+      <c r="D178" s="5" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A163" s="30" t="s">
+    <row r="179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A179" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="B163" s="35" t="s">
+      <c r="B179" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="C163" s="30" t="s">
+      <c r="C179" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D179" s="2" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A164" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C164" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A165" s="30" t="s">
-        <v>718</v>
-      </c>
-      <c r="B165" s="48" t="s">
-        <v>720</v>
-      </c>
-      <c r="C165" s="30" t="s">
-        <v>719</v>
-      </c>
-      <c r="D165" s="2"/>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A166" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B166" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="C166" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A167" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B167" s="5"/>
-      <c r="C167" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="30" customHeight="1">
-      <c r="A168" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B168" s="5"/>
-      <c r="C168" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="B169" s="5"/>
-      <c r="C169" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="B170" s="2"/>
-      <c r="C170" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="B171" s="39"/>
-      <c r="C171" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="D171" s="11" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A172" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B172" s="5"/>
-      <c r="C172" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A173" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A174" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B174" s="2"/>
-      <c r="C174" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A175" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="B175" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="C175" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A176" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B176" s="26"/>
-      <c r="C176" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A177" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="B177" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="C177" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A178" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B178" s="26"/>
-      <c r="C178" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A179" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B179" s="26"/>
-      <c r="C179" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1">
       <c r="A180" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="B180" s="35" t="s">
-        <v>366</v>
+        <v>319</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="C180" s="30" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1">
       <c r="A181" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="B181" s="35"/>
+        <v>718</v>
+      </c>
+      <c r="B181" s="48" t="s">
+        <v>720</v>
+      </c>
       <c r="C181" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>371</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="D181" s="2"/>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1">
       <c r="A182" s="30" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="B182" s="35" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="C182" s="30" t="s">
-        <v>374</v>
+        <v>325</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>375</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1">
       <c r="A183" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B183" s="4"/>
+        <v>327</v>
+      </c>
+      <c r="B183" s="5"/>
       <c r="C183" s="16" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A184" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B184" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="C184" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>382</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="30" customHeight="1">
+      <c r="A184" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B184" s="5"/>
+      <c r="C184" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A185" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="B185" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="C185" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>386</v>
+      <c r="A185" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B185" s="5"/>
+      <c r="C185" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1">
       <c r="A186" s="30" t="s">
-        <v>660</v>
-      </c>
-      <c r="B186" s="3"/>
+        <v>336</v>
+      </c>
+      <c r="B186" s="2"/>
       <c r="C186" s="30" t="s">
-        <v>387</v>
+        <v>337</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A187" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="B187" s="3"/>
-      <c r="C187" s="30" t="s">
-        <v>663</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>690</v>
+      <c r="A187" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="B187" s="39"/>
+      <c r="C187" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A188" s="30" t="s">
-        <v>661</v>
-      </c>
-      <c r="B188" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="C188" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>390</v>
+      <c r="A188" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B188" s="5"/>
+      <c r="C188" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A189" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="B189" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>394</v>
+      <c r="A189" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A190" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="B190" s="39"/>
-      <c r="C190" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="D190" s="11" t="s">
-        <v>397</v>
+      <c r="A190" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B190" s="2"/>
+      <c r="C190" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A191" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="C191" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>401</v>
+      <c r="A191" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="B191" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="C191" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A192" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B192" s="3"/>
-      <c r="C192" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>604</v>
+      <c r="A192" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B192" s="26"/>
+      <c r="C192" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D192" s="14" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A193" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B193" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="C193" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="D193" s="21" t="s">
-        <v>406</v>
+      <c r="A193" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B193" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="C193" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A194" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="B194" s="39"/>
-      <c r="C194" s="54" t="s">
-        <v>408</v>
-      </c>
-      <c r="D194" s="21" t="s">
-        <v>585</v>
+      <c r="A194" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B194" s="26"/>
+      <c r="C194" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D194" s="14" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A195" s="55" t="s">
-        <v>409</v>
-      </c>
-      <c r="B195" s="4"/>
-      <c r="C195" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="D195" s="9" t="s">
-        <v>586</v>
+      <c r="A195" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B195" s="26"/>
+      <c r="C195" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1">
       <c r="A196" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B196" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="B196" s="35" t="s">
+        <v>366</v>
+      </c>
       <c r="C196" s="30" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1">
       <c r="A197" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B197" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="B197" s="35"/>
       <c r="C197" s="30" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>588</v>
+        <v>371</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1">
       <c r="A198" s="30" t="s">
-        <v>743</v>
-      </c>
-      <c r="B198" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="B198" s="35" t="s">
+        <v>373</v>
+      </c>
       <c r="C198" s="30" t="s">
-        <v>744</v>
-      </c>
-      <c r="D198" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A199" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C199" s="30" t="s">
-        <v>417</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>418</v>
+      <c r="A199" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B199" s="4"/>
+      <c r="C199" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A200" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="B200" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="C200" s="56" t="s">
-        <v>421</v>
+      <c r="A200" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B200" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="C200" s="30" t="s">
+        <v>381</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1">
       <c r="A201" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="B201" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="B201" s="35" t="s">
+        <v>384</v>
+      </c>
       <c r="C201" s="30" t="s">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A202" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C202" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D202" s="33" t="s">
-        <v>428</v>
+      <c r="A202" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="B202" s="3"/>
+      <c r="C202" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A203" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C203" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>432</v>
+      <c r="A203" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="B203" s="3"/>
+      <c r="C203" s="30" t="s">
+        <v>663</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1">
       <c r="A204" s="30" t="s">
-        <v>433</v>
+        <v>661</v>
       </c>
       <c r="B204" s="35" t="s">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="C204" s="30" t="s">
-        <v>583</v>
+        <v>389</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>435</v>
+        <v>390</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A205" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C205" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>439</v>
+      <c r="A205" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="B205" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A206" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C206" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>443</v>
+      <c r="A206" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B206" s="39"/>
+      <c r="C206" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A207" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B207" s="2"/>
-      <c r="C207" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>590</v>
+      <c r="A207" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C207" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1">
       <c r="A208" s="30" t="s">
-        <v>446</v>
-      </c>
-      <c r="B208" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="B208" s="3"/>
       <c r="C208" s="30" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A209" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B209" s="14"/>
-      <c r="C209" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="D209" s="14" t="s">
-        <v>664</v>
+      <c r="A209" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B209" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C209" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D209" s="21" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A210" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B210" s="14"/>
-      <c r="C210" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="D210" s="14" t="s">
-        <v>555</v>
+      <c r="A210" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="B210" s="39"/>
+      <c r="C210" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D210" s="21" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A211" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="B211" s="14"/>
-      <c r="C211" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="D211" s="14" t="s">
-        <v>558</v>
+      <c r="A211" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A212" s="31" t="s">
-        <v>559</v>
-      </c>
-      <c r="B212" s="14"/>
-      <c r="C212" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="D212" s="14" t="s">
-        <v>561</v>
+      <c r="A212" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="B212" s="2"/>
+      <c r="C212" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A213" s="31" t="s">
-        <v>562</v>
-      </c>
-      <c r="B213" s="14"/>
-      <c r="C213" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="D213" s="14" t="s">
-        <v>564</v>
+      <c r="A213" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="B213" s="2"/>
+      <c r="C213" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A214" s="31" t="s">
-        <v>565</v>
-      </c>
-      <c r="B214" s="14"/>
-      <c r="C214" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="D214" s="14" t="s">
-        <v>567</v>
-      </c>
+      <c r="A214" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="B214" s="2"/>
+      <c r="C214" s="30" t="s">
+        <v>744</v>
+      </c>
+      <c r="D214" s="2"/>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A215" s="31" t="s">
-        <v>748</v>
-      </c>
-      <c r="B215" s="14" t="s">
-        <v>747</v>
-      </c>
-      <c r="C215" s="31" t="s">
-        <v>746</v>
-      </c>
-      <c r="D215" s="62"/>
+      <c r="A215" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C215" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A216" s="31" t="s">
-        <v>448</v>
-      </c>
-      <c r="B216" s="48" t="s">
-        <v>498</v>
-      </c>
-      <c r="C216" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="D216" s="14" t="s">
-        <v>450</v>
+      <c r="A216" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B216" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C216" s="56" t="s">
+        <v>421</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A217" s="31" t="s">
-        <v>800</v>
-      </c>
-      <c r="B217" s="48" t="s">
-        <v>802</v>
-      </c>
-      <c r="C217" s="31" t="s">
-        <v>801</v>
-      </c>
-      <c r="D217" s="14"/>
+      <c r="A217" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="B217" s="2"/>
+      <c r="C217" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1">
       <c r="A218" s="16" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="C218" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>454</v>
+        <v>427</v>
+      </c>
+      <c r="D218" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1">
       <c r="A219" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B219" s="4"/>
+        <v>429</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="C219" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="D219" s="5"/>
+        <v>431</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A220" s="16" t="s">
-        <v>798</v>
-      </c>
-      <c r="B220" s="4"/>
-      <c r="C220" s="16" t="s">
-        <v>799</v>
-      </c>
-      <c r="D220" s="5"/>
+      <c r="A220" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="B220" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="C220" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A221" s="16" t="s">
-        <v>645</v>
-      </c>
-      <c r="B221" s="4"/>
-      <c r="C221" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>689</v>
+      <c r="A221" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C221" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1">
       <c r="A222" s="30" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C222" s="30" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A223" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C223" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D223" s="7" t="s">
-        <v>462</v>
+      <c r="A223" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B223" s="2"/>
+      <c r="C223" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1">
       <c r="A224" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>464</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="B224" s="2"/>
       <c r="C224" s="30" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>466</v>
+        <v>591</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A225" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="B225" s="20"/>
-      <c r="C225" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>688</v>
+      <c r="A225" s="31" t="s">
+        <v>551</v>
+      </c>
+      <c r="B225" s="14"/>
+      <c r="C225" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="D225" s="14" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1">
       <c r="A226" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>569</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="B226" s="14"/>
       <c r="C226" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>581</v>
+        <v>554</v>
+      </c>
+      <c r="D226" s="14" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1">
       <c r="A227" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B227" s="14"/>
+      <c r="C227" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="D227" s="14" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A228" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="B228" s="14"/>
+      <c r="C228" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="D228" s="14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A229" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="B229" s="14"/>
+      <c r="C229" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="D229" s="14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A230" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B230" s="14"/>
+      <c r="C230" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D230" s="14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A231" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="B231" s="14" t="s">
+        <v>747</v>
+      </c>
+      <c r="C231" s="31" t="s">
+        <v>746</v>
+      </c>
+      <c r="D231" s="62"/>
+    </row>
+    <row r="232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A232" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B232" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="C232" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="D232" s="14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A233" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C233" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A234" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D234" s="5"/>
+    </row>
+    <row r="235" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A235" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A236" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C236" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A237" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A238" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C238" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A239" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="B239" s="20"/>
+      <c r="C239" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A240" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C240" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A241" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B227" s="6" t="s">
+      <c r="B241" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C227" s="31" t="s">
+      <c r="C241" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D227" s="6" t="s">
+      <c r="D241" s="6" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A228" s="16" t="s">
+    <row r="242" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A242" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="B228" s="20"/>
-      <c r="C228" s="16" t="s">
+      <c r="B242" s="20"/>
+      <c r="C242" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="D228" s="5" t="s">
+      <c r="D242" s="5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A229" s="16" t="s">
+    <row r="243" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A243" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="B229" s="20"/>
-      <c r="C229" s="16" t="s">
+      <c r="B243" s="20"/>
+      <c r="C243" s="16" t="s">
         <v>652</v>
       </c>
-      <c r="D229" s="5" t="s">
+      <c r="D243" s="5" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A230" s="16" t="s">
+    <row r="244" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A244" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B230" s="20" t="s">
+      <c r="B244" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C230" s="16" t="s">
+      <c r="C244" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D244" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="16" t="s">
+    <row r="245" spans="1:25">
+      <c r="A245" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B245" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C231" s="16" t="s">
+      <c r="C245" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D231" s="5" t="s">
+      <c r="D245" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A232" s="30" t="s">
+    <row r="246" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A246" s="30" t="s">
         <v>684</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B246" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C232" s="30" t="s">
+      <c r="C246" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="D246" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A233" s="30" t="s">
+    <row r="247" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A247" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B233" s="3"/>
-      <c r="C233" s="30" t="s">
+      <c r="B247" s="3"/>
+      <c r="C247" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D233" s="2"/>
-    </row>
-    <row r="234" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A234" s="2" t="s">
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A248" s="63" t="s">
+        <v>858</v>
+      </c>
+      <c r="B248" s="64" t="s">
+        <v>856</v>
+      </c>
+      <c r="C248" s="63" t="s">
+        <v>857</v>
+      </c>
+      <c r="D248" s="65" t="s">
+        <v>859</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+      <c r="J248" s="2"/>
+      <c r="K248" s="2"/>
+      <c r="L248" s="2"/>
+      <c r="M248" s="2"/>
+      <c r="N248" s="2"/>
+      <c r="O248" s="2"/>
+      <c r="P248" s="2"/>
+      <c r="Q248" s="2"/>
+      <c r="R248" s="2"/>
+      <c r="S248" s="2"/>
+      <c r="T248" s="2"/>
+      <c r="U248" s="2"/>
+      <c r="V248" s="2"/>
+      <c r="W248" s="2"/>
+      <c r="X248" s="2"/>
+      <c r="Y248" s="2"/>
+    </row>
+    <row r="249" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A249" s="63" t="s">
+        <v>862</v>
+      </c>
+      <c r="B249" s="64" t="s">
+        <v>860</v>
+      </c>
+      <c r="C249" s="63" t="s">
+        <v>861</v>
+      </c>
+      <c r="D249" s="65" t="s">
+        <v>863</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+      <c r="I249" s="2"/>
+      <c r="J249" s="2"/>
+      <c r="K249" s="2"/>
+      <c r="L249" s="2"/>
+      <c r="M249" s="2"/>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
+      <c r="P249" s="2"/>
+      <c r="Q249" s="2"/>
+      <c r="R249" s="2"/>
+      <c r="S249" s="2"/>
+      <c r="T249" s="2"/>
+      <c r="U249" s="2"/>
+      <c r="V249" s="2"/>
+      <c r="W249" s="2"/>
+      <c r="X249" s="2"/>
+      <c r="Y249" s="2"/>
+    </row>
+    <row r="250" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A250" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B250" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C250" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="D250" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A235" s="2" t="s">
+    <row r="251" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A251" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B235" s="35" t="s">
+      <c r="B251" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C251" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="D251" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A236" s="58" t="s">
+    <row r="252" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A252" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B236" s="6" t="s">
+      <c r="B252" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C236" s="31" t="s">
+      <c r="C252" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D236" s="6" t="s">
+      <c r="D252" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A237" s="2" t="s">
+    <row r="253" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A253" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B253" t="s">
         <v>786</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C253" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="239" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="240" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="254" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="255" spans="1:25" ht="15.75" customHeight="1"/>
+    <row r="256" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="257" ht="15.75" customHeight="1"/>
     <row r="258" ht="15.75" customHeight="1"/>
     <row r="259" ht="15.75" customHeight="1"/>
@@ -7765,166 +8536,192 @@
     <row r="1164" ht="15.75" customHeight="1"/>
     <row r="1165" ht="15.75" customHeight="1"/>
     <row r="1166" ht="15.75" customHeight="1"/>
+    <row r="1167" ht="15.75" customHeight="1"/>
+    <row r="1168" ht="15.75" customHeight="1"/>
+    <row r="1169" ht="15.75" customHeight="1"/>
+    <row r="1170" ht="15.75" customHeight="1"/>
+    <row r="1171" ht="15.75" customHeight="1"/>
+    <row r="1172" ht="15.75" customHeight="1"/>
+    <row r="1173" ht="15.75" customHeight="1"/>
+    <row r="1174" ht="15.75" customHeight="1"/>
+    <row r="1175" ht="15.75" customHeight="1"/>
+    <row r="1176" ht="15.75" customHeight="1"/>
+    <row r="1177" ht="15.75" customHeight="1"/>
+    <row r="1178" ht="15.75" customHeight="1"/>
+    <row r="1179" ht="15.75" customHeight="1"/>
+    <row r="1180" ht="15.75" customHeight="1"/>
+    <row r="1181" ht="15.75" customHeight="1"/>
+    <row r="1182" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B231" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D20" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D25" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B27" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B30" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B31" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B35" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B36" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B37" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D37" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B38" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B39" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B41" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B22" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B45" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D45" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B46" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B51" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B53" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B55" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B58" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B62" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D62" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B63" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B64" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B65" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B67" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B68" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B69" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B70" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B71" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B73" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B74" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D78" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B79" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B87" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D90" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B95" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D95" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B96" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D96" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B99" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B102" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D102" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B104" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B105" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B112" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D112" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B113" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B115" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B116" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B125" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B126" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B127" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B129" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B140" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B146" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B150" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B153" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B154" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B155" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D155" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B157" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B160" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B161" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D161" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B163" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B164" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B166" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B175" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B177" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B180" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B182" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B184" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B185" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B188" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B189" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B191" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D191" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B193" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B199" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B200" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B202" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D202" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B203" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B204" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B205" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B206" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B222" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B223" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B224" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B152" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B232" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B72" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B234" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B235" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B103" r:id="rId110" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
-    <hyperlink ref="B130" r:id="rId111" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
-    <hyperlink ref="B216" r:id="rId112" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B245" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B21" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D21" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D26" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B33" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B38" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B39" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B43" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D43" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B45" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B46" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B48" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B23" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D23" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B53" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D53" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B54" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B59" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B61" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B63" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B66" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B67" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D67" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B68" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B70" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D70" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B73" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B74" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B76" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B78" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B79" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B80" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B81" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B82" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B84" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B85" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B86" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B87" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B88" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B89" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D89" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B90" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B93" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B99" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D102" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B107" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D107" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B108" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D108" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B111" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B114" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D114" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B116" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B117" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B125" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D125" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B126" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B128" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B129" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B139" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B140" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B141" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B143" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B161" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B165" r:id="rId70" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B169" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B170" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B171" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D171" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B173" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B176" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="B177" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D177" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="B179" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B180" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="B182" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="B191" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B193" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B196" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="B198" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="B200" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="B201" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="B204" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B205" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="B207" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D207" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="B209" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B215" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="B216" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="B218" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D218" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="B219" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B220" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="B221" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="B222" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="B233" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B236" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B237" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B238" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B167" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="B246" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B83" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="B250" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B251" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B115" r:id="rId110" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
+    <hyperlink ref="B144" r:id="rId111" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
+    <hyperlink ref="B232" r:id="rId112" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
     <hyperlink ref="D7" r:id="rId113" xr:uid="{AE166E41-45CE-0B4F-9AF7-CC1DD5F8DB0A}"/>
     <hyperlink ref="B9" r:id="rId114" xr:uid="{CEBD8475-045E-8A48-8BEE-522233CB5CE4}"/>
     <hyperlink ref="D9" r:id="rId115" xr:uid="{6D337170-E81E-3643-BE2C-3B39B4D25C02}"/>
-    <hyperlink ref="B43" r:id="rId116" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
-    <hyperlink ref="D43" r:id="rId117" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
-    <hyperlink ref="B82" r:id="rId118" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
-    <hyperlink ref="D82" r:id="rId119" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
-    <hyperlink ref="B93" r:id="rId120" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
-    <hyperlink ref="D93" r:id="rId121" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
-    <hyperlink ref="B97" r:id="rId122" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
-    <hyperlink ref="D97" r:id="rId123" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
-    <hyperlink ref="B98" r:id="rId124" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
-    <hyperlink ref="D98" r:id="rId125" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
-    <hyperlink ref="B122" r:id="rId126" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B226" r:id="rId127" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D226" r:id="rId128" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B227" r:id="rId129" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D227" r:id="rId130" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B236" r:id="rId131" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D236" r:id="rId132" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
-    <hyperlink ref="B24" r:id="rId133" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
-    <hyperlink ref="B19" r:id="rId134" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
-    <hyperlink ref="B66" r:id="rId135" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
-    <hyperlink ref="B28" r:id="rId136" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
+    <hyperlink ref="B51" r:id="rId116" xr:uid="{FB8B2766-C779-9244-800E-D1CBA97B195F}"/>
+    <hyperlink ref="D51" r:id="rId117" xr:uid="{C8094924-A1DC-1E4C-A647-2E6578A9BDF2}"/>
+    <hyperlink ref="B94" r:id="rId118" xr:uid="{3664332C-AD90-3E4C-8D32-32646EA16196}"/>
+    <hyperlink ref="D94" r:id="rId119" xr:uid="{52F7202A-C336-8B40-814D-BF3286C682FD}"/>
+    <hyperlink ref="B105" r:id="rId120" xr:uid="{79D3745C-5E83-CF42-80A3-B755A1F94C63}"/>
+    <hyperlink ref="D105" r:id="rId121" xr:uid="{106A8800-9C66-D741-B2DE-3878074DD3E8}"/>
+    <hyperlink ref="B109" r:id="rId122" xr:uid="{9A13C68E-FE77-EF45-9A4F-6398D58B1C0B}"/>
+    <hyperlink ref="D109" r:id="rId123" xr:uid="{EB43DD6F-804A-EC40-924C-5F5A446530E2}"/>
+    <hyperlink ref="B110" r:id="rId124" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
+    <hyperlink ref="D110" r:id="rId125" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
+    <hyperlink ref="B136" r:id="rId126" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
+    <hyperlink ref="B240" r:id="rId127" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D240" r:id="rId128" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B241" r:id="rId129" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D241" r:id="rId130" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B252" r:id="rId131" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D252" r:id="rId132" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B25" r:id="rId133" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
+    <hyperlink ref="B20" r:id="rId134" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
+    <hyperlink ref="B77" r:id="rId135" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
+    <hyperlink ref="B30" r:id="rId136" xr:uid="{3DED7FB1-970C-8F40-9911-C97CCB13E15F}"/>
     <hyperlink ref="B7" r:id="rId137" xr:uid="{FC681248-55FF-9748-B521-6B0B25ABE69F}"/>
     <hyperlink ref="B3" r:id="rId138" xr:uid="{2055A687-1373-8A48-9C73-C9F0E7B6B5A4}"/>
-    <hyperlink ref="B91" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B90" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B88" r:id="rId141" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
-    <hyperlink ref="B61" r:id="rId142" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
-    <hyperlink ref="B54" r:id="rId143" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
-    <hyperlink ref="B165" r:id="rId144" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
-    <hyperlink ref="B89" r:id="rId145" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
-    <hyperlink ref="B138" r:id="rId146" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
-    <hyperlink ref="B119" r:id="rId147" tooltip="https://d-nb.info/gnd/7729567-5" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
+    <hyperlink ref="B103" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B102" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B100" r:id="rId141" xr:uid="{BDFA9E5E-778F-184D-B887-840F44BA9BC6}"/>
+    <hyperlink ref="B69" r:id="rId142" tooltip="https://d-nb.info/gnd/5123628-X" xr:uid="{58AAA300-E367-CE4E-AA38-B57A72BFA751}"/>
+    <hyperlink ref="B62" r:id="rId143" xr:uid="{38C50E32-FFB2-A740-B185-5714F1AA2FA7}"/>
+    <hyperlink ref="B181" r:id="rId144" xr:uid="{B1C488F1-5BD8-2C47-8D9C-7D7458C02F64}"/>
+    <hyperlink ref="B101" r:id="rId145" xr:uid="{92DAAC6C-54D2-AA47-9F91-A1282380107B}"/>
+    <hyperlink ref="B152" r:id="rId146" xr:uid="{5B7323AD-F051-0044-BEE5-7C5E5C2CFA22}"/>
+    <hyperlink ref="B132" r:id="rId147" xr:uid="{760FD68E-4928-DE41-A2C8-1102702FA415}"/>
     <hyperlink ref="B5" r:id="rId148" xr:uid="{7AB633D8-5F39-3E48-9411-99D92E6830AA}"/>
     <hyperlink ref="B12" r:id="rId149" xr:uid="{43DC6B56-B3E7-0644-A678-35C18F005640}"/>
     <hyperlink ref="B14" r:id="rId150" xr:uid="{96D8BA99-5A2C-084E-8DE9-B98A7ADF8C44}"/>
-    <hyperlink ref="B142" r:id="rId151" xr:uid="{3C7F0CC8-6291-B845-8271-16779E9DCE6A}"/>
-    <hyperlink ref="B218" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B217" r:id="rId153" tooltip="https://d-nb.info/gnd/7518596-9" xr:uid="{B6754BE5-59A2-9D40-8AF2-E7F344761281}"/>
+    <hyperlink ref="B15" r:id="rId151" xr:uid="{7DB5B514-750D-AD43-ABEA-D5BAC4B04D0E}"/>
+    <hyperlink ref="B28" r:id="rId152" xr:uid="{48944BC8-D599-FD41-A3E8-E6D723E75995}"/>
+    <hyperlink ref="B40" r:id="rId153" xr:uid="{6ABC26E1-6E95-2942-8BAE-1FC90BEBAD29}"/>
+    <hyperlink ref="B41" r:id="rId154" xr:uid="{754CD1B5-C177-604B-98EE-184A59B9E1EB}"/>
+    <hyperlink ref="B44" r:id="rId155" xr:uid="{596D8C2C-8FF3-EC40-8DCF-8B6A58C66320}"/>
+    <hyperlink ref="B71" r:id="rId156" xr:uid="{F36910DA-0B29-E74A-A123-E3FF461A0E5A}"/>
+    <hyperlink ref="B72" r:id="rId157" xr:uid="{5BD9BAFA-070B-4241-AF53-188A83468A5D}"/>
+    <hyperlink ref="B75" r:id="rId158" xr:uid="{6147CE6E-C87C-784C-8C82-C20012B2A793}"/>
+    <hyperlink ref="B122" r:id="rId159" xr:uid="{11B0BE32-8750-FF4D-BE35-F123CC7F462C}"/>
+    <hyperlink ref="B153" r:id="rId160" xr:uid="{EE64827B-2F7B-2144-AB5C-9D496B0649E5}"/>
+    <hyperlink ref="B168" r:id="rId161" xr:uid="{24423ED9-B692-2647-B3BC-E6C1ABF6EF15}"/>
+    <hyperlink ref="B248" r:id="rId162" xr:uid="{9A59C1DE-E4DD-8B45-9363-F539266D8923}"/>
+    <hyperlink ref="B249" r:id="rId163" xr:uid="{ED036015-8086-4B49-A150-4A8112E7A493}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId154"/>
+    <tablePart r:id="rId164"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/xlsx/Baernreither_orgNames_2023.xlsx
+++ b/data/xlsx/Baernreither_orgNames_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF49199-9F95-C24E-877D-D37847C3C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1339A8F-9E02-1F4B-AF45-DD007291367E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="500" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="760" windowWidth="25600" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="867">
   <si>
     <t>Spalte 1</t>
   </si>
@@ -3201,6 +3201,15 @@
   </si>
   <si>
     <t>&lt;orgName key="UniversitaetZagreb" ref="https://d-nb.info/gnd/1014349-X"&gt;</t>
+  </si>
+  <si>
+    <t>Schichau-Werke</t>
+  </si>
+  <si>
+    <t>https://d-nb.info/gnd/7518596-9</t>
+  </si>
+  <si>
+    <t>SchichauWerke</t>
   </si>
 </sst>
 </file>
@@ -3647,7 +3656,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D244" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:D245" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spalte 1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spalte 2" dataDxfId="2"/>
@@ -3856,7 +3865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1182"/>
+  <dimension ref="A1:Z1183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="73.1640625" customWidth="1"/>
@@ -4179,7 +4188,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" ht="30">
       <c r="A20" s="16" t="s">
         <v>633</v>
       </c>
@@ -7307,246 +7316,223 @@
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A233" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C233" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>454</v>
-      </c>
+      <c r="A233" s="31" t="s">
+        <v>864</v>
+      </c>
+      <c r="B233" s="48" t="s">
+        <v>865</v>
+      </c>
+      <c r="C233" s="31" t="s">
+        <v>866</v>
+      </c>
+      <c r="D233" s="14"/>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1">
       <c r="A234" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B234" s="4"/>
+        <v>451</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="C234" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="D234" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1">
       <c r="A235" s="16" t="s">
-        <v>645</v>
+        <v>730</v>
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="D235" s="5"/>
+    </row>
+    <row r="236" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A236" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="D235" s="5" t="s">
+      <c r="D236" s="5" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A236" s="30" t="s">
+    <row r="237" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A237" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B237" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C236" s="30" t="s">
+      <c r="C237" s="30" t="s">
         <v>457</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="D237" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A237" s="7" t="s">
+    <row r="238" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A238" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B238" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C237" s="7" t="s">
+      <c r="C238" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D237" s="7" t="s">
+      <c r="D238" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A238" s="30" t="s">
+    <row r="239" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A239" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B239" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C238" s="30" t="s">
+      <c r="C239" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="D239" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A239" s="16" t="s">
+    <row r="240" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A240" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="B239" s="20"/>
-      <c r="C239" s="16" t="s">
+      <c r="B240" s="20"/>
+      <c r="C240" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="D239" s="5" t="s">
+      <c r="D240" s="5" t="s">
         <v>688</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A240" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="C240" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="D240" s="6" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="241" spans="1:25" ht="15.75" customHeight="1">
       <c r="A241" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C241" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A242" s="31" t="s">
         <v>571</v>
       </c>
-      <c r="B241" s="6" t="s">
+      <c r="B242" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C241" s="31" t="s">
+      <c r="C242" s="31" t="s">
         <v>573</v>
       </c>
-      <c r="D241" s="6" t="s">
+      <c r="D242" s="6" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="242" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A242" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="B242" s="20"/>
-      <c r="C242" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="D242" s="5" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="243" spans="1:25" ht="15.75" customHeight="1">
       <c r="A243" s="16" t="s">
-        <v>651</v>
+        <v>476</v>
       </c>
       <c r="B243" s="20"/>
       <c r="C243" s="16" t="s">
-        <v>652</v>
+        <v>477</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="244" spans="1:25" ht="15.75" customHeight="1">
       <c r="A244" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B244" s="20"/>
+      <c r="C244" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A245" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="B244" s="20" t="s">
+      <c r="B245" s="20" t="s">
         <v>681</v>
       </c>
-      <c r="C244" s="16" t="s">
+      <c r="C245" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D244" s="5" t="s">
+      <c r="D245" s="5" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="245" spans="1:25">
-      <c r="A245" s="16" t="s">
+    <row r="246" spans="1:25">
+      <c r="A246" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C245" s="16" t="s">
+      <c r="C246" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D245" s="5" t="s">
+      <c r="D246" s="5" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="246" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A246" s="30" t="s">
-        <v>684</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C246" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="247" spans="1:25" ht="15.75" customHeight="1">
       <c r="A247" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C247" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A248" s="30" t="s">
         <v>735</v>
       </c>
-      <c r="B247" s="3"/>
-      <c r="C247" s="30" t="s">
+      <c r="B248" s="3"/>
+      <c r="C248" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="D247" s="2"/>
-    </row>
-    <row r="248" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A248" s="63" t="s">
-        <v>858</v>
-      </c>
-      <c r="B248" s="64" t="s">
-        <v>856</v>
-      </c>
-      <c r="C248" s="63" t="s">
-        <v>857</v>
-      </c>
-      <c r="D248" s="65" t="s">
-        <v>859</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
-      <c r="J248" s="2"/>
-      <c r="K248" s="2"/>
-      <c r="L248" s="2"/>
-      <c r="M248" s="2"/>
-      <c r="N248" s="2"/>
-      <c r="O248" s="2"/>
-      <c r="P248" s="2"/>
-      <c r="Q248" s="2"/>
-      <c r="R248" s="2"/>
-      <c r="S248" s="2"/>
-      <c r="T248" s="2"/>
-      <c r="U248" s="2"/>
-      <c r="V248" s="2"/>
-      <c r="W248" s="2"/>
-      <c r="X248" s="2"/>
-      <c r="Y248" s="2"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" spans="1:25" ht="15.75" customHeight="1">
       <c r="A249" s="63" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B249" s="64" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C249" s="63" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D249" s="65" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
@@ -7571,59 +7557,93 @@
       <c r="Y249" s="2"/>
     </row>
     <row r="250" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A250" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>487</v>
-      </c>
+      <c r="A250" s="63" t="s">
+        <v>862</v>
+      </c>
+      <c r="B250" s="64" t="s">
+        <v>860</v>
+      </c>
+      <c r="C250" s="63" t="s">
+        <v>861</v>
+      </c>
+      <c r="D250" s="65" t="s">
+        <v>863</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+      <c r="I250" s="2"/>
+      <c r="J250" s="2"/>
+      <c r="K250" s="2"/>
+      <c r="L250" s="2"/>
+      <c r="M250" s="2"/>
+      <c r="N250" s="2"/>
+      <c r="O250" s="2"/>
+      <c r="P250" s="2"/>
+      <c r="Q250" s="2"/>
+      <c r="R250" s="2"/>
+      <c r="S250" s="2"/>
+      <c r="T250" s="2"/>
+      <c r="U250" s="2"/>
+      <c r="V250" s="2"/>
+      <c r="W250" s="2"/>
+      <c r="X250" s="2"/>
+      <c r="Y250" s="2"/>
     </row>
     <row r="251" spans="1:25" ht="15.75" customHeight="1">
       <c r="A251" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A252" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B251" s="35" t="s">
+      <c r="B252" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C252" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="D252" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A252" s="58" t="s">
+    <row r="253" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A253" s="58" t="s">
         <v>478</v>
       </c>
-      <c r="B252" s="6" t="s">
+      <c r="B253" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C252" s="31" t="s">
+      <c r="C253" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="D252" s="6" t="s">
+      <c r="D253" s="6" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A253" s="2" t="s">
+    <row r="254" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A254" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B254" t="s">
         <v>786</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C254" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="255" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="256" spans="1:25" ht="15.75" customHeight="1"/>
     <row r="257" ht="15.75" customHeight="1"/>
@@ -8552,11 +8572,12 @@
     <row r="1180" ht="15.75" customHeight="1"/>
     <row r="1181" ht="15.75" customHeight="1"/>
     <row r="1182" ht="15.75" customHeight="1"/>
+    <row r="1183" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B245" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B246" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="B21" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D21" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="B26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -8654,15 +8675,15 @@
     <hyperlink ref="B220" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
     <hyperlink ref="B221" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
     <hyperlink ref="B222" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B233" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B236" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B237" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B238" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="B234" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B237" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="B238" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="B239" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
     <hyperlink ref="B167" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B246" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B247" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
     <hyperlink ref="B83" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B250" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B251" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="B251" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B252" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
     <hyperlink ref="B115" r:id="rId110" display="https://reconcile.gnd.network/gnd/4142078-0" xr:uid="{B8894048-7ABE-4D4D-8C7A-CA8FEB064ED8}"/>
     <hyperlink ref="B144" r:id="rId111" display="https://reconcile.gnd.network/gnd/4777777-1" xr:uid="{0339D8C4-8531-904F-B5E1-CE32AEDE7C8A}"/>
     <hyperlink ref="B232" r:id="rId112" display="https://reconcile.gnd.network/gnd/4271516-7" xr:uid="{131A5B64-43BD-934F-A89A-71B867E96CB7}"/>
@@ -8680,12 +8701,12 @@
     <hyperlink ref="B110" r:id="rId124" xr:uid="{5C25490C-D700-6E4E-8FB9-C82DAE83BA73}"/>
     <hyperlink ref="D110" r:id="rId125" xr:uid="{8780E0A3-3A0F-0B40-94C5-5B0999F3CE9A}"/>
     <hyperlink ref="B136" r:id="rId126" xr:uid="{75279FAC-4D2C-3F4D-91B0-C4D1E087BA6F}"/>
-    <hyperlink ref="B240" r:id="rId127" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
-    <hyperlink ref="D240" r:id="rId128" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
-    <hyperlink ref="B241" r:id="rId129" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
-    <hyperlink ref="D241" r:id="rId130" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
-    <hyperlink ref="B252" r:id="rId131" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
-    <hyperlink ref="D252" r:id="rId132" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
+    <hyperlink ref="B241" r:id="rId127" xr:uid="{E291A450-3237-7F43-AA89-E9AEA3916579}"/>
+    <hyperlink ref="D241" r:id="rId128" xr:uid="{E7904F2F-CD47-DF42-9E62-A1B8BF68BC3F}"/>
+    <hyperlink ref="B242" r:id="rId129" xr:uid="{7E5AACB8-62E9-8E40-A26B-2B75FFE82466}"/>
+    <hyperlink ref="D242" r:id="rId130" xr:uid="{A9569EF5-13BC-604C-83D0-9DB159A012F7}"/>
+    <hyperlink ref="B253" r:id="rId131" xr:uid="{8A002831-7543-DA40-B0F2-E5DE201A1301}"/>
+    <hyperlink ref="D253" r:id="rId132" xr:uid="{7E13D368-E02D-6B40-B0CE-B480B6252E4D}"/>
     <hyperlink ref="B25" r:id="rId133" xr:uid="{A352DE32-B947-2E4B-BCD4-43B1C9CED900}"/>
     <hyperlink ref="B20" r:id="rId134" xr:uid="{5C1B02C6-3E34-1446-8161-B8F12EF7AE97}"/>
     <hyperlink ref="B77" r:id="rId135" xr:uid="{3E6D0A41-8127-5042-B6C4-7E9EA8A749BA}"/>
@@ -8715,13 +8736,14 @@
     <hyperlink ref="B122" r:id="rId159" xr:uid="{11B0BE32-8750-FF4D-BE35-F123CC7F462C}"/>
     <hyperlink ref="B153" r:id="rId160" xr:uid="{EE64827B-2F7B-2144-AB5C-9D496B0649E5}"/>
     <hyperlink ref="B168" r:id="rId161" xr:uid="{24423ED9-B692-2647-B3BC-E6C1ABF6EF15}"/>
-    <hyperlink ref="B248" r:id="rId162" xr:uid="{9A59C1DE-E4DD-8B45-9363-F539266D8923}"/>
-    <hyperlink ref="B249" r:id="rId163" xr:uid="{ED036015-8086-4B49-A150-4A8112E7A493}"/>
+    <hyperlink ref="B249" r:id="rId162" xr:uid="{9A59C1DE-E4DD-8B45-9363-F539266D8923}"/>
+    <hyperlink ref="B250" r:id="rId163" xr:uid="{ED036015-8086-4B49-A150-4A8112E7A493}"/>
+    <hyperlink ref="B233" r:id="rId164" tooltip="https://d-nb.info/gnd/7518596-9" xr:uid="{105CEFC0-4117-F441-8CE3-F0A48E573109}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId164"/>
+    <tablePart r:id="rId165"/>
   </tableParts>
 </worksheet>
 </file>